--- a/Daniil/задание 1.xlsx
+++ b/Daniil/задание 1.xlsx
@@ -18,12 +18,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0000E+00"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
     <numFmt numFmtId="166" formatCode="0.000000"/>
+    <numFmt numFmtId="167" formatCode="0.000E+00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,11 +43,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00548235"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +93,11 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -115,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -124,10 +134,14 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -155,6 +169,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -984,7 +1002,7 @@
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="0.000" sourceLinked="0"/>
+        <numFmt formatCode="0.00E+00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="20"/>
@@ -1081,7 +1099,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Sheet1'!D9</f>
+              <f>'Sheet1'!J69</f>
             </strRef>
           </tx>
           <spPr>
@@ -1102,7 +1120,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$A$10:$A$60</f>
+              <f>'Sheet1'!$I$70:$I$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -1110,161 +1128,161 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>5e-05</v>
+                  <v>1.5e-06</v>
                 </pt>
                 <pt idx="2">
-                  <v>0.0001</v>
+                  <v>3e-06</v>
                 </pt>
                 <pt idx="3">
-                  <v>0.00015</v>
+                  <v>4.5e-06</v>
                 </pt>
                 <pt idx="4">
-                  <v>0.0002</v>
+                  <v>6e-06</v>
                 </pt>
                 <pt idx="5">
-                  <v>0.00025</v>
+                  <v>7.5e-06</v>
                 </pt>
                 <pt idx="6">
-                  <v>0.0003</v>
+                  <v>9e-06</v>
                 </pt>
                 <pt idx="7">
-                  <v>0.00035</v>
+                  <v>1.05e-05</v>
                 </pt>
                 <pt idx="8">
-                  <v>0.0004</v>
+                  <v>1.2e-05</v>
                 </pt>
                 <pt idx="9">
-                  <v>0.00045</v>
+                  <v>1.35e-05</v>
                 </pt>
                 <pt idx="10">
-                  <v>0.0005</v>
+                  <v>1.5e-05</v>
                 </pt>
                 <pt idx="11">
-                  <v>0.00055</v>
+                  <v>1.65e-05</v>
                 </pt>
                 <pt idx="12">
-                  <v>0.0006</v>
+                  <v>1.8e-05</v>
                 </pt>
                 <pt idx="13">
-                  <v>0.00065</v>
+                  <v>1.95e-05</v>
                 </pt>
                 <pt idx="14">
-                  <v>0.0007</v>
+                  <v>2.1e-05</v>
                 </pt>
                 <pt idx="15">
-                  <v>0.00075</v>
+                  <v>2.25e-05</v>
                 </pt>
                 <pt idx="16">
-                  <v>0.0008</v>
+                  <v>2.4e-05</v>
                 </pt>
                 <pt idx="17">
-                  <v>0.00085</v>
+                  <v>2.55e-05</v>
                 </pt>
                 <pt idx="18">
-                  <v>0.0009</v>
+                  <v>2.7e-05</v>
                 </pt>
                 <pt idx="19">
-                  <v>0.00095</v>
+                  <v>2.85e-05</v>
                 </pt>
                 <pt idx="20">
-                  <v>0.001</v>
+                  <v>3e-05</v>
                 </pt>
                 <pt idx="21">
-                  <v>0.00105</v>
+                  <v>3.15e-05</v>
                 </pt>
                 <pt idx="22">
-                  <v>0.0011</v>
+                  <v>3.3e-05</v>
                 </pt>
                 <pt idx="23">
-                  <v>0.00115</v>
+                  <v>3.45e-05</v>
                 </pt>
                 <pt idx="24">
-                  <v>0.0012</v>
+                  <v>3.6e-05</v>
                 </pt>
                 <pt idx="25">
-                  <v>0.00125</v>
+                  <v>3.75e-05</v>
                 </pt>
                 <pt idx="26">
-                  <v>0.0013</v>
+                  <v>3.9e-05</v>
                 </pt>
                 <pt idx="27">
-                  <v>0.00135</v>
+                  <v>4.05e-05</v>
                 </pt>
                 <pt idx="28">
-                  <v>0.0014</v>
+                  <v>4.2e-05</v>
                 </pt>
                 <pt idx="29">
-                  <v>0.00145</v>
+                  <v>4.35e-05</v>
                 </pt>
                 <pt idx="30">
-                  <v>0.0015</v>
+                  <v>4.5e-05</v>
                 </pt>
                 <pt idx="31">
-                  <v>0.00155</v>
+                  <v>4.65e-05</v>
                 </pt>
                 <pt idx="32">
-                  <v>0.0016</v>
+                  <v>4.8e-05</v>
                 </pt>
                 <pt idx="33">
-                  <v>0.00165</v>
+                  <v>4.95e-05</v>
                 </pt>
                 <pt idx="34">
-                  <v>0.0017</v>
+                  <v>5.1e-05</v>
                 </pt>
                 <pt idx="35">
-                  <v>0.00175</v>
+                  <v>5.25e-05</v>
                 </pt>
                 <pt idx="36">
-                  <v>0.0018</v>
+                  <v>5.4e-05</v>
                 </pt>
                 <pt idx="37">
-                  <v>0.00185</v>
+                  <v>5.55e-05</v>
                 </pt>
                 <pt idx="38">
-                  <v>0.0019</v>
+                  <v>5.7e-05</v>
                 </pt>
                 <pt idx="39">
-                  <v>0.00195</v>
+                  <v>5.85e-05</v>
                 </pt>
                 <pt idx="40">
-                  <v>0.002</v>
+                  <v>6e-05</v>
                 </pt>
                 <pt idx="41">
-                  <v>0.00205</v>
+                  <v>6.15e-05</v>
                 </pt>
                 <pt idx="42">
-                  <v>0.0021</v>
+                  <v>6.3e-05</v>
                 </pt>
                 <pt idx="43">
-                  <v>0.00215</v>
+                  <v>6.45e-05</v>
                 </pt>
                 <pt idx="44">
-                  <v>0.0022</v>
+                  <v>6.6e-05</v>
                 </pt>
                 <pt idx="45">
-                  <v>0.00225</v>
+                  <v>6.75e-05</v>
                 </pt>
                 <pt idx="46">
-                  <v>0.0023</v>
+                  <v>6.9e-05</v>
                 </pt>
                 <pt idx="47">
-                  <v>0.00235</v>
+                  <v>7.05e-05</v>
                 </pt>
                 <pt idx="48">
-                  <v>0.0024</v>
+                  <v>7.2e-05</v>
                 </pt>
                 <pt idx="49">
-                  <v>0.00245</v>
+                  <v>7.35e-05</v>
                 </pt>
                 <pt idx="50">
-                  <v>0.0025</v>
+                  <v>7.5e-05</v>
                 </pt>
               </numCache>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Sheet1'!$D$10:$D$60</f>
+              <f>'Sheet1'!$J$70:$J$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -1272,154 +1290,154 @@
                   <v>0.0666666666666667</v>
                 </pt>
                 <pt idx="1">
-                  <v>8.48422534226539e-05</v>
+                  <v>0.0545820502051988</v>
                 </pt>
                 <pt idx="2">
-                  <v>1.07973119487507e-07</v>
+                  <v>0.0446880030690426</v>
                 </pt>
                 <pt idx="3">
-                  <v>1.37410241495903e-10</v>
+                  <v>0.0365874424062684</v>
                 </pt>
                 <pt idx="4">
-                  <v>1.74872917977953e-13</v>
+                  <v>0.0299552642744814</v>
                 </pt>
                 <pt idx="5">
-                  <v>2.22549186357667e-16</v>
+                  <v>0.0245252960780962</v>
                 </pt>
                 <pt idx="6">
-                  <v>2.83223617019437e-19</v>
+                  <v>0.0200796141274801</v>
                 </pt>
                 <pt idx="7">
-                  <v>3.60439948356657e-22</v>
+                  <v>0.0164397975961071</v>
                 </pt>
                 <pt idx="8">
-                  <v>4.58708061631858e-25</v>
+                  <v>0.0134597678663104</v>
                 </pt>
                 <pt idx="9">
-                  <v>5.83767384179764e-28</v>
+                  <v>0.0110199258814391</v>
                 </pt>
                 <pt idx="10">
-                  <v>7.42922105226891e-31</v>
+                  <v>0.00902235221577418</v>
                 </pt>
                 <pt idx="11">
-                  <v>9.45467782874267e-34</v>
+                  <v>0.00738687722415559</v>
                 </pt>
                 <pt idx="12">
-                  <v>1.20323425856359e-36</v>
+                  <v>0.0060478635526275</v>
                 </pt>
                 <pt idx="13">
-                  <v>1.53127658837806e-39</v>
+                  <v>0.00495157188095559</v>
                 </pt>
                 <pt idx="14">
-                  <v>1.94875434557025e-42</v>
+                  <v>0.00405400417501453</v>
                 </pt>
                 <pt idx="15">
-                  <v>2.48005065068056e-45</v>
+                  <v>0.00331913789119093</v>
                 </pt>
                 <pt idx="16">
-                  <v>3.15619628709085e-48</v>
+                  <v>0.00271748026522441</v>
                 </pt>
                 <pt idx="17">
-                  <v>4.016682078615e-51</v>
+                  <v>0.00222488466402174</v>
                 </pt>
                 <pt idx="18">
-                  <v>5.11176538248126e-54</v>
+                  <v>0.00182158149648617</v>
                 </pt>
                 <pt idx="19">
-                  <v>6.50540541026443e-57</v>
+                  <v>0.00149138479041104</v>
                 </pt>
                 <pt idx="20">
-                  <v>8.27899881652133e-60</v>
+                  <v>0.00122104259258228</v>
                 </pt>
                 <pt idx="21">
-                  <v>1.05361337351571e-62</v>
+                  <v>0.00099970512136518</v>
                 </pt>
                 <pt idx="22">
-                  <v>1.34086399267977e-65</v>
+                  <v>0.000818489326871229</v>
                 </pt>
                 <pt idx="23">
-                  <v>1.70642884008375e-68</v>
+                  <v>0.000670122382975572</v>
                 </pt>
                 <pt idx="24">
-                  <v>2.17165902147162e-71</v>
+                  <v>0.000548649803268002</v>
                 </pt>
                 <pt idx="25">
-                  <v>2.76372667570942e-74</v>
+                  <v>0.000449196466605697</v>
                 </pt>
                 <pt idx="26">
-                  <v>3.51721198517214e-77</v>
+                  <v>0.000367770961384051</v>
                 </pt>
                 <pt idx="27">
-                  <v>4.47612285880773e-80</v>
+                  <v>0.000301105396174177</v>
                 </pt>
                 <pt idx="28">
-                  <v>5.69646524906838e-83</v>
+                  <v>0.000246524247765529</v>
                 </pt>
                 <pt idx="29">
-                  <v>7.24951422412208e-86</v>
+                  <v>0.000201836983025054</v>
                 </pt>
                 <pt idx="30">
-                  <v>9.22597684491158e-89</v>
+                  <v>0.00016525014511109</v>
                 </pt>
                 <pt idx="31">
-                  <v>1.17412899832123e-91</v>
+                  <v>0.000135295375753049</v>
                 </pt>
                 <pt idx="32">
-                  <v>1.49423625039691e-94</v>
+                  <v>0.000110770484878262</v>
                 </pt>
                 <pt idx="33">
-                  <v>1.90161555944232e-97</v>
+                  <v>9.06912025031928e-05</v>
                 </pt>
                 <pt idx="34">
-                  <v>2.42006023810003e-100</v>
+                  <v>7.42516765229869e-05</v>
                 </pt>
                 <pt idx="35">
-                  <v>3.07985046028459e-103</v>
+                  <v>6.07921310369678e-05</v>
                 </pt>
                 <pt idx="36">
-                  <v>3.91952179883007e-106</v>
+                  <v>4.97723872251119e-05</v>
                 </pt>
                 <pt idx="37">
-                  <v>4.9881159262794e-109</v>
+                  <v>4.07501840753048e-05</v>
                 </pt>
                 <pt idx="38">
-                  <v>6.34804493278465e-112</v>
+                  <v>3.33634288960407e-05</v>
                 </pt>
                 <pt idx="39">
-                  <v>8.07873655388572e-115</v>
+                  <v>2.73156652653191e-05</v>
                 </pt>
                 <pt idx="40">
-                  <v>1.02812732105942e-117</v>
+                  <v>2.23641751935008e-05</v>
                 </pt>
                 <pt idx="41">
-                  <v>1.30842958086114e-120</v>
+                  <v>1.83102379981428e-05</v>
                 </pt>
                 <pt idx="42">
-                  <v>1.66515171127674e-123</v>
+                  <v>1.49911549452565e-05</v>
                 </pt>
                 <pt idx="43">
-                  <v>2.11912835212968e-126</v>
+                  <v>1.22737195778386e-05</v>
                 </pt>
                 <pt idx="44">
-                  <v>2.69687437029771e-129</v>
+                  <v>1.00488716730318e-05</v>
                 </pt>
                 <pt idx="45">
-                  <v>3.43213348160801e-132</v>
+                  <v>8.2273202724453e-06</v>
                 </pt>
                 <pt idx="46">
-                  <v>4.36784907940435e-135</v>
+                  <v>6.73596012247289e-06</v>
                 </pt>
                 <pt idx="47">
-                  <v>5.55867237760083e-138</v>
+                  <v>5.51493770377548e-06</v>
                 </pt>
                 <pt idx="48">
-                  <v>7.0741543583086e-141</v>
+                  <v>4.51524909939026e-06</v>
                 </pt>
                 <pt idx="49">
-                  <v>9.00280795227919e-144</v>
+                  <v>3.69677329547846e-06</v>
                 </pt>
                 <pt idx="50">
-                  <v>1.14572777070418e-146</v>
+                  <v>3.02666198416565e-06</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1436,7 +1454,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Sheet1'!E9</f>
+              <f>'Sheet1'!K69</f>
             </strRef>
           </tx>
           <spPr>
@@ -1457,7 +1475,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$A$10:$A$60</f>
+              <f>'Sheet1'!$I$70:$I$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -1465,161 +1483,161 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>5e-05</v>
+                  <v>1.5e-06</v>
                 </pt>
                 <pt idx="2">
-                  <v>0.0001</v>
+                  <v>3e-06</v>
                 </pt>
                 <pt idx="3">
-                  <v>0.00015</v>
+                  <v>4.5e-06</v>
                 </pt>
                 <pt idx="4">
-                  <v>0.0002</v>
+                  <v>6e-06</v>
                 </pt>
                 <pt idx="5">
-                  <v>0.00025</v>
+                  <v>7.5e-06</v>
                 </pt>
                 <pt idx="6">
-                  <v>0.0003</v>
+                  <v>9e-06</v>
                 </pt>
                 <pt idx="7">
-                  <v>0.00035</v>
+                  <v>1.05e-05</v>
                 </pt>
                 <pt idx="8">
-                  <v>0.0004</v>
+                  <v>1.2e-05</v>
                 </pt>
                 <pt idx="9">
-                  <v>0.00045</v>
+                  <v>1.35e-05</v>
                 </pt>
                 <pt idx="10">
-                  <v>0.0005</v>
+                  <v>1.5e-05</v>
                 </pt>
                 <pt idx="11">
-                  <v>0.00055</v>
+                  <v>1.65e-05</v>
                 </pt>
                 <pt idx="12">
-                  <v>0.0006</v>
+                  <v>1.8e-05</v>
                 </pt>
                 <pt idx="13">
-                  <v>0.00065</v>
+                  <v>1.95e-05</v>
                 </pt>
                 <pt idx="14">
-                  <v>0.0007</v>
+                  <v>2.1e-05</v>
                 </pt>
                 <pt idx="15">
-                  <v>0.00075</v>
+                  <v>2.25e-05</v>
                 </pt>
                 <pt idx="16">
-                  <v>0.0008</v>
+                  <v>2.4e-05</v>
                 </pt>
                 <pt idx="17">
-                  <v>0.00085</v>
+                  <v>2.55e-05</v>
                 </pt>
                 <pt idx="18">
-                  <v>0.0009</v>
+                  <v>2.7e-05</v>
                 </pt>
                 <pt idx="19">
-                  <v>0.00095</v>
+                  <v>2.85e-05</v>
                 </pt>
                 <pt idx="20">
-                  <v>0.001</v>
+                  <v>3e-05</v>
                 </pt>
                 <pt idx="21">
-                  <v>0.00105</v>
+                  <v>3.15e-05</v>
                 </pt>
                 <pt idx="22">
-                  <v>0.0011</v>
+                  <v>3.3e-05</v>
                 </pt>
                 <pt idx="23">
-                  <v>0.00115</v>
+                  <v>3.45e-05</v>
                 </pt>
                 <pt idx="24">
-                  <v>0.0012</v>
+                  <v>3.6e-05</v>
                 </pt>
                 <pt idx="25">
-                  <v>0.00125</v>
+                  <v>3.75e-05</v>
                 </pt>
                 <pt idx="26">
-                  <v>0.0013</v>
+                  <v>3.9e-05</v>
                 </pt>
                 <pt idx="27">
-                  <v>0.00135</v>
+                  <v>4.05e-05</v>
                 </pt>
                 <pt idx="28">
-                  <v>0.0014</v>
+                  <v>4.2e-05</v>
                 </pt>
                 <pt idx="29">
-                  <v>0.00145</v>
+                  <v>4.35e-05</v>
                 </pt>
                 <pt idx="30">
-                  <v>0.0015</v>
+                  <v>4.5e-05</v>
                 </pt>
                 <pt idx="31">
-                  <v>0.00155</v>
+                  <v>4.65e-05</v>
                 </pt>
                 <pt idx="32">
-                  <v>0.0016</v>
+                  <v>4.8e-05</v>
                 </pt>
                 <pt idx="33">
-                  <v>0.00165</v>
+                  <v>4.95e-05</v>
                 </pt>
                 <pt idx="34">
-                  <v>0.0017</v>
+                  <v>5.1e-05</v>
                 </pt>
                 <pt idx="35">
-                  <v>0.00175</v>
+                  <v>5.25e-05</v>
                 </pt>
                 <pt idx="36">
-                  <v>0.0018</v>
+                  <v>5.4e-05</v>
                 </pt>
                 <pt idx="37">
-                  <v>0.00185</v>
+                  <v>5.55e-05</v>
                 </pt>
                 <pt idx="38">
-                  <v>0.0019</v>
+                  <v>5.7e-05</v>
                 </pt>
                 <pt idx="39">
-                  <v>0.00195</v>
+                  <v>5.85e-05</v>
                 </pt>
                 <pt idx="40">
-                  <v>0.002</v>
+                  <v>6e-05</v>
                 </pt>
                 <pt idx="41">
-                  <v>0.00205</v>
+                  <v>6.15e-05</v>
                 </pt>
                 <pt idx="42">
-                  <v>0.0021</v>
+                  <v>6.3e-05</v>
                 </pt>
                 <pt idx="43">
-                  <v>0.00215</v>
+                  <v>6.45e-05</v>
                 </pt>
                 <pt idx="44">
-                  <v>0.0022</v>
+                  <v>6.6e-05</v>
                 </pt>
                 <pt idx="45">
-                  <v>0.00225</v>
+                  <v>6.75e-05</v>
                 </pt>
                 <pt idx="46">
-                  <v>0.0023</v>
+                  <v>6.9e-05</v>
                 </pt>
                 <pt idx="47">
-                  <v>0.00235</v>
+                  <v>7.05e-05</v>
                 </pt>
                 <pt idx="48">
-                  <v>0.0024</v>
+                  <v>7.2e-05</v>
                 </pt>
                 <pt idx="49">
-                  <v>0.00245</v>
+                  <v>7.35e-05</v>
                 </pt>
                 <pt idx="50">
-                  <v>0.0025</v>
+                  <v>7.5e-05</v>
                 </pt>
               </numCache>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Sheet1'!$E$10:$E$60</f>
+              <f>'Sheet1'!$K$70:$K$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -1627,154 +1645,154 @@
                   <v>-8</v>
                 </pt>
                 <pt idx="1">
-                  <v>-0.0101810704107185</v>
+                  <v>-6.54984602462385</v>
                 </pt>
                 <pt idx="2">
-                  <v>-1.29567743385009e-05</v>
+                  <v>-5.36256036828511</v>
                 </pt>
                 <pt idx="3">
-                  <v>-1.64892289795084e-08</v>
+                  <v>-4.39049308875221</v>
                 </pt>
                 <pt idx="4">
-                  <v>-2.09847501573544e-11</v>
+                  <v>-3.59463171293777</v>
                 </pt>
                 <pt idx="5">
-                  <v>-2.670590236292e-14</v>
+                  <v>-2.94303552937154</v>
                 </pt>
                 <pt idx="6">
-                  <v>-3.39868340423325e-17</v>
+                  <v>-2.40955369529762</v>
                 </pt>
                 <pt idx="7">
-                  <v>-4.32527938027989e-20</v>
+                  <v>-1.97277571153285</v>
                 </pt>
                 <pt idx="8">
-                  <v>-5.5044967395823e-23</v>
+                  <v>-1.61517214395724</v>
                 </pt>
                 <pt idx="9">
-                  <v>-7.00520861015717e-26</v>
+                  <v>-1.32239110577269</v>
                 </pt>
                 <pt idx="10">
-                  <v>-8.91506526272269e-29</v>
+                  <v>-1.0826822658929</v>
                 </pt>
                 <pt idx="11">
-                  <v>-1.13456133944912e-31</v>
+                  <v>-0.886425266898671</v>
                 </pt>
                 <pt idx="12">
-                  <v>-1.44388111027631e-34</v>
+                  <v>-0.7257436263153</v>
                 </pt>
                 <pt idx="13">
-                  <v>-1.83753190605368e-37</v>
+                  <v>-0.594188625714671</v>
                 </pt>
                 <pt idx="14">
-                  <v>-2.3385052146843e-40</v>
+                  <v>-0.486480501001744</v>
                 </pt>
                 <pt idx="15">
-                  <v>-2.97606078081667e-43</v>
+                  <v>-0.398296546942911</v>
                 </pt>
                 <pt idx="16">
-                  <v>-3.78743554450902e-46</v>
+                  <v>-0.32609763182693</v>
                 </pt>
                 <pt idx="17">
-                  <v>-4.82001849433799e-49</v>
+                  <v>-0.266986159682609</v>
                 </pt>
                 <pt idx="18">
-                  <v>-6.13411845897751e-52</v>
+                  <v>-0.21858977957834</v>
                 </pt>
                 <pt idx="19">
-                  <v>-7.80648649231731e-55</v>
+                  <v>-0.178966174849325</v>
                 </pt>
                 <pt idx="20">
-                  <v>-9.9347985798256e-58</v>
+                  <v>-0.146525111109873</v>
                 </pt>
                 <pt idx="21">
-                  <v>-1.26433604821885e-60</v>
+                  <v>-0.119964614563822</v>
                 </pt>
                 <pt idx="22">
-                  <v>-1.60903679121573e-63</v>
+                  <v>-0.0982187192245475</v>
                 </pt>
                 <pt idx="23">
-                  <v>-2.0477146081005e-66</v>
+                  <v>-0.0804146859570687</v>
                 </pt>
                 <pt idx="24">
-                  <v>-2.60599082576594e-69</v>
+                  <v>-0.0658379763921602</v>
                 </pt>
                 <pt idx="25">
-                  <v>-3.3164720108513e-72</v>
+                  <v>-0.0539035759926837</v>
                 </pt>
                 <pt idx="26">
-                  <v>-4.22065438220657e-75</v>
+                  <v>-0.0441325153660862</v>
                 </pt>
                 <pt idx="27">
-                  <v>-5.37134743056927e-78</v>
+                  <v>-0.0361326475409013</v>
                 </pt>
                 <pt idx="28">
-                  <v>-6.83575829888206e-81</v>
+                  <v>-0.0295829097318634</v>
                 </pt>
                 <pt idx="29">
-                  <v>-8.6994170689465e-84</v>
+                  <v>-0.0242204379630065</v>
                 </pt>
                 <pt idx="30">
-                  <v>-1.10711722138939e-86</v>
+                  <v>-0.0198300174133309</v>
                 </pt>
                 <pt idx="31">
-                  <v>-1.40895479798548e-89</v>
+                  <v>-0.0162354450903659</v>
                 </pt>
                 <pt idx="32">
-                  <v>-1.79308350047629e-92</v>
+                  <v>-0.0132924581853915</v>
                 </pt>
                 <pt idx="33">
-                  <v>-2.28193867133079e-95</v>
+                  <v>-0.0108829443003831</v>
                 </pt>
                 <pt idx="34">
-                  <v>-2.90407228572004e-98</v>
+                  <v>-0.00891020118275843</v>
                 </pt>
                 <pt idx="35">
-                  <v>-3.69582055234151e-101</v>
+                  <v>-0.00729505572443613</v>
                 </pt>
                 <pt idx="36">
-                  <v>-4.70342615859608e-104</v>
+                  <v>-0.00597268646701343</v>
                 </pt>
                 <pt idx="37">
-                  <v>-5.98573911153528e-107</v>
+                  <v>-0.00489002208903658</v>
                 </pt>
                 <pt idx="38">
-                  <v>-7.61765391934158e-110</v>
+                  <v>-0.00400361146752488</v>
                 </pt>
                 <pt idx="39">
-                  <v>-9.69448386466286e-113</v>
+                  <v>-0.00327787983183829</v>
                 </pt>
                 <pt idx="40">
-                  <v>-1.23375278527131e-115</v>
+                  <v>-0.00268370102322009</v>
                 </pt>
                 <pt idx="41">
-                  <v>-1.57011549703337e-118</v>
+                  <v>-0.00219722855977714</v>
                 </pt>
                 <pt idx="42">
-                  <v>-1.99818205353209e-121</v>
+                  <v>-0.00179893859343079</v>
                 </pt>
                 <pt idx="43">
-                  <v>-2.54295402255562e-124</v>
+                  <v>-0.00147284634934063</v>
                 </pt>
                 <pt idx="44">
-                  <v>-3.23624924435725e-127</v>
+                  <v>-0.00120586460076381</v>
                 </pt>
                 <pt idx="45">
-                  <v>-4.11856017792961e-130</v>
+                  <v>-0.000987278432693436</v>
                 </pt>
                 <pt idx="46">
-                  <v>-5.24141889528522e-133</v>
+                  <v>-0.000808315214696747</v>
                 </pt>
                 <pt idx="47">
-                  <v>-6.670406853121e-136</v>
+                  <v>-0.000661792524453058</v>
                 </pt>
                 <pt idx="48">
-                  <v>-8.48898522997033e-139</v>
+                  <v>-0.000541829891926831</v>
                 </pt>
                 <pt idx="49">
-                  <v>-1.0803369542735e-141</v>
+                  <v>-0.000443612795457416</v>
                 </pt>
                 <pt idx="50">
-                  <v>-1.37487332484501e-144</v>
+                  <v>-0.000363199438099878</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1807,7 +1825,7 @@
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="0.000" sourceLinked="0"/>
+        <numFmt formatCode="0.00E+00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="20"/>
@@ -2630,7 +2648,7 @@
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="0.000" sourceLinked="0"/>
+        <numFmt formatCode="0.00E+00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="20"/>
@@ -2727,7 +2745,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Sheet1'!W9</f>
+              <f>'Sheet1'!AC69</f>
             </strRef>
           </tx>
           <spPr>
@@ -2748,7 +2766,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$T$10:$T$60</f>
+              <f>'Sheet1'!$AB$70:$AB$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -2756,161 +2774,161 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>5e-05</v>
+                  <v>5e-07</v>
                 </pt>
                 <pt idx="2">
-                  <v>0.0001</v>
+                  <v>1e-06</v>
                 </pt>
                 <pt idx="3">
-                  <v>0.00015</v>
+                  <v>1.5e-06</v>
                 </pt>
                 <pt idx="4">
-                  <v>0.0002</v>
+                  <v>2e-06</v>
                 </pt>
                 <pt idx="5">
-                  <v>0.00025</v>
+                  <v>2.5e-06</v>
                 </pt>
                 <pt idx="6">
-                  <v>0.0003</v>
+                  <v>3e-06</v>
                 </pt>
                 <pt idx="7">
-                  <v>0.00035</v>
+                  <v>3.5e-06</v>
                 </pt>
                 <pt idx="8">
-                  <v>0.0004</v>
+                  <v>4e-06</v>
                 </pt>
                 <pt idx="9">
-                  <v>0.00045</v>
+                  <v>4.5e-06</v>
                 </pt>
                 <pt idx="10">
-                  <v>0.0005</v>
+                  <v>5e-06</v>
                 </pt>
                 <pt idx="11">
-                  <v>0.00055</v>
+                  <v>5.5e-06</v>
                 </pt>
                 <pt idx="12">
-                  <v>0.0006</v>
+                  <v>6e-06</v>
                 </pt>
                 <pt idx="13">
-                  <v>0.00065</v>
+                  <v>6.5e-06</v>
                 </pt>
                 <pt idx="14">
-                  <v>0.0007</v>
+                  <v>7e-06</v>
                 </pt>
                 <pt idx="15">
-                  <v>0.00075</v>
+                  <v>7.5e-06</v>
                 </pt>
                 <pt idx="16">
-                  <v>0.0008</v>
+                  <v>8e-06</v>
                 </pt>
                 <pt idx="17">
-                  <v>0.00085</v>
+                  <v>8.5e-06</v>
                 </pt>
                 <pt idx="18">
-                  <v>0.0009</v>
+                  <v>9e-06</v>
                 </pt>
                 <pt idx="19">
-                  <v>0.00095</v>
+                  <v>9.5e-06</v>
                 </pt>
                 <pt idx="20">
-                  <v>0.001</v>
+                  <v>1e-05</v>
                 </pt>
                 <pt idx="21">
-                  <v>0.00105</v>
+                  <v>1.05e-05</v>
                 </pt>
                 <pt idx="22">
-                  <v>0.0011</v>
+                  <v>1.1e-05</v>
                 </pt>
                 <pt idx="23">
-                  <v>0.00115</v>
+                  <v>1.15e-05</v>
                 </pt>
                 <pt idx="24">
-                  <v>0.0012</v>
+                  <v>1.2e-05</v>
                 </pt>
                 <pt idx="25">
-                  <v>0.00125</v>
+                  <v>1.25e-05</v>
                 </pt>
                 <pt idx="26">
-                  <v>0.0013</v>
+                  <v>1.3e-05</v>
                 </pt>
                 <pt idx="27">
-                  <v>0.00135</v>
+                  <v>1.35e-05</v>
                 </pt>
                 <pt idx="28">
-                  <v>0.0014</v>
+                  <v>1.4e-05</v>
                 </pt>
                 <pt idx="29">
-                  <v>0.00145</v>
+                  <v>1.45e-05</v>
                 </pt>
                 <pt idx="30">
-                  <v>0.0015</v>
+                  <v>1.5e-05</v>
                 </pt>
                 <pt idx="31">
-                  <v>0.00155</v>
+                  <v>1.55e-05</v>
                 </pt>
                 <pt idx="32">
-                  <v>0.0016</v>
+                  <v>1.6e-05</v>
                 </pt>
                 <pt idx="33">
-                  <v>0.00165</v>
+                  <v>1.65e-05</v>
                 </pt>
                 <pt idx="34">
-                  <v>0.0017</v>
+                  <v>1.7e-05</v>
                 </pt>
                 <pt idx="35">
-                  <v>0.00175</v>
+                  <v>1.75e-05</v>
                 </pt>
                 <pt idx="36">
-                  <v>0.0018</v>
+                  <v>1.8e-05</v>
                 </pt>
                 <pt idx="37">
-                  <v>0.00185</v>
+                  <v>1.85e-05</v>
                 </pt>
                 <pt idx="38">
-                  <v>0.0019</v>
+                  <v>1.9e-05</v>
                 </pt>
                 <pt idx="39">
-                  <v>0.00195</v>
+                  <v>1.95e-05</v>
                 </pt>
                 <pt idx="40">
-                  <v>0.002</v>
+                  <v>2e-05</v>
                 </pt>
                 <pt idx="41">
-                  <v>0.00205</v>
+                  <v>2.05e-05</v>
                 </pt>
                 <pt idx="42">
-                  <v>0.0021</v>
+                  <v>2.1e-05</v>
                 </pt>
                 <pt idx="43">
-                  <v>0.00215</v>
+                  <v>2.15e-05</v>
                 </pt>
                 <pt idx="44">
-                  <v>0.0022</v>
+                  <v>2.2e-05</v>
                 </pt>
                 <pt idx="45">
-                  <v>0.00225</v>
+                  <v>2.25e-05</v>
                 </pt>
                 <pt idx="46">
-                  <v>0.0023</v>
+                  <v>2.3e-05</v>
                 </pt>
                 <pt idx="47">
-                  <v>0.00235</v>
+                  <v>2.35e-05</v>
                 </pt>
                 <pt idx="48">
-                  <v>0.0024</v>
+                  <v>2.4e-05</v>
                 </pt>
                 <pt idx="49">
-                  <v>0.00245</v>
+                  <v>2.45e-05</v>
                 </pt>
                 <pt idx="50">
-                  <v>0.0025</v>
+                  <v>2.5e-05</v>
                 </pt>
               </numCache>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Sheet1'!$W$10:$W$60</f>
+              <f>'Sheet1'!$AC$70:$AC$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -2918,154 +2936,154 @@
                   <v>0.0666666666666667</v>
                 </pt>
                 <pt idx="1">
-                  <v>1.37410241495903e-10</v>
+                  <v>0.0545820502051988</v>
                 </pt>
                 <pt idx="2">
-                  <v>2.83223617019437e-19</v>
+                  <v>0.0446880030690426</v>
                 </pt>
                 <pt idx="3">
-                  <v>5.8376738417976e-28</v>
+                  <v>0.0365874424062684</v>
                 </pt>
                 <pt idx="4">
-                  <v>1.20323425856359e-36</v>
+                  <v>0.0299552642744814</v>
                 </pt>
                 <pt idx="5">
-                  <v>2.48005065068056e-45</v>
+                  <v>0.0245252960780962</v>
                 </pt>
                 <pt idx="6">
-                  <v>5.11176538248119e-54</v>
+                  <v>0.0200796141274801</v>
                 </pt>
                 <pt idx="7">
-                  <v>1.05361337351571e-62</v>
+                  <v>0.0164397975961071</v>
                 </pt>
                 <pt idx="8">
-                  <v>2.17165902147162e-71</v>
+                  <v>0.0134597678663104</v>
                 </pt>
                 <pt idx="9">
-                  <v>4.4761228588076e-80</v>
+                  <v>0.0110199258814391</v>
                 </pt>
                 <pt idx="10">
-                  <v>9.22597684491158e-89</v>
+                  <v>0.00902235221577418</v>
                 </pt>
                 <pt idx="11">
-                  <v>1.90161555944232e-97</v>
+                  <v>0.00738687722415559</v>
                 </pt>
                 <pt idx="12">
-                  <v>3.91952179882996e-106</v>
+                  <v>0.0060478635526275</v>
                 </pt>
                 <pt idx="13">
-                  <v>8.07873655388526e-115</v>
+                  <v>0.00495157188095559</v>
                 </pt>
                 <pt idx="14">
-                  <v>1.66515171127674e-123</v>
+                  <v>0.00405400417501453</v>
                 </pt>
                 <pt idx="15">
-                  <v>3.43213348160801e-132</v>
+                  <v>0.00331913789119093</v>
                 </pt>
                 <pt idx="16">
-                  <v>7.0741543583086e-141</v>
+                  <v>0.00271748026522441</v>
                 </pt>
                 <pt idx="17">
-                  <v>1.45809188813173e-149</v>
+                  <v>0.00222488466402174</v>
                 </pt>
                 <pt idx="18">
-                  <v>3.00535137707099e-158</v>
+                  <v>0.00182158149648617</v>
                 </pt>
                 <pt idx="19">
-                  <v>6.19449087755058e-167</v>
+                  <v>0.00149138479041104</v>
                 </pt>
                 <pt idx="20">
-                  <v>1.27677973114267e-175</v>
+                  <v>0.00122104259258228</v>
                 </pt>
                 <pt idx="21">
-                  <v>2.63163916790054e-184</v>
+                  <v>0.00099970512136518</v>
                 </pt>
                 <pt idx="22">
-                  <v>5.42421260386971e-193</v>
+                  <v>0.000818489326871229</v>
                 </pt>
                 <pt idx="23">
-                  <v>1.11801354573429e-201</v>
+                  <v>0.000670122382975572</v>
                 </pt>
                 <pt idx="24">
-                  <v>2.30439766972548e-210</v>
+                  <v>0.000548649803268001</v>
                 </pt>
                 <pt idx="25">
-                  <v>4.74971760449419e-219</v>
+                  <v>0.000449196466605698</v>
                 </pt>
                 <pt idx="26">
-                  <v>9.78989764606228e-228</v>
+                  <v>0.000367770961384051</v>
                 </pt>
                 <pt idx="27">
-                  <v>2.0178482996484e-236</v>
+                  <v>0.000301105396174178</v>
                 </pt>
                 <pt idx="28">
-                  <v>4.15909533235178e-245</v>
+                  <v>0.000246524247765529</v>
                 </pt>
                 <pt idx="29">
-                  <v>8.57253441034417e-254</v>
+                  <v>0.000201836983025054</v>
                 </pt>
                 <pt idx="30">
-                  <v>1.76693103533621e-262</v>
+                  <v>0.000165250145111091</v>
                 </pt>
                 <pt idx="31">
-                  <v>3.64191630408192e-271</v>
+                  <v>0.000135295375753049</v>
                 </pt>
                 <pt idx="32">
-                  <v>7.5065489827765e-280</v>
+                  <v>0.000110770484878262</v>
                 </pt>
                 <pt idx="33">
-                  <v>1.54721506278622e-288</v>
+                  <v>9.0691202503193e-05</v>
                 </pt>
                 <pt idx="34">
-                  <v>3.18904793135333e-297</v>
+                  <v>7.42516765229868e-05</v>
                 </pt>
                 <pt idx="35">
-                  <v>6.57311769583985e-306</v>
+                  <v>6.07921310369678e-05</v>
                 </pt>
                 <pt idx="36">
-                  <v>1.35482053494557e-314</v>
+                  <v>4.97723872251119e-05</v>
                 </pt>
                 <pt idx="37">
-                  <v>2.96439387504748e-323</v>
+                  <v>4.07501840753049e-05</v>
                 </pt>
                 <pt idx="38">
-                  <v>0</v>
+                  <v>3.33634288960407e-05</v>
                 </pt>
                 <pt idx="39">
-                  <v>0</v>
+                  <v>2.73156652653191e-05</v>
                 </pt>
                 <pt idx="40">
-                  <v>0</v>
+                  <v>2.23641751935008e-05</v>
                 </pt>
                 <pt idx="41">
-                  <v>0</v>
+                  <v>1.83102379981428e-05</v>
                 </pt>
                 <pt idx="42">
-                  <v>0</v>
+                  <v>1.49911549452565e-05</v>
                 </pt>
                 <pt idx="43">
-                  <v>0</v>
+                  <v>1.22737195778386e-05</v>
                 </pt>
                 <pt idx="44">
-                  <v>0</v>
+                  <v>1.00488716730318e-05</v>
                 </pt>
                 <pt idx="45">
-                  <v>0</v>
+                  <v>8.2273202724453e-06</v>
                 </pt>
                 <pt idx="46">
-                  <v>0</v>
+                  <v>6.73596012247288e-06</v>
                 </pt>
                 <pt idx="47">
-                  <v>0</v>
+                  <v>5.51493770377548e-06</v>
                 </pt>
                 <pt idx="48">
-                  <v>0</v>
+                  <v>4.51524909939025e-06</v>
                 </pt>
                 <pt idx="49">
-                  <v>0</v>
+                  <v>3.69677329547846e-06</v>
                 </pt>
                 <pt idx="50">
-                  <v>0</v>
+                  <v>3.02666198416566e-06</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3082,7 +3100,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Sheet1'!X9</f>
+              <f>'Sheet1'!AD69</f>
             </strRef>
           </tx>
           <spPr>
@@ -3103,7 +3121,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$T$10:$T$60</f>
+              <f>'Sheet1'!$AB$70:$AB$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -3111,161 +3129,161 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>5e-05</v>
+                  <v>5e-07</v>
                 </pt>
                 <pt idx="2">
-                  <v>0.0001</v>
+                  <v>1e-06</v>
                 </pt>
                 <pt idx="3">
-                  <v>0.00015</v>
+                  <v>1.5e-06</v>
                 </pt>
                 <pt idx="4">
-                  <v>0.0002</v>
+                  <v>2e-06</v>
                 </pt>
                 <pt idx="5">
-                  <v>0.00025</v>
+                  <v>2.5e-06</v>
                 </pt>
                 <pt idx="6">
-                  <v>0.0003</v>
+                  <v>3e-06</v>
                 </pt>
                 <pt idx="7">
-                  <v>0.00035</v>
+                  <v>3.5e-06</v>
                 </pt>
                 <pt idx="8">
-                  <v>0.0004</v>
+                  <v>4e-06</v>
                 </pt>
                 <pt idx="9">
-                  <v>0.00045</v>
+                  <v>4.5e-06</v>
                 </pt>
                 <pt idx="10">
-                  <v>0.0005</v>
+                  <v>5e-06</v>
                 </pt>
                 <pt idx="11">
-                  <v>0.00055</v>
+                  <v>5.5e-06</v>
                 </pt>
                 <pt idx="12">
-                  <v>0.0006</v>
+                  <v>6e-06</v>
                 </pt>
                 <pt idx="13">
-                  <v>0.00065</v>
+                  <v>6.5e-06</v>
                 </pt>
                 <pt idx="14">
-                  <v>0.0007</v>
+                  <v>7e-06</v>
                 </pt>
                 <pt idx="15">
-                  <v>0.00075</v>
+                  <v>7.5e-06</v>
                 </pt>
                 <pt idx="16">
-                  <v>0.0008</v>
+                  <v>8e-06</v>
                 </pt>
                 <pt idx="17">
-                  <v>0.00085</v>
+                  <v>8.5e-06</v>
                 </pt>
                 <pt idx="18">
-                  <v>0.0009</v>
+                  <v>9e-06</v>
                 </pt>
                 <pt idx="19">
-                  <v>0.00095</v>
+                  <v>9.5e-06</v>
                 </pt>
                 <pt idx="20">
-                  <v>0.001</v>
+                  <v>1e-05</v>
                 </pt>
                 <pt idx="21">
-                  <v>0.00105</v>
+                  <v>1.05e-05</v>
                 </pt>
                 <pt idx="22">
-                  <v>0.0011</v>
+                  <v>1.1e-05</v>
                 </pt>
                 <pt idx="23">
-                  <v>0.00115</v>
+                  <v>1.15e-05</v>
                 </pt>
                 <pt idx="24">
-                  <v>0.0012</v>
+                  <v>1.2e-05</v>
                 </pt>
                 <pt idx="25">
-                  <v>0.00125</v>
+                  <v>1.25e-05</v>
                 </pt>
                 <pt idx="26">
-                  <v>0.0013</v>
+                  <v>1.3e-05</v>
                 </pt>
                 <pt idx="27">
-                  <v>0.00135</v>
+                  <v>1.35e-05</v>
                 </pt>
                 <pt idx="28">
-                  <v>0.0014</v>
+                  <v>1.4e-05</v>
                 </pt>
                 <pt idx="29">
-                  <v>0.00145</v>
+                  <v>1.45e-05</v>
                 </pt>
                 <pt idx="30">
-                  <v>0.0015</v>
+                  <v>1.5e-05</v>
                 </pt>
                 <pt idx="31">
-                  <v>0.00155</v>
+                  <v>1.55e-05</v>
                 </pt>
                 <pt idx="32">
-                  <v>0.0016</v>
+                  <v>1.6e-05</v>
                 </pt>
                 <pt idx="33">
-                  <v>0.00165</v>
+                  <v>1.65e-05</v>
                 </pt>
                 <pt idx="34">
-                  <v>0.0017</v>
+                  <v>1.7e-05</v>
                 </pt>
                 <pt idx="35">
-                  <v>0.00175</v>
+                  <v>1.75e-05</v>
                 </pt>
                 <pt idx="36">
-                  <v>0.0018</v>
+                  <v>1.8e-05</v>
                 </pt>
                 <pt idx="37">
-                  <v>0.00185</v>
+                  <v>1.85e-05</v>
                 </pt>
                 <pt idx="38">
-                  <v>0.0019</v>
+                  <v>1.9e-05</v>
                 </pt>
                 <pt idx="39">
-                  <v>0.00195</v>
+                  <v>1.95e-05</v>
                 </pt>
                 <pt idx="40">
-                  <v>0.002</v>
+                  <v>2e-05</v>
                 </pt>
                 <pt idx="41">
-                  <v>0.00205</v>
+                  <v>2.05e-05</v>
                 </pt>
                 <pt idx="42">
-                  <v>0.0021</v>
+                  <v>2.1e-05</v>
                 </pt>
                 <pt idx="43">
-                  <v>0.00215</v>
+                  <v>2.15e-05</v>
                 </pt>
                 <pt idx="44">
-                  <v>0.0022</v>
+                  <v>2.2e-05</v>
                 </pt>
                 <pt idx="45">
-                  <v>0.00225</v>
+                  <v>2.25e-05</v>
                 </pt>
                 <pt idx="46">
-                  <v>0.0023</v>
+                  <v>2.3e-05</v>
                 </pt>
                 <pt idx="47">
-                  <v>0.00235</v>
+                  <v>2.35e-05</v>
                 </pt>
                 <pt idx="48">
-                  <v>0.0024</v>
+                  <v>2.4e-05</v>
                 </pt>
                 <pt idx="49">
-                  <v>0.00245</v>
+                  <v>2.45e-05</v>
                 </pt>
                 <pt idx="50">
-                  <v>0.0025</v>
+                  <v>2.5e-05</v>
                 </pt>
               </numCache>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Sheet1'!$X$10:$X$60</f>
+              <f>'Sheet1'!$AD$70:$AD$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -3273,154 +3291,154 @@
                   <v>-8</v>
                 </pt>
                 <pt idx="1">
-                  <v>-1.64892289795084e-08</v>
+                  <v>-6.54984602462385</v>
                 </pt>
                 <pt idx="2">
-                  <v>-3.39868340423325e-17</v>
+                  <v>-5.36256036828511</v>
                 </pt>
                 <pt idx="3">
-                  <v>-7.00520861015712e-26</v>
+                  <v>-4.39049308875221</v>
                 </pt>
                 <pt idx="4">
-                  <v>-1.44388111027631e-34</v>
+                  <v>-3.59463171293777</v>
                 </pt>
                 <pt idx="5">
-                  <v>-2.97606078081667e-43</v>
+                  <v>-2.94303552937154</v>
                 </pt>
                 <pt idx="6">
-                  <v>-6.13411845897743e-52</v>
+                  <v>-2.40955369529762</v>
                 </pt>
                 <pt idx="7">
-                  <v>-1.26433604821885e-60</v>
+                  <v>-1.97277571153285</v>
                 </pt>
                 <pt idx="8">
-                  <v>-2.60599082576594e-69</v>
+                  <v>-1.61517214395724</v>
                 </pt>
                 <pt idx="9">
-                  <v>-5.37134743056912e-78</v>
+                  <v>-1.32239110577269</v>
                 </pt>
                 <pt idx="10">
-                  <v>-1.10711722138939e-86</v>
+                  <v>-1.0826822658929</v>
                 </pt>
                 <pt idx="11">
-                  <v>-2.28193867133079e-95</v>
+                  <v>-0.886425266898671</v>
                 </pt>
                 <pt idx="12">
-                  <v>-4.70342615859595e-104</v>
+                  <v>-0.7257436263153</v>
                 </pt>
                 <pt idx="13">
-                  <v>-9.69448386466231e-113</v>
+                  <v>-0.594188625714671</v>
                 </pt>
                 <pt idx="14">
-                  <v>-1.99818205353209e-121</v>
+                  <v>-0.486480501001744</v>
                 </pt>
                 <pt idx="15">
-                  <v>-4.11856017792961e-130</v>
+                  <v>-0.398296546942912</v>
                 </pt>
                 <pt idx="16">
-                  <v>-8.48898522997033e-139</v>
+                  <v>-0.32609763182693</v>
                 </pt>
                 <pt idx="17">
-                  <v>-1.74971026575808e-147</v>
+                  <v>-0.266986159682609</v>
                 </pt>
                 <pt idx="18">
-                  <v>-3.60642165248519e-156</v>
+                  <v>-0.21858977957834</v>
                 </pt>
                 <pt idx="19">
-                  <v>-7.4333890530607e-165</v>
+                  <v>-0.178966174849325</v>
                 </pt>
                 <pt idx="20">
-                  <v>-1.5321356773712e-173</v>
+                  <v>-0.146525111109873</v>
                 </pt>
                 <pt idx="21">
-                  <v>-3.15796700148065e-182</v>
+                  <v>-0.119964614563822</v>
                 </pt>
                 <pt idx="22">
-                  <v>-6.50905512464365e-191</v>
+                  <v>-0.0982187192245475</v>
                 </pt>
                 <pt idx="23">
-                  <v>-1.34161625488115e-199</v>
+                  <v>-0.0804146859570686</v>
                 </pt>
                 <pt idx="24">
-                  <v>-2.76527720367058e-208</v>
+                  <v>-0.0658379763921602</v>
                 </pt>
                 <pt idx="25">
-                  <v>-5.69966112539303e-217</v>
+                  <v>-0.0539035759926837</v>
                 </pt>
                 <pt idx="26">
-                  <v>-1.17478771752747e-225</v>
+                  <v>-0.0441325153660862</v>
                 </pt>
                 <pt idx="27">
-                  <v>-2.42141795957808e-234</v>
+                  <v>-0.0361326475409013</v>
                 </pt>
                 <pt idx="28">
-                  <v>-4.99091439882213e-243</v>
+                  <v>-0.0295829097318634</v>
                 </pt>
                 <pt idx="29">
-                  <v>-1.0287041292413e-251</v>
+                  <v>-0.0242204379630065</v>
                 </pt>
                 <pt idx="30">
-                  <v>-2.12031724240345e-260</v>
+                  <v>-0.0198300174133309</v>
                 </pt>
                 <pt idx="31">
-                  <v>-4.37029956489831e-269</v>
+                  <v>-0.0162354450903659</v>
                 </pt>
                 <pt idx="32">
-                  <v>-9.00785877933179e-278</v>
+                  <v>-0.0132924581853915</v>
                 </pt>
                 <pt idx="33">
-                  <v>-1.85665807534347e-286</v>
+                  <v>-0.0108829443003832</v>
                 </pt>
                 <pt idx="34">
-                  <v>-3.82685751762399e-295</v>
+                  <v>-0.00891020118275842</v>
                 </pt>
                 <pt idx="35">
-                  <v>-7.88774123500782e-304</v>
+                  <v>-0.00729505572443613</v>
                 </pt>
                 <pt idx="36">
-                  <v>-1.62578464193469e-312</v>
+                  <v>-0.00597268646701343</v>
                 </pt>
                 <pt idx="37">
-                  <v>-3.35964639172048e-321</v>
+                  <v>-0.00489002208903658</v>
                 </pt>
                 <pt idx="38">
-                  <v>-0</v>
+                  <v>-0.00400361146752488</v>
                 </pt>
                 <pt idx="39">
-                  <v>-0</v>
+                  <v>-0.00327787983183829</v>
                 </pt>
                 <pt idx="40">
-                  <v>-0</v>
+                  <v>-0.00268370102322009</v>
                 </pt>
                 <pt idx="41">
-                  <v>-0</v>
+                  <v>-0.00219722855977714</v>
                 </pt>
                 <pt idx="42">
-                  <v>-0</v>
+                  <v>-0.00179893859343079</v>
                 </pt>
                 <pt idx="43">
-                  <v>-0</v>
+                  <v>-0.00147284634934063</v>
                 </pt>
                 <pt idx="44">
-                  <v>-0</v>
+                  <v>-0.00120586460076381</v>
                 </pt>
                 <pt idx="45">
-                  <v>-0</v>
+                  <v>-0.000987278432693436</v>
                 </pt>
                 <pt idx="46">
-                  <v>-0</v>
+                  <v>-0.000808315214696746</v>
                 </pt>
                 <pt idx="47">
-                  <v>-0</v>
+                  <v>-0.000661792524453058</v>
                 </pt>
                 <pt idx="48">
-                  <v>-0</v>
+                  <v>-0.00054182989192683</v>
                 </pt>
                 <pt idx="49">
-                  <v>-0</v>
+                  <v>-0.000443612795457416</v>
                 </pt>
                 <pt idx="50">
-                  <v>-0</v>
+                  <v>-0.000363199438099879</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3453,7 +3471,7 @@
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="0.000" sourceLinked="0"/>
+        <numFmt formatCode="0.00E+00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="20"/>
@@ -4276,7 +4294,7 @@
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="0.000" sourceLinked="0"/>
+        <numFmt formatCode="0.00E+00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="20"/>
@@ -4373,7 +4391,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Sheet1'!AR9</f>
+              <f>'Sheet1'!AX69</f>
             </strRef>
           </tx>
           <spPr>
@@ -4394,7 +4412,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$AO$10:$AO$60</f>
+              <f>'Sheet1'!$AW$70:$AW$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -4402,161 +4420,161 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>5e-05</v>
+                  <v>1.5e-05</v>
                 </pt>
                 <pt idx="2">
-                  <v>0.0001</v>
+                  <v>3e-05</v>
                 </pt>
                 <pt idx="3">
+                  <v>4.5e-05</v>
+                </pt>
+                <pt idx="4">
+                  <v>6e-05</v>
+                </pt>
+                <pt idx="5">
+                  <v>7.5e-05</v>
+                </pt>
+                <pt idx="6">
+                  <v>9e-05</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.000105</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.00012</v>
+                </pt>
+                <pt idx="9">
+                  <v>0.000135</v>
+                </pt>
+                <pt idx="10">
                   <v>0.00015</v>
                 </pt>
-                <pt idx="4">
-                  <v>0.0002</v>
-                </pt>
-                <pt idx="5">
-                  <v>0.00025</v>
-                </pt>
-                <pt idx="6">
+                <pt idx="11">
+                  <v>0.000165</v>
+                </pt>
+                <pt idx="12">
+                  <v>0.00018</v>
+                </pt>
+                <pt idx="13">
+                  <v>0.000195</v>
+                </pt>
+                <pt idx="14">
+                  <v>0.00021</v>
+                </pt>
+                <pt idx="15">
+                  <v>0.000225</v>
+                </pt>
+                <pt idx="16">
+                  <v>0.00024</v>
+                </pt>
+                <pt idx="17">
+                  <v>0.000255</v>
+                </pt>
+                <pt idx="18">
+                  <v>0.00027</v>
+                </pt>
+                <pt idx="19">
+                  <v>0.000285</v>
+                </pt>
+                <pt idx="20">
                   <v>0.0003</v>
                 </pt>
-                <pt idx="7">
-                  <v>0.00035</v>
-                </pt>
-                <pt idx="8">
-                  <v>0.0004</v>
-                </pt>
-                <pt idx="9">
+                <pt idx="21">
+                  <v>0.000315</v>
+                </pt>
+                <pt idx="22">
+                  <v>0.00033</v>
+                </pt>
+                <pt idx="23">
+                  <v>0.000345</v>
+                </pt>
+                <pt idx="24">
+                  <v>0.00036</v>
+                </pt>
+                <pt idx="25">
+                  <v>0.000375</v>
+                </pt>
+                <pt idx="26">
+                  <v>0.00039</v>
+                </pt>
+                <pt idx="27">
+                  <v>0.000405</v>
+                </pt>
+                <pt idx="28">
+                  <v>0.00042</v>
+                </pt>
+                <pt idx="29">
+                  <v>0.000435</v>
+                </pt>
+                <pt idx="30">
                   <v>0.00045</v>
                 </pt>
-                <pt idx="10">
-                  <v>0.0005</v>
-                </pt>
-                <pt idx="11">
-                  <v>0.00055</v>
-                </pt>
-                <pt idx="12">
+                <pt idx="31">
+                  <v>0.000465</v>
+                </pt>
+                <pt idx="32">
+                  <v>0.00048</v>
+                </pt>
+                <pt idx="33">
+                  <v>0.000495</v>
+                </pt>
+                <pt idx="34">
+                  <v>0.00051</v>
+                </pt>
+                <pt idx="35">
+                  <v>0.000525</v>
+                </pt>
+                <pt idx="36">
+                  <v>0.00054</v>
+                </pt>
+                <pt idx="37">
+                  <v>0.000555</v>
+                </pt>
+                <pt idx="38">
+                  <v>0.00057</v>
+                </pt>
+                <pt idx="39">
+                  <v>0.000585</v>
+                </pt>
+                <pt idx="40">
                   <v>0.0006</v>
                 </pt>
-                <pt idx="13">
-                  <v>0.00065</v>
-                </pt>
-                <pt idx="14">
-                  <v>0.0007</v>
-                </pt>
-                <pt idx="15">
+                <pt idx="41">
+                  <v>0.000615</v>
+                </pt>
+                <pt idx="42">
+                  <v>0.00063</v>
+                </pt>
+                <pt idx="43">
+                  <v>0.000645</v>
+                </pt>
+                <pt idx="44">
+                  <v>0.00066</v>
+                </pt>
+                <pt idx="45">
+                  <v>0.000675</v>
+                </pt>
+                <pt idx="46">
+                  <v>0.00069</v>
+                </pt>
+                <pt idx="47">
+                  <v>0.000705</v>
+                </pt>
+                <pt idx="48">
+                  <v>0.00072</v>
+                </pt>
+                <pt idx="49">
+                  <v>0.000735</v>
+                </pt>
+                <pt idx="50">
                   <v>0.00075</v>
-                </pt>
-                <pt idx="16">
-                  <v>0.0008</v>
-                </pt>
-                <pt idx="17">
-                  <v>0.00085</v>
-                </pt>
-                <pt idx="18">
-                  <v>0.0009</v>
-                </pt>
-                <pt idx="19">
-                  <v>0.00095</v>
-                </pt>
-                <pt idx="20">
-                  <v>0.001</v>
-                </pt>
-                <pt idx="21">
-                  <v>0.00105</v>
-                </pt>
-                <pt idx="22">
-                  <v>0.0011</v>
-                </pt>
-                <pt idx="23">
-                  <v>0.00115</v>
-                </pt>
-                <pt idx="24">
-                  <v>0.0012</v>
-                </pt>
-                <pt idx="25">
-                  <v>0.00125</v>
-                </pt>
-                <pt idx="26">
-                  <v>0.0013</v>
-                </pt>
-                <pt idx="27">
-                  <v>0.00135</v>
-                </pt>
-                <pt idx="28">
-                  <v>0.0014</v>
-                </pt>
-                <pt idx="29">
-                  <v>0.00145</v>
-                </pt>
-                <pt idx="30">
-                  <v>0.0015</v>
-                </pt>
-                <pt idx="31">
-                  <v>0.00155</v>
-                </pt>
-                <pt idx="32">
-                  <v>0.0016</v>
-                </pt>
-                <pt idx="33">
-                  <v>0.00165</v>
-                </pt>
-                <pt idx="34">
-                  <v>0.0017</v>
-                </pt>
-                <pt idx="35">
-                  <v>0.00175</v>
-                </pt>
-                <pt idx="36">
-                  <v>0.0018</v>
-                </pt>
-                <pt idx="37">
-                  <v>0.00185</v>
-                </pt>
-                <pt idx="38">
-                  <v>0.0019</v>
-                </pt>
-                <pt idx="39">
-                  <v>0.00195</v>
-                </pt>
-                <pt idx="40">
-                  <v>0.002</v>
-                </pt>
-                <pt idx="41">
-                  <v>0.00205</v>
-                </pt>
-                <pt idx="42">
-                  <v>0.0021</v>
-                </pt>
-                <pt idx="43">
-                  <v>0.00215</v>
-                </pt>
-                <pt idx="44">
-                  <v>0.0022</v>
-                </pt>
-                <pt idx="45">
-                  <v>0.00225</v>
-                </pt>
-                <pt idx="46">
-                  <v>0.0023</v>
-                </pt>
-                <pt idx="47">
-                  <v>0.00235</v>
-                </pt>
-                <pt idx="48">
-                  <v>0.0024</v>
-                </pt>
-                <pt idx="49">
-                  <v>0.00245</v>
-                </pt>
-                <pt idx="50">
-                  <v>0.0025</v>
                 </pt>
               </numCache>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Sheet1'!$AR$10:$AR$60</f>
+              <f>'Sheet1'!$AX$70:$AX$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -4564,154 +4582,154 @@
                   <v>0.666666666666667</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.342278079355061</v>
+                  <v>0.545820502051988</v>
                 </pt>
                 <pt idx="2">
-                  <v>0.175731425410484</v>
+                  <v>0.446880030690426</v>
                 </pt>
                 <pt idx="3">
-                  <v>0.0902235221577417</v>
+                  <v>0.365874424062684</v>
                 </pt>
                 <pt idx="4">
-                  <v>0.046322300815201</v>
+                  <v>0.299552642744814</v>
                 </pt>
                 <pt idx="5">
-                  <v>0.0237826622315016</v>
+                  <v>0.245252960780962</v>
                 </pt>
                 <pt idx="6">
+                  <v>0.200796141274801</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.164397975961071</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.134597678663104</v>
+                </pt>
+                <pt idx="9">
+                  <v>0.110199258814391</v>
+                </pt>
+                <pt idx="10">
+                  <v>0.0902235221577418</v>
+                </pt>
+                <pt idx="11">
+                  <v>0.0738687722415559</v>
+                </pt>
+                <pt idx="12">
+                  <v>0.060478635526275</v>
+                </pt>
+                <pt idx="13">
+                  <v>0.0495157188095559</v>
+                </pt>
+                <pt idx="14">
+                  <v>0.0405400417501453</v>
+                </pt>
+                <pt idx="15">
+                  <v>0.0331913789119093</v>
+                </pt>
+                <pt idx="16">
+                  <v>0.0271748026522441</v>
+                </pt>
+                <pt idx="17">
+                  <v>0.0222488466402174</v>
+                </pt>
+                <pt idx="18">
+                  <v>0.0182158149648617</v>
+                </pt>
+                <pt idx="19">
+                  <v>0.0149138479041104</v>
+                </pt>
+                <pt idx="20">
                   <v>0.0122104259258228</v>
                 </pt>
-                <pt idx="7">
-                  <v>0.00626904170099681</v>
-                </pt>
-                <pt idx="8">
-                  <v>0.00321863332922096</v>
-                </pt>
-                <pt idx="9">
+                <pt idx="21">
+                  <v>0.00999705121365181</v>
+                </pt>
+                <pt idx="22">
+                  <v>0.00818489326871229</v>
+                </pt>
+                <pt idx="23">
+                  <v>0.00670122382975572</v>
+                </pt>
+                <pt idx="24">
+                  <v>0.00548649803268002</v>
+                </pt>
+                <pt idx="25">
+                  <v>0.00449196466605698</v>
+                </pt>
+                <pt idx="26">
+                  <v>0.00367770961384052</v>
+                </pt>
+                <pt idx="27">
+                  <v>0.00301105396174178</v>
+                </pt>
+                <pt idx="28">
+                  <v>0.00246524247765529</v>
+                </pt>
+                <pt idx="29">
+                  <v>0.00201836983025055</v>
+                </pt>
+                <pt idx="30">
                   <v>0.0016525014511109</v>
                 </pt>
-                <pt idx="10">
-                  <v>0.000848422534226539</v>
-                </pt>
-                <pt idx="11">
-                  <v>0.00043559465324492</v>
-                </pt>
-                <pt idx="12">
-                  <v>0.000223641751935007</v>
-                </pt>
-                <pt idx="13">
-                  <v>0.000114821503973873</v>
-                </pt>
-                <pt idx="14">
-                  <v>5.89513257732555e-05</v>
-                </pt>
-                <pt idx="15">
-                  <v>3.02666198416565e-05</v>
-                </pt>
-                <pt idx="16">
-                  <v>1.5539400761958e-05</v>
-                </pt>
-                <pt idx="17">
-                  <v>7.97819437069734e-06</v>
-                </pt>
-                <pt idx="18">
-                  <v>4.09614156888547e-06</v>
-                </pt>
-                <pt idx="19">
-                  <v>2.10302920344682e-06</v>
-                </pt>
-                <pt idx="20">
-                  <v>1.07973119487507e-06</v>
-                </pt>
-                <pt idx="21">
-                  <v>5.54352479402378e-07</v>
-                </pt>
-                <pt idx="22">
-                  <v>2.84614052903343e-07</v>
-                </pt>
-                <pt idx="23">
-                  <v>1.46125727077824e-07</v>
-                </pt>
-                <pt idx="24">
-                  <v>7.50234498128391e-08</v>
-                </pt>
-                <pt idx="25">
-                  <v>3.85183234627942e-08</v>
-                </pt>
-                <pt idx="26">
-                  <v>1.97759666622333e-08</v>
-                </pt>
-                <pt idx="27">
-                  <v>1.01533198298084e-08</v>
-                </pt>
-                <pt idx="28">
-                  <v>5.21288821563674e-09</v>
-                </pt>
-                <pt idx="29">
-                  <v>2.67638604951115e-09</v>
-                </pt>
-                <pt idx="30">
-                  <v>1.37410241495903e-09</v>
-                </pt>
                 <pt idx="31">
-                  <v>7.05487703143996e-10</v>
+                  <v>0.00135295375753049</v>
                 </pt>
                 <pt idx="32">
-                  <v>3.6220946406111e-10</v>
+                  <v>0.00110770484878262</v>
                 </pt>
                 <pt idx="33">
-                  <v>1.85964539524595e-10</v>
+                  <v>0.000906912025031929</v>
                 </pt>
                 <pt idx="34">
-                  <v>9.547737812494e-11</v>
+                  <v>0.00074251676522987</v>
                 </pt>
                 <pt idx="35">
-                  <v>4.90197204096921e-11</v>
+                  <v>0.000607921310369677</v>
                 </pt>
                 <pt idx="36">
-                  <v>2.51675636285272e-11</v>
+                  <v>0.00049772387225112</v>
                 </pt>
                 <pt idx="37">
-                  <v>1.29214580112279e-11</v>
+                  <v>0.000407501840753049</v>
                 </pt>
                 <pt idx="38">
-                  <v>6.63409774582524e-12</v>
+                  <v>0.000333634288960407</v>
                 </pt>
                 <pt idx="39">
-                  <v>3.40605935204222e-12</v>
+                  <v>0.000273156652653191</v>
                 </pt>
                 <pt idx="40">
-                  <v>1.74872917977953e-12</v>
+                  <v>0.000223641751935008</v>
                 </pt>
                 <pt idx="41">
-                  <v>8.9782749745063e-13</v>
+                  <v>0.000183102379981428</v>
                 </pt>
                 <pt idx="42">
-                  <v>4.60960007129345e-13</v>
+                  <v>0.000149911549452566</v>
                 </pt>
                 <pt idx="43">
-                  <v>2.36664758849592e-13</v>
+                  <v>0.000122737195778386</v>
                 </pt>
                 <pt idx="44">
-                  <v>1.21507738665101e-13</v>
+                  <v>0.000100488716730318</v>
                 </pt>
                 <pt idx="45">
-                  <v>6.23841531256009e-14</v>
+                  <v>8.2273202724453e-05</v>
                 </pt>
                 <pt idx="46">
-                  <v>3.20290921710342e-14</v>
+                  <v>6.73596012247289e-05</v>
                 </pt>
                 <pt idx="47">
-                  <v>1.64442842276817e-14</v>
+                  <v>5.51493770377549e-05</v>
                 </pt>
                 <pt idx="48">
-                  <v>8.44277703272939e-15</v>
+                  <v>4.51524909939027e-05</v>
                 </pt>
                 <pt idx="49">
-                  <v>4.3346662607785e-15</v>
+                  <v>3.69677329547846e-05</v>
                 </pt>
                 <pt idx="50">
-                  <v>2.22549186357667e-15</v>
+                  <v>3.02666198416566e-05</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4728,7 +4746,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Sheet1'!AS9</f>
+              <f>'Sheet1'!AY69</f>
             </strRef>
           </tx>
           <spPr>
@@ -4749,7 +4767,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$AO$10:$AO$60</f>
+              <f>'Sheet1'!$AW$70:$AW$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -4757,161 +4775,161 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>5e-05</v>
+                  <v>1.5e-05</v>
                 </pt>
                 <pt idx="2">
-                  <v>0.0001</v>
+                  <v>3e-05</v>
                 </pt>
                 <pt idx="3">
+                  <v>4.5e-05</v>
+                </pt>
+                <pt idx="4">
+                  <v>6e-05</v>
+                </pt>
+                <pt idx="5">
+                  <v>7.5e-05</v>
+                </pt>
+                <pt idx="6">
+                  <v>9e-05</v>
+                </pt>
+                <pt idx="7">
+                  <v>0.000105</v>
+                </pt>
+                <pt idx="8">
+                  <v>0.00012</v>
+                </pt>
+                <pt idx="9">
+                  <v>0.000135</v>
+                </pt>
+                <pt idx="10">
                   <v>0.00015</v>
                 </pt>
-                <pt idx="4">
-                  <v>0.0002</v>
-                </pt>
-                <pt idx="5">
-                  <v>0.00025</v>
-                </pt>
-                <pt idx="6">
+                <pt idx="11">
+                  <v>0.000165</v>
+                </pt>
+                <pt idx="12">
+                  <v>0.00018</v>
+                </pt>
+                <pt idx="13">
+                  <v>0.000195</v>
+                </pt>
+                <pt idx="14">
+                  <v>0.00021</v>
+                </pt>
+                <pt idx="15">
+                  <v>0.000225</v>
+                </pt>
+                <pt idx="16">
+                  <v>0.00024</v>
+                </pt>
+                <pt idx="17">
+                  <v>0.000255</v>
+                </pt>
+                <pt idx="18">
+                  <v>0.00027</v>
+                </pt>
+                <pt idx="19">
+                  <v>0.000285</v>
+                </pt>
+                <pt idx="20">
                   <v>0.0003</v>
                 </pt>
-                <pt idx="7">
-                  <v>0.00035</v>
-                </pt>
-                <pt idx="8">
-                  <v>0.0004</v>
-                </pt>
-                <pt idx="9">
+                <pt idx="21">
+                  <v>0.000315</v>
+                </pt>
+                <pt idx="22">
+                  <v>0.00033</v>
+                </pt>
+                <pt idx="23">
+                  <v>0.000345</v>
+                </pt>
+                <pt idx="24">
+                  <v>0.00036</v>
+                </pt>
+                <pt idx="25">
+                  <v>0.000375</v>
+                </pt>
+                <pt idx="26">
+                  <v>0.00039</v>
+                </pt>
+                <pt idx="27">
+                  <v>0.000405</v>
+                </pt>
+                <pt idx="28">
+                  <v>0.00042</v>
+                </pt>
+                <pt idx="29">
+                  <v>0.000435</v>
+                </pt>
+                <pt idx="30">
                   <v>0.00045</v>
                 </pt>
-                <pt idx="10">
-                  <v>0.0005</v>
-                </pt>
-                <pt idx="11">
-                  <v>0.00055</v>
-                </pt>
-                <pt idx="12">
+                <pt idx="31">
+                  <v>0.000465</v>
+                </pt>
+                <pt idx="32">
+                  <v>0.00048</v>
+                </pt>
+                <pt idx="33">
+                  <v>0.000495</v>
+                </pt>
+                <pt idx="34">
+                  <v>0.00051</v>
+                </pt>
+                <pt idx="35">
+                  <v>0.000525</v>
+                </pt>
+                <pt idx="36">
+                  <v>0.00054</v>
+                </pt>
+                <pt idx="37">
+                  <v>0.000555</v>
+                </pt>
+                <pt idx="38">
+                  <v>0.00057</v>
+                </pt>
+                <pt idx="39">
+                  <v>0.000585</v>
+                </pt>
+                <pt idx="40">
                   <v>0.0006</v>
                 </pt>
-                <pt idx="13">
-                  <v>0.00065</v>
-                </pt>
-                <pt idx="14">
-                  <v>0.0007</v>
-                </pt>
-                <pt idx="15">
+                <pt idx="41">
+                  <v>0.000615</v>
+                </pt>
+                <pt idx="42">
+                  <v>0.00063</v>
+                </pt>
+                <pt idx="43">
+                  <v>0.000645</v>
+                </pt>
+                <pt idx="44">
+                  <v>0.00066</v>
+                </pt>
+                <pt idx="45">
+                  <v>0.000675</v>
+                </pt>
+                <pt idx="46">
+                  <v>0.00069</v>
+                </pt>
+                <pt idx="47">
+                  <v>0.000705</v>
+                </pt>
+                <pt idx="48">
+                  <v>0.00072</v>
+                </pt>
+                <pt idx="49">
+                  <v>0.000735</v>
+                </pt>
+                <pt idx="50">
                   <v>0.00075</v>
-                </pt>
-                <pt idx="16">
-                  <v>0.0008</v>
-                </pt>
-                <pt idx="17">
-                  <v>0.00085</v>
-                </pt>
-                <pt idx="18">
-                  <v>0.0009</v>
-                </pt>
-                <pt idx="19">
-                  <v>0.00095</v>
-                </pt>
-                <pt idx="20">
-                  <v>0.001</v>
-                </pt>
-                <pt idx="21">
-                  <v>0.00105</v>
-                </pt>
-                <pt idx="22">
-                  <v>0.0011</v>
-                </pt>
-                <pt idx="23">
-                  <v>0.00115</v>
-                </pt>
-                <pt idx="24">
-                  <v>0.0012</v>
-                </pt>
-                <pt idx="25">
-                  <v>0.00125</v>
-                </pt>
-                <pt idx="26">
-                  <v>0.0013</v>
-                </pt>
-                <pt idx="27">
-                  <v>0.00135</v>
-                </pt>
-                <pt idx="28">
-                  <v>0.0014</v>
-                </pt>
-                <pt idx="29">
-                  <v>0.00145</v>
-                </pt>
-                <pt idx="30">
-                  <v>0.0015</v>
-                </pt>
-                <pt idx="31">
-                  <v>0.00155</v>
-                </pt>
-                <pt idx="32">
-                  <v>0.0016</v>
-                </pt>
-                <pt idx="33">
-                  <v>0.00165</v>
-                </pt>
-                <pt idx="34">
-                  <v>0.0017</v>
-                </pt>
-                <pt idx="35">
-                  <v>0.00175</v>
-                </pt>
-                <pt idx="36">
-                  <v>0.0018</v>
-                </pt>
-                <pt idx="37">
-                  <v>0.00185</v>
-                </pt>
-                <pt idx="38">
-                  <v>0.0019</v>
-                </pt>
-                <pt idx="39">
-                  <v>0.00195</v>
-                </pt>
-                <pt idx="40">
-                  <v>0.002</v>
-                </pt>
-                <pt idx="41">
-                  <v>0.00205</v>
-                </pt>
-                <pt idx="42">
-                  <v>0.0021</v>
-                </pt>
-                <pt idx="43">
-                  <v>0.00215</v>
-                </pt>
-                <pt idx="44">
-                  <v>0.0022</v>
-                </pt>
-                <pt idx="45">
-                  <v>0.00225</v>
-                </pt>
-                <pt idx="46">
-                  <v>0.0023</v>
-                </pt>
-                <pt idx="47">
-                  <v>0.00235</v>
-                </pt>
-                <pt idx="48">
-                  <v>0.0024</v>
-                </pt>
-                <pt idx="49">
-                  <v>0.00245</v>
-                </pt>
-                <pt idx="50">
-                  <v>0.0025</v>
                 </pt>
               </numCache>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Sheet1'!$AS$10:$AS$60</f>
+              <f>'Sheet1'!$AY$70:$AY$120</f>
               <numCache>
                 <formatCode>General</formatCode>
                 <ptCount val="51"/>
@@ -4919,154 +4937,154 @@
                   <v>-8</v>
                 </pt>
                 <pt idx="1">
-                  <v>-4.10733695226074</v>
+                  <v>-6.54984602462385</v>
                 </pt>
                 <pt idx="2">
-                  <v>-2.10877710492581</v>
+                  <v>-5.36256036828511</v>
                 </pt>
                 <pt idx="3">
+                  <v>-4.39049308875221</v>
+                </pt>
+                <pt idx="4">
+                  <v>-3.59463171293777</v>
+                </pt>
+                <pt idx="5">
+                  <v>-2.94303552937154</v>
+                </pt>
+                <pt idx="6">
+                  <v>-2.40955369529762</v>
+                </pt>
+                <pt idx="7">
+                  <v>-1.97277571153285</v>
+                </pt>
+                <pt idx="8">
+                  <v>-1.61517214395724</v>
+                </pt>
+                <pt idx="9">
+                  <v>-1.32239110577269</v>
+                </pt>
+                <pt idx="10">
                   <v>-1.0826822658929</v>
                 </pt>
-                <pt idx="4">
-                  <v>-0.555867609782412</v>
-                </pt>
-                <pt idx="5">
-                  <v>-0.285391946778019</v>
-                </pt>
-                <pt idx="6">
+                <pt idx="11">
+                  <v>-0.886425266898671</v>
+                </pt>
+                <pt idx="12">
+                  <v>-0.7257436263153</v>
+                </pt>
+                <pt idx="13">
+                  <v>-0.594188625714671</v>
+                </pt>
+                <pt idx="14">
+                  <v>-0.486480501001744</v>
+                </pt>
+                <pt idx="15">
+                  <v>-0.398296546942911</v>
+                </pt>
+                <pt idx="16">
+                  <v>-0.32609763182693</v>
+                </pt>
+                <pt idx="17">
+                  <v>-0.266986159682609</v>
+                </pt>
+                <pt idx="18">
+                  <v>-0.218589779578341</v>
+                </pt>
+                <pt idx="19">
+                  <v>-0.178966174849325</v>
+                </pt>
+                <pt idx="20">
                   <v>-0.146525111109873</v>
                 </pt>
-                <pt idx="7">
-                  <v>-0.0752285004119617</v>
-                </pt>
-                <pt idx="8">
-                  <v>-0.0386235999506515</v>
-                </pt>
-                <pt idx="9">
+                <pt idx="21">
+                  <v>-0.119964614563822</v>
+                </pt>
+                <pt idx="22">
+                  <v>-0.0982187192245475</v>
+                </pt>
+                <pt idx="23">
+                  <v>-0.0804146859570687</v>
+                </pt>
+                <pt idx="24">
+                  <v>-0.0658379763921603</v>
+                </pt>
+                <pt idx="25">
+                  <v>-0.0539035759926837</v>
+                </pt>
+                <pt idx="26">
+                  <v>-0.0441325153660862</v>
+                </pt>
+                <pt idx="27">
+                  <v>-0.0361326475409014</v>
+                </pt>
+                <pt idx="28">
+                  <v>-0.0295829097318635</v>
+                </pt>
+                <pt idx="29">
+                  <v>-0.0242204379630065</v>
+                </pt>
+                <pt idx="30">
                   <v>-0.0198300174133309</v>
                 </pt>
-                <pt idx="10">
-                  <v>-0.0101810704107185</v>
-                </pt>
-                <pt idx="11">
-                  <v>-0.00522713583893904</v>
-                </pt>
-                <pt idx="12">
+                <pt idx="31">
+                  <v>-0.0162354450903659</v>
+                </pt>
+                <pt idx="32">
+                  <v>-0.0132924581853915</v>
+                </pt>
+                <pt idx="33">
+                  <v>-0.0108829443003831</v>
+                </pt>
+                <pt idx="34">
+                  <v>-0.00891020118275843</v>
+                </pt>
+                <pt idx="35">
+                  <v>-0.00729505572443613</v>
+                </pt>
+                <pt idx="36">
+                  <v>-0.00597268646701344</v>
+                </pt>
+                <pt idx="37">
+                  <v>-0.00489002208903658</v>
+                </pt>
+                <pt idx="38">
+                  <v>-0.00400361146752489</v>
+                </pt>
+                <pt idx="39">
+                  <v>-0.0032778798318383</v>
+                </pt>
+                <pt idx="40">
                   <v>-0.00268370102322009</v>
                 </pt>
-                <pt idx="13">
-                  <v>-0.00137785804768648</v>
-                </pt>
-                <pt idx="14">
-                  <v>-0.000707415909279065</v>
-                </pt>
-                <pt idx="15">
-                  <v>-0.000363199438099878</v>
-                </pt>
-                <pt idx="16">
-                  <v>-0.000186472809143496</v>
-                </pt>
-                <pt idx="17">
-                  <v>-9.57383324483681e-05</v>
-                </pt>
-                <pt idx="18">
-                  <v>-4.91536988266256e-05</v>
-                </pt>
-                <pt idx="19">
-                  <v>-2.52363504413618e-05</v>
-                </pt>
-                <pt idx="20">
-                  <v>-1.29567743385009e-05</v>
-                </pt>
-                <pt idx="21">
-                  <v>-6.65222975282853e-06</v>
-                </pt>
-                <pt idx="22">
-                  <v>-3.41536863484012e-06</v>
-                </pt>
-                <pt idx="23">
-                  <v>-1.75350872493389e-06</v>
-                </pt>
-                <pt idx="24">
-                  <v>-9.0028139775407e-07</v>
-                </pt>
-                <pt idx="25">
-                  <v>-4.62219881553531e-07</v>
-                </pt>
-                <pt idx="26">
-                  <v>-2.37311599946799e-07</v>
-                </pt>
-                <pt idx="27">
-                  <v>-1.21839837957701e-07</v>
-                </pt>
-                <pt idx="28">
-                  <v>-6.25546585876409e-08</v>
-                </pt>
-                <pt idx="29">
-                  <v>-3.21166325941338e-08</v>
-                </pt>
-                <pt idx="30">
-                  <v>-1.64892289795084e-08</v>
-                </pt>
-                <pt idx="31">
-                  <v>-8.46585243772795e-09</v>
-                </pt>
-                <pt idx="32">
-                  <v>-4.34651356873333e-09</v>
-                </pt>
-                <pt idx="33">
-                  <v>-2.23157447429514e-09</v>
-                </pt>
-                <pt idx="34">
-                  <v>-1.14572853749928e-09</v>
-                </pt>
-                <pt idx="35">
-                  <v>-5.88236644916305e-10</v>
-                </pt>
-                <pt idx="36">
-                  <v>-3.02010763542327e-10</v>
-                </pt>
-                <pt idx="37">
-                  <v>-1.55057496134735e-10</v>
-                </pt>
-                <pt idx="38">
-                  <v>-7.96091729499029e-11</v>
-                </pt>
-                <pt idx="39">
-                  <v>-4.08727122245066e-11</v>
-                </pt>
-                <pt idx="40">
-                  <v>-2.09847501573544e-11</v>
-                </pt>
                 <pt idx="41">
-                  <v>-1.07739299694076e-11</v>
+                  <v>-0.00219722855977714</v>
                 </pt>
                 <pt idx="42">
-                  <v>-5.53152008555214e-12</v>
+                  <v>-0.00179893859343079</v>
                 </pt>
                 <pt idx="43">
-                  <v>-2.8399771061951e-12</v>
+                  <v>-0.00147284634934063</v>
                 </pt>
                 <pt idx="44">
-                  <v>-1.45809286398121e-12</v>
+                  <v>-0.00120586460076381</v>
                 </pt>
                 <pt idx="45">
-                  <v>-7.48609837507211e-13</v>
+                  <v>-0.000987278432693436</v>
                 </pt>
                 <pt idx="46">
-                  <v>-3.8434910605241e-13</v>
+                  <v>-0.000808315214696747</v>
                 </pt>
                 <pt idx="47">
-                  <v>-1.9733141073218e-13</v>
+                  <v>-0.000661792524453059</v>
                 </pt>
                 <pt idx="48">
-                  <v>-1.01313324392753e-13</v>
+                  <v>-0.000541829891926832</v>
                 </pt>
                 <pt idx="49">
-                  <v>-5.2015995129342e-14</v>
+                  <v>-0.000443612795457416</v>
                 </pt>
                 <pt idx="50">
-                  <v>-2.670590236292e-14</v>
+                  <v>-0.000363199438099879</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5099,7 +5117,7 @@
             </rich>
           </tx>
         </title>
-        <numFmt formatCode="0.000" sourceLinked="0"/>
+        <numFmt formatCode="0.00E+00" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="20"/>
@@ -5595,7 +5613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AU106"/>
+  <dimension ref="A1:AY137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5605,6 +5623,10 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
@@ -5612,6 +5634,10 @@
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
     <col width="14" customWidth="1" min="41" max="41"/>
     <col width="16" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
@@ -5619,6 +5645,10 @@
     <col width="14" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
     <col width="14" customWidth="1" min="47" max="47"/>
+    <col width="18" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5634,6 +5664,11 @@
           <t>Базовый режим</t>
         </is>
       </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Δtр = 10τр/(n-1)</t>
+        </is>
+      </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Исходные данные</t>
@@ -5646,6 +5681,11 @@
           <t>L меньше в 3 раза</t>
         </is>
       </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>Δtр = 10τр/(n-1)</t>
+        </is>
+      </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Исходные данные</t>
@@ -5658,19 +5698,24 @@
           <t>r/2 и R/10</t>
         </is>
       </c>
+      <c r="AV1" s="4" t="inlineStr">
+        <is>
+          <t>Δtр = 10τр/(n-1)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Величина</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Размерность</t>
         </is>
@@ -5680,20 +5725,24 @@
           <t>Δt</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="6" t="n">
         <v>5e-05</v>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="H2" s="7">
+        <f>10*$B$8/50</f>
+        <v/>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
         <is>
           <t>Величина</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="U2" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="V2" s="5" t="inlineStr">
         <is>
           <t>Размерность</t>
         </is>
@@ -5703,20 +5752,24 @@
           <t>Δt</t>
         </is>
       </c>
-      <c r="Z2" s="5" t="n">
+      <c r="Z2" s="6" t="n">
         <v>5e-05</v>
       </c>
-      <c r="AO2" s="4" t="inlineStr">
+      <c r="AA2" s="7">
+        <f>10*$U$8/50</f>
+        <v/>
+      </c>
+      <c r="AO2" s="5" t="inlineStr">
         <is>
           <t>Величина</t>
         </is>
       </c>
-      <c r="AP2" s="4" t="inlineStr">
+      <c r="AP2" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="AQ2" s="4" t="inlineStr">
+      <c r="AQ2" s="5" t="inlineStr">
         <is>
           <t>Размерность</t>
         </is>
@@ -5726,20 +5779,24 @@
           <t>Δt</t>
         </is>
       </c>
-      <c r="AU2" s="5" t="n">
+      <c r="AU2" s="6" t="n">
         <v>5e-05</v>
       </c>
+      <c r="AV2" s="7">
+        <f>10*$AP$8/50</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>В</t>
         </is>
@@ -5754,15 +5811,15 @@
           <t>с</t>
         </is>
       </c>
-      <c r="T3" s="6" t="inlineStr">
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="U3" s="7" t="n">
+      <c r="U3" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="V3" s="8" t="inlineStr">
+      <c r="V3" s="10" t="inlineStr">
         <is>
           <t>В</t>
         </is>
@@ -5777,15 +5834,15 @@
           <t>с</t>
         </is>
       </c>
-      <c r="AO3" s="6" t="inlineStr">
+      <c r="AO3" s="8" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="AP3" s="7" t="n">
+      <c r="AP3" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AQ3" s="8" t="inlineStr">
+      <c r="AQ3" s="10" t="inlineStr">
         <is>
           <t>В</t>
         </is>
@@ -5802,57 +5859,57 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Ом</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Заряд: ключ на источник через r.
 Разряд: контур L–R, I(0)=E/R.</t>
         </is>
       </c>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="U4" s="7" t="n">
+      <c r="U4" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="V4" s="8" t="inlineStr">
+      <c r="V4" s="10" t="inlineStr">
         <is>
           <t>Ом</t>
         </is>
       </c>
-      <c r="Y4" s="9" t="inlineStr">
+      <c r="Y4" s="11" t="inlineStr">
         <is>
           <t>τз=L/r уменьшается → ток нарастает быстрее.</t>
         </is>
       </c>
-      <c r="AO4" s="6" t="inlineStr">
+      <c r="AO4" s="8" t="inlineStr">
         <is>
           <t>r</t>
         </is>
       </c>
-      <c r="AP4" s="7" t="n">
+      <c r="AP4" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ4" s="8" t="inlineStr">
+      <c r="AQ4" s="10" t="inlineStr">
         <is>
           <t>Ом</t>
         </is>
       </c>
-      <c r="AT4" s="9" t="inlineStr">
+      <c r="AT4" s="11" t="inlineStr">
         <is>
           <t>E/r растёт, τз=L/r растёт.
 Разряд через меньшее R.</t>
@@ -5860,173 +5917,173 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Ом</t>
         </is>
       </c>
-      <c r="T5" s="6" t="inlineStr">
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="U5" s="7" t="n">
+      <c r="U5" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="V5" s="10" t="inlineStr">
         <is>
           <t>Ом</t>
         </is>
       </c>
-      <c r="AO5" s="6" t="inlineStr">
+      <c r="AO5" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AP5" s="7" t="n">
+      <c r="AP5" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="AQ5" s="8" t="inlineStr">
+      <c r="AQ5" s="10" t="inlineStr">
         <is>
           <t>Ом</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="12">
         <f>POWER(10,-4)*9</f>
         <v/>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Гн</t>
         </is>
       </c>
-      <c r="T6" s="6" t="inlineStr">
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U6" s="10">
+      <c r="U6" s="12">
         <f>POWER(10,-4)*3</f>
         <v/>
       </c>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="V6" s="10" t="inlineStr">
         <is>
           <t>Гн</t>
         </is>
       </c>
-      <c r="AO6" s="6" t="inlineStr">
+      <c r="AO6" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="AP6" s="10">
+      <c r="AP6" s="12">
         <f>POWER(10,-4)*9</f>
         <v/>
       </c>
-      <c r="AQ6" s="8" t="inlineStr">
+      <c r="AQ6" s="10" t="inlineStr">
         <is>
           <t>Гн</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>τз = L/r</t>
         </is>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="14">
         <f>B6/B4</f>
         <v/>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>с</t>
         </is>
       </c>
-      <c r="T7" s="11" t="inlineStr">
+      <c r="T7" s="13" t="inlineStr">
         <is>
           <t>τз = L/r</t>
         </is>
       </c>
-      <c r="U7" s="12">
+      <c r="U7" s="14">
         <f>U6/U4</f>
         <v/>
       </c>
-      <c r="V7" s="11" t="inlineStr">
+      <c r="V7" s="13" t="inlineStr">
         <is>
           <t>с</t>
         </is>
       </c>
-      <c r="AO7" s="11" t="inlineStr">
+      <c r="AO7" s="13" t="inlineStr">
         <is>
           <t>τз = L/r</t>
         </is>
       </c>
-      <c r="AP7" s="12">
+      <c r="AP7" s="14">
         <f>AP6/AP4</f>
         <v/>
       </c>
-      <c r="AQ7" s="11" t="inlineStr">
+      <c r="AQ7" s="13" t="inlineStr">
         <is>
           <t>с</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>τр = L/R</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="14">
         <f>B6/B5</f>
         <v/>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>с</t>
         </is>
       </c>
-      <c r="T8" s="11" t="inlineStr">
+      <c r="T8" s="13" t="inlineStr">
         <is>
           <t>τр = L/R</t>
         </is>
       </c>
-      <c r="U8" s="12">
+      <c r="U8" s="14">
         <f>U6/U5</f>
         <v/>
       </c>
-      <c r="V8" s="11" t="inlineStr">
+      <c r="V8" s="13" t="inlineStr">
         <is>
           <t>с</t>
         </is>
       </c>
-      <c r="AO8" s="11" t="inlineStr">
+      <c r="AO8" s="13" t="inlineStr">
         <is>
           <t>τр = L/R</t>
         </is>
       </c>
-      <c r="AP8" s="12">
+      <c r="AP8" s="14">
         <f>AP6/AP5</f>
         <v/>
       </c>
-      <c r="AQ8" s="11" t="inlineStr">
+      <c r="AQ8" s="13" t="inlineStr">
         <is>
           <t>с</t>
         </is>
@@ -6043,7 +6100,7 @@
           <t>Iз, А</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Uз, В</t>
         </is>
@@ -6053,7 +6110,7 @@
           <t>Iр, А</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Uр, В</t>
         </is>
@@ -6068,7 +6125,7 @@
           <t>Iз, А</t>
         </is>
       </c>
-      <c r="V9" s="4" t="inlineStr">
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>Uз, В</t>
         </is>
@@ -6078,7 +6135,7 @@
           <t>Iр, А</t>
         </is>
       </c>
-      <c r="X9" s="4" t="inlineStr">
+      <c r="X9" s="5" t="inlineStr">
         <is>
           <t>Uр, В</t>
         </is>
@@ -6093,7 +6150,7 @@
           <t>Iз, А</t>
         </is>
       </c>
-      <c r="AQ9" s="4" t="inlineStr">
+      <c r="AQ9" s="5" t="inlineStr">
         <is>
           <t>Uз, В</t>
         </is>
@@ -6103,3217 +6160,5223 @@
           <t>Iр, А</t>
         </is>
       </c>
-      <c r="AS9" s="4" t="inlineStr">
+      <c r="AS9" s="5" t="inlineStr">
         <is>
           <t>Uр, В</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A10*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="16">
         <f>$B$3*EXP(-A10*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="17">
         <f>($B$3/$B$5)*EXP(-A10*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="17">
         <f>-$B$3*EXP(-A10*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T10" s="13" t="n">
+      <c r="T10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="U10" s="14">
+      <c r="U10" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T10*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V10" s="14">
+      <c r="V10" s="16">
         <f>$U$3*EXP(-T10*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W10" s="15">
+      <c r="W10" s="17">
         <f>($U$3/$U$5)*EXP(-T10*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X10" s="15">
+      <c r="X10" s="17">
         <f>-$U$3*EXP(-T10*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO10" s="13" t="n">
+      <c r="AO10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AP10" s="14">
+      <c r="AP10" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO10*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ10" s="14">
+      <c r="AQ10" s="16">
         <f>$AP$3*EXP(-AO10*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR10" s="15">
+      <c r="AR10" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO10*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS10" s="15">
+      <c r="AS10" s="17">
         <f>-$AP$3*EXP(-AO10*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13">
+      <c r="A11" s="15">
         <f>A10+$G$2</f>
         <v/>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A11*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="16">
         <f>$B$3*EXP(-A11*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="17">
         <f>($B$3/$B$5)*EXP(-A11*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="17">
         <f>-$B$3*EXP(-A11*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T11" s="13">
+      <c r="T11" s="15">
         <f>T10+$Z$2</f>
         <v/>
       </c>
-      <c r="U11" s="14">
+      <c r="U11" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T11*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V11" s="14">
+      <c r="V11" s="16">
         <f>$U$3*EXP(-T11*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W11" s="15">
+      <c r="W11" s="17">
         <f>($U$3/$U$5)*EXP(-T11*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X11" s="15">
+      <c r="X11" s="17">
         <f>-$U$3*EXP(-T11*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO11" s="13">
+      <c r="AO11" s="15">
         <f>AO10+$AU$2</f>
         <v/>
       </c>
-      <c r="AP11" s="14">
+      <c r="AP11" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO11*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ11" s="14">
+      <c r="AQ11" s="16">
         <f>$AP$3*EXP(-AO11*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR11" s="15">
+      <c r="AR11" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO11*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS11" s="15">
+      <c r="AS11" s="17">
         <f>-$AP$3*EXP(-AO11*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="15">
         <f>A11+$G$2</f>
         <v/>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A12*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="16">
         <f>$B$3*EXP(-A12*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="17">
         <f>($B$3/$B$5)*EXP(-A12*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="17">
         <f>-$B$3*EXP(-A12*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T12" s="13">
+      <c r="T12" s="15">
         <f>T11+$Z$2</f>
         <v/>
       </c>
-      <c r="U12" s="14">
+      <c r="U12" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T12*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V12" s="14">
+      <c r="V12" s="16">
         <f>$U$3*EXP(-T12*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W12" s="15">
+      <c r="W12" s="17">
         <f>($U$3/$U$5)*EXP(-T12*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X12" s="15">
+      <c r="X12" s="17">
         <f>-$U$3*EXP(-T12*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO12" s="13">
+      <c r="AO12" s="15">
         <f>AO11+$AU$2</f>
         <v/>
       </c>
-      <c r="AP12" s="14">
+      <c r="AP12" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO12*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ12" s="14">
+      <c r="AQ12" s="16">
         <f>$AP$3*EXP(-AO12*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR12" s="15">
+      <c r="AR12" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO12*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS12" s="15">
+      <c r="AS12" s="17">
         <f>-$AP$3*EXP(-AO12*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13">
+      <c r="A13" s="15">
         <f>A12+$G$2</f>
         <v/>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A13*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="16">
         <f>$B$3*EXP(-A13*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="17">
         <f>($B$3/$B$5)*EXP(-A13*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="17">
         <f>-$B$3*EXP(-A13*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T13" s="13">
+      <c r="T13" s="15">
         <f>T12+$Z$2</f>
         <v/>
       </c>
-      <c r="U13" s="14">
+      <c r="U13" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T13*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V13" s="14">
+      <c r="V13" s="16">
         <f>$U$3*EXP(-T13*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W13" s="15">
+      <c r="W13" s="17">
         <f>($U$3/$U$5)*EXP(-T13*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X13" s="15">
+      <c r="X13" s="17">
         <f>-$U$3*EXP(-T13*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO13" s="13">
+      <c r="AO13" s="15">
         <f>AO12+$AU$2</f>
         <v/>
       </c>
-      <c r="AP13" s="14">
+      <c r="AP13" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO13*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ13" s="14">
+      <c r="AQ13" s="16">
         <f>$AP$3*EXP(-AO13*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR13" s="15">
+      <c r="AR13" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO13*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS13" s="15">
+      <c r="AS13" s="17">
         <f>-$AP$3*EXP(-AO13*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13">
+      <c r="A14" s="15">
         <f>A13+$G$2</f>
         <v/>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A14*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="16">
         <f>$B$3*EXP(-A14*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="17">
         <f>($B$3/$B$5)*EXP(-A14*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="17">
         <f>-$B$3*EXP(-A14*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T14" s="13">
+      <c r="T14" s="15">
         <f>T13+$Z$2</f>
         <v/>
       </c>
-      <c r="U14" s="14">
+      <c r="U14" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T14*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V14" s="14">
+      <c r="V14" s="16">
         <f>$U$3*EXP(-T14*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W14" s="15">
+      <c r="W14" s="17">
         <f>($U$3/$U$5)*EXP(-T14*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X14" s="15">
+      <c r="X14" s="17">
         <f>-$U$3*EXP(-T14*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO14" s="13">
+      <c r="AO14" s="15">
         <f>AO13+$AU$2</f>
         <v/>
       </c>
-      <c r="AP14" s="14">
+      <c r="AP14" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO14*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ14" s="14">
+      <c r="AQ14" s="16">
         <f>$AP$3*EXP(-AO14*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR14" s="15">
+      <c r="AR14" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO14*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS14" s="15">
+      <c r="AS14" s="17">
         <f>-$AP$3*EXP(-AO14*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13">
+      <c r="A15" s="15">
         <f>A14+$G$2</f>
         <v/>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A15*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="16">
         <f>$B$3*EXP(-A15*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="17">
         <f>($B$3/$B$5)*EXP(-A15*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="17">
         <f>-$B$3*EXP(-A15*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T15" s="13">
+      <c r="T15" s="15">
         <f>T14+$Z$2</f>
         <v/>
       </c>
-      <c r="U15" s="14">
+      <c r="U15" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T15*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V15" s="14">
+      <c r="V15" s="16">
         <f>$U$3*EXP(-T15*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W15" s="15">
+      <c r="W15" s="17">
         <f>($U$3/$U$5)*EXP(-T15*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X15" s="15">
+      <c r="X15" s="17">
         <f>-$U$3*EXP(-T15*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO15" s="13">
+      <c r="AO15" s="15">
         <f>AO14+$AU$2</f>
         <v/>
       </c>
-      <c r="AP15" s="14">
+      <c r="AP15" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO15*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ15" s="14">
+      <c r="AQ15" s="16">
         <f>$AP$3*EXP(-AO15*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR15" s="15">
+      <c r="AR15" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO15*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS15" s="15">
+      <c r="AS15" s="17">
         <f>-$AP$3*EXP(-AO15*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13">
+      <c r="A16" s="15">
         <f>A15+$G$2</f>
         <v/>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A16*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="16">
         <f>$B$3*EXP(-A16*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="17">
         <f>($B$3/$B$5)*EXP(-A16*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="17">
         <f>-$B$3*EXP(-A16*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T16" s="13">
+      <c r="T16" s="15">
         <f>T15+$Z$2</f>
         <v/>
       </c>
-      <c r="U16" s="14">
+      <c r="U16" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T16*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V16" s="14">
+      <c r="V16" s="16">
         <f>$U$3*EXP(-T16*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W16" s="15">
+      <c r="W16" s="17">
         <f>($U$3/$U$5)*EXP(-T16*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X16" s="15">
+      <c r="X16" s="17">
         <f>-$U$3*EXP(-T16*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO16" s="13">
+      <c r="AO16" s="15">
         <f>AO15+$AU$2</f>
         <v/>
       </c>
-      <c r="AP16" s="14">
+      <c r="AP16" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO16*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ16" s="14">
+      <c r="AQ16" s="16">
         <f>$AP$3*EXP(-AO16*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR16" s="15">
+      <c r="AR16" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO16*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS16" s="15">
+      <c r="AS16" s="17">
         <f>-$AP$3*EXP(-AO16*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13">
+      <c r="A17" s="15">
         <f>A16+$G$2</f>
         <v/>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A17*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="16">
         <f>$B$3*EXP(-A17*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="17">
         <f>($B$3/$B$5)*EXP(-A17*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="17">
         <f>-$B$3*EXP(-A17*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T17" s="13">
+      <c r="T17" s="15">
         <f>T16+$Z$2</f>
         <v/>
       </c>
-      <c r="U17" s="14">
+      <c r="U17" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T17*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V17" s="14">
+      <c r="V17" s="16">
         <f>$U$3*EXP(-T17*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W17" s="15">
+      <c r="W17" s="17">
         <f>($U$3/$U$5)*EXP(-T17*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X17" s="15">
+      <c r="X17" s="17">
         <f>-$U$3*EXP(-T17*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO17" s="13">
+      <c r="AO17" s="15">
         <f>AO16+$AU$2</f>
         <v/>
       </c>
-      <c r="AP17" s="14">
+      <c r="AP17" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO17*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ17" s="14">
+      <c r="AQ17" s="16">
         <f>$AP$3*EXP(-AO17*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR17" s="15">
+      <c r="AR17" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO17*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS17" s="15">
+      <c r="AS17" s="17">
         <f>-$AP$3*EXP(-AO17*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13">
+      <c r="A18" s="15">
         <f>A17+$G$2</f>
         <v/>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A18*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="16">
         <f>$B$3*EXP(-A18*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="17">
         <f>($B$3/$B$5)*EXP(-A18*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="17">
         <f>-$B$3*EXP(-A18*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T18" s="13">
+      <c r="T18" s="15">
         <f>T17+$Z$2</f>
         <v/>
       </c>
-      <c r="U18" s="14">
+      <c r="U18" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T18*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V18" s="14">
+      <c r="V18" s="16">
         <f>$U$3*EXP(-T18*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W18" s="15">
+      <c r="W18" s="17">
         <f>($U$3/$U$5)*EXP(-T18*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X18" s="15">
+      <c r="X18" s="17">
         <f>-$U$3*EXP(-T18*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO18" s="13">
+      <c r="AO18" s="15">
         <f>AO17+$AU$2</f>
         <v/>
       </c>
-      <c r="AP18" s="14">
+      <c r="AP18" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO18*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ18" s="14">
+      <c r="AQ18" s="16">
         <f>$AP$3*EXP(-AO18*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR18" s="15">
+      <c r="AR18" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO18*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS18" s="15">
+      <c r="AS18" s="17">
         <f>-$AP$3*EXP(-AO18*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13">
+      <c r="A19" s="15">
         <f>A18+$G$2</f>
         <v/>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A19*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="16">
         <f>$B$3*EXP(-A19*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="17">
         <f>($B$3/$B$5)*EXP(-A19*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="17">
         <f>-$B$3*EXP(-A19*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T19" s="13">
+      <c r="T19" s="15">
         <f>T18+$Z$2</f>
         <v/>
       </c>
-      <c r="U19" s="14">
+      <c r="U19" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T19*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V19" s="14">
+      <c r="V19" s="16">
         <f>$U$3*EXP(-T19*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W19" s="15">
+      <c r="W19" s="17">
         <f>($U$3/$U$5)*EXP(-T19*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X19" s="15">
+      <c r="X19" s="17">
         <f>-$U$3*EXP(-T19*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO19" s="13">
+      <c r="AO19" s="15">
         <f>AO18+$AU$2</f>
         <v/>
       </c>
-      <c r="AP19" s="14">
+      <c r="AP19" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO19*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ19" s="14">
+      <c r="AQ19" s="16">
         <f>$AP$3*EXP(-AO19*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR19" s="15">
+      <c r="AR19" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO19*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS19" s="15">
+      <c r="AS19" s="17">
         <f>-$AP$3*EXP(-AO19*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13">
+      <c r="A20" s="15">
         <f>A19+$G$2</f>
         <v/>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A20*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="16">
         <f>$B$3*EXP(-A20*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="17">
         <f>($B$3/$B$5)*EXP(-A20*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="17">
         <f>-$B$3*EXP(-A20*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T20" s="13">
+      <c r="T20" s="15">
         <f>T19+$Z$2</f>
         <v/>
       </c>
-      <c r="U20" s="14">
+      <c r="U20" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T20*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V20" s="14">
+      <c r="V20" s="16">
         <f>$U$3*EXP(-T20*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W20" s="15">
+      <c r="W20" s="17">
         <f>($U$3/$U$5)*EXP(-T20*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X20" s="15">
+      <c r="X20" s="17">
         <f>-$U$3*EXP(-T20*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO20" s="13">
+      <c r="AO20" s="15">
         <f>AO19+$AU$2</f>
         <v/>
       </c>
-      <c r="AP20" s="14">
+      <c r="AP20" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO20*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ20" s="14">
+      <c r="AQ20" s="16">
         <f>$AP$3*EXP(-AO20*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR20" s="15">
+      <c r="AR20" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO20*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS20" s="15">
+      <c r="AS20" s="17">
         <f>-$AP$3*EXP(-AO20*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13">
+      <c r="A21" s="15">
         <f>A20+$G$2</f>
         <v/>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A21*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="16">
         <f>$B$3*EXP(-A21*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="17">
         <f>($B$3/$B$5)*EXP(-A21*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="17">
         <f>-$B$3*EXP(-A21*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T21" s="13">
+      <c r="T21" s="15">
         <f>T20+$Z$2</f>
         <v/>
       </c>
-      <c r="U21" s="14">
+      <c r="U21" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T21*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V21" s="14">
+      <c r="V21" s="16">
         <f>$U$3*EXP(-T21*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W21" s="15">
+      <c r="W21" s="17">
         <f>($U$3/$U$5)*EXP(-T21*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X21" s="15">
+      <c r="X21" s="17">
         <f>-$U$3*EXP(-T21*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO21" s="13">
+      <c r="AO21" s="15">
         <f>AO20+$AU$2</f>
         <v/>
       </c>
-      <c r="AP21" s="14">
+      <c r="AP21" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO21*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ21" s="14">
+      <c r="AQ21" s="16">
         <f>$AP$3*EXP(-AO21*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR21" s="15">
+      <c r="AR21" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO21*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS21" s="15">
+      <c r="AS21" s="17">
         <f>-$AP$3*EXP(-AO21*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13">
+      <c r="A22" s="15">
         <f>A21+$G$2</f>
         <v/>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A22*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="16">
         <f>$B$3*EXP(-A22*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="17">
         <f>($B$3/$B$5)*EXP(-A22*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="17">
         <f>-$B$3*EXP(-A22*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T22" s="13">
+      <c r="T22" s="15">
         <f>T21+$Z$2</f>
         <v/>
       </c>
-      <c r="U22" s="14">
+      <c r="U22" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T22*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V22" s="14">
+      <c r="V22" s="16">
         <f>$U$3*EXP(-T22*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W22" s="15">
+      <c r="W22" s="17">
         <f>($U$3/$U$5)*EXP(-T22*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X22" s="15">
+      <c r="X22" s="17">
         <f>-$U$3*EXP(-T22*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO22" s="13">
+      <c r="AO22" s="15">
         <f>AO21+$AU$2</f>
         <v/>
       </c>
-      <c r="AP22" s="14">
+      <c r="AP22" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO22*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ22" s="14">
+      <c r="AQ22" s="16">
         <f>$AP$3*EXP(-AO22*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR22" s="15">
+      <c r="AR22" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO22*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS22" s="15">
+      <c r="AS22" s="17">
         <f>-$AP$3*EXP(-AO22*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13">
+      <c r="A23" s="15">
         <f>A22+$G$2</f>
         <v/>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A23*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="16">
         <f>$B$3*EXP(-A23*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="17">
         <f>($B$3/$B$5)*EXP(-A23*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="17">
         <f>-$B$3*EXP(-A23*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T23" s="13">
+      <c r="T23" s="15">
         <f>T22+$Z$2</f>
         <v/>
       </c>
-      <c r="U23" s="14">
+      <c r="U23" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T23*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V23" s="14">
+      <c r="V23" s="16">
         <f>$U$3*EXP(-T23*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W23" s="15">
+      <c r="W23" s="17">
         <f>($U$3/$U$5)*EXP(-T23*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X23" s="15">
+      <c r="X23" s="17">
         <f>-$U$3*EXP(-T23*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO23" s="13">
+      <c r="AO23" s="15">
         <f>AO22+$AU$2</f>
         <v/>
       </c>
-      <c r="AP23" s="14">
+      <c r="AP23" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO23*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ23" s="14">
+      <c r="AQ23" s="16">
         <f>$AP$3*EXP(-AO23*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR23" s="15">
+      <c r="AR23" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO23*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS23" s="15">
+      <c r="AS23" s="17">
         <f>-$AP$3*EXP(-AO23*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13">
+      <c r="A24" s="15">
         <f>A23+$G$2</f>
         <v/>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A24*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="16">
         <f>$B$3*EXP(-A24*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="17">
         <f>($B$3/$B$5)*EXP(-A24*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="17">
         <f>-$B$3*EXP(-A24*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T24" s="13">
+      <c r="T24" s="15">
         <f>T23+$Z$2</f>
         <v/>
       </c>
-      <c r="U24" s="14">
+      <c r="U24" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T24*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V24" s="14">
+      <c r="V24" s="16">
         <f>$U$3*EXP(-T24*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W24" s="15">
+      <c r="W24" s="17">
         <f>($U$3/$U$5)*EXP(-T24*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X24" s="15">
+      <c r="X24" s="17">
         <f>-$U$3*EXP(-T24*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO24" s="13">
+      <c r="AO24" s="15">
         <f>AO23+$AU$2</f>
         <v/>
       </c>
-      <c r="AP24" s="14">
+      <c r="AP24" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO24*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ24" s="14">
+      <c r="AQ24" s="16">
         <f>$AP$3*EXP(-AO24*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR24" s="15">
+      <c r="AR24" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO24*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS24" s="15">
+      <c r="AS24" s="17">
         <f>-$AP$3*EXP(-AO24*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13">
+      <c r="A25" s="15">
         <f>A24+$G$2</f>
         <v/>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A25*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="16">
         <f>$B$3*EXP(-A25*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="17">
         <f>($B$3/$B$5)*EXP(-A25*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="17">
         <f>-$B$3*EXP(-A25*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T25" s="13">
+      <c r="T25" s="15">
         <f>T24+$Z$2</f>
         <v/>
       </c>
-      <c r="U25" s="14">
+      <c r="U25" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T25*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V25" s="14">
+      <c r="V25" s="16">
         <f>$U$3*EXP(-T25*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W25" s="15">
+      <c r="W25" s="17">
         <f>($U$3/$U$5)*EXP(-T25*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X25" s="15">
+      <c r="X25" s="17">
         <f>-$U$3*EXP(-T25*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO25" s="13">
+      <c r="AO25" s="15">
         <f>AO24+$AU$2</f>
         <v/>
       </c>
-      <c r="AP25" s="14">
+      <c r="AP25" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO25*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ25" s="14">
+      <c r="AQ25" s="16">
         <f>$AP$3*EXP(-AO25*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR25" s="15">
+      <c r="AR25" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO25*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS25" s="15">
+      <c r="AS25" s="17">
         <f>-$AP$3*EXP(-AO25*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13">
+      <c r="A26" s="15">
         <f>A25+$G$2</f>
         <v/>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A26*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="16">
         <f>$B$3*EXP(-A26*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="17">
         <f>($B$3/$B$5)*EXP(-A26*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="17">
         <f>-$B$3*EXP(-A26*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T26" s="13">
+      <c r="T26" s="15">
         <f>T25+$Z$2</f>
         <v/>
       </c>
-      <c r="U26" s="14">
+      <c r="U26" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T26*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V26" s="14">
+      <c r="V26" s="16">
         <f>$U$3*EXP(-T26*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W26" s="15">
+      <c r="W26" s="17">
         <f>($U$3/$U$5)*EXP(-T26*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X26" s="15">
+      <c r="X26" s="17">
         <f>-$U$3*EXP(-T26*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO26" s="13">
+      <c r="AO26" s="15">
         <f>AO25+$AU$2</f>
         <v/>
       </c>
-      <c r="AP26" s="14">
+      <c r="AP26" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO26*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ26" s="14">
+      <c r="AQ26" s="16">
         <f>$AP$3*EXP(-AO26*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR26" s="15">
+      <c r="AR26" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO26*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS26" s="15">
+      <c r="AS26" s="17">
         <f>-$AP$3*EXP(-AO26*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13">
+      <c r="A27" s="15">
         <f>A26+$G$2</f>
         <v/>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A27*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="16">
         <f>$B$3*EXP(-A27*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="17">
         <f>($B$3/$B$5)*EXP(-A27*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="17">
         <f>-$B$3*EXP(-A27*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T27" s="13">
+      <c r="T27" s="15">
         <f>T26+$Z$2</f>
         <v/>
       </c>
-      <c r="U27" s="14">
+      <c r="U27" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T27*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V27" s="14">
+      <c r="V27" s="16">
         <f>$U$3*EXP(-T27*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W27" s="15">
+      <c r="W27" s="17">
         <f>($U$3/$U$5)*EXP(-T27*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X27" s="15">
+      <c r="X27" s="17">
         <f>-$U$3*EXP(-T27*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO27" s="13">
+      <c r="AO27" s="15">
         <f>AO26+$AU$2</f>
         <v/>
       </c>
-      <c r="AP27" s="14">
+      <c r="AP27" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO27*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ27" s="14">
+      <c r="AQ27" s="16">
         <f>$AP$3*EXP(-AO27*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR27" s="15">
+      <c r="AR27" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO27*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS27" s="15">
+      <c r="AS27" s="17">
         <f>-$AP$3*EXP(-AO27*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13">
+      <c r="A28" s="15">
         <f>A27+$G$2</f>
         <v/>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A28*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="16">
         <f>$B$3*EXP(-A28*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="17">
         <f>($B$3/$B$5)*EXP(-A28*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="17">
         <f>-$B$3*EXP(-A28*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T28" s="13">
+      <c r="T28" s="15">
         <f>T27+$Z$2</f>
         <v/>
       </c>
-      <c r="U28" s="14">
+      <c r="U28" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T28*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V28" s="14">
+      <c r="V28" s="16">
         <f>$U$3*EXP(-T28*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W28" s="15">
+      <c r="W28" s="17">
         <f>($U$3/$U$5)*EXP(-T28*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X28" s="15">
+      <c r="X28" s="17">
         <f>-$U$3*EXP(-T28*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO28" s="13">
+      <c r="AO28" s="15">
         <f>AO27+$AU$2</f>
         <v/>
       </c>
-      <c r="AP28" s="14">
+      <c r="AP28" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO28*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ28" s="14">
+      <c r="AQ28" s="16">
         <f>$AP$3*EXP(-AO28*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR28" s="15">
+      <c r="AR28" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO28*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS28" s="15">
+      <c r="AS28" s="17">
         <f>-$AP$3*EXP(-AO28*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13">
+      <c r="A29" s="15">
         <f>A28+$G$2</f>
         <v/>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A29*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="16">
         <f>$B$3*EXP(-A29*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="17">
         <f>($B$3/$B$5)*EXP(-A29*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="17">
         <f>-$B$3*EXP(-A29*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T29" s="13">
+      <c r="T29" s="15">
         <f>T28+$Z$2</f>
         <v/>
       </c>
-      <c r="U29" s="14">
+      <c r="U29" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T29*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V29" s="14">
+      <c r="V29" s="16">
         <f>$U$3*EXP(-T29*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W29" s="15">
+      <c r="W29" s="17">
         <f>($U$3/$U$5)*EXP(-T29*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X29" s="15">
+      <c r="X29" s="17">
         <f>-$U$3*EXP(-T29*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO29" s="13">
+      <c r="AO29" s="15">
         <f>AO28+$AU$2</f>
         <v/>
       </c>
-      <c r="AP29" s="14">
+      <c r="AP29" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO29*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ29" s="14">
+      <c r="AQ29" s="16">
         <f>$AP$3*EXP(-AO29*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR29" s="15">
+      <c r="AR29" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO29*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS29" s="15">
+      <c r="AS29" s="17">
         <f>-$AP$3*EXP(-AO29*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13">
+      <c r="A30" s="15">
         <f>A29+$G$2</f>
         <v/>
       </c>
-      <c r="B30" s="14">
+      <c r="B30" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A30*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="16">
         <f>$B$3*EXP(-A30*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="17">
         <f>($B$3/$B$5)*EXP(-A30*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="17">
         <f>-$B$3*EXP(-A30*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T30" s="13">
+      <c r="T30" s="15">
         <f>T29+$Z$2</f>
         <v/>
       </c>
-      <c r="U30" s="14">
+      <c r="U30" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T30*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V30" s="14">
+      <c r="V30" s="16">
         <f>$U$3*EXP(-T30*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W30" s="15">
+      <c r="W30" s="17">
         <f>($U$3/$U$5)*EXP(-T30*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X30" s="15">
+      <c r="X30" s="17">
         <f>-$U$3*EXP(-T30*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO30" s="13">
+      <c r="AO30" s="15">
         <f>AO29+$AU$2</f>
         <v/>
       </c>
-      <c r="AP30" s="14">
+      <c r="AP30" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO30*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ30" s="14">
+      <c r="AQ30" s="16">
         <f>$AP$3*EXP(-AO30*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR30" s="15">
+      <c r="AR30" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO30*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS30" s="15">
+      <c r="AS30" s="17">
         <f>-$AP$3*EXP(-AO30*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13">
+      <c r="A31" s="15">
         <f>A30+$G$2</f>
         <v/>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A31*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="16">
         <f>$B$3*EXP(-A31*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="17">
         <f>($B$3/$B$5)*EXP(-A31*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="17">
         <f>-$B$3*EXP(-A31*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T31" s="13">
+      <c r="T31" s="15">
         <f>T30+$Z$2</f>
         <v/>
       </c>
-      <c r="U31" s="14">
+      <c r="U31" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T31*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V31" s="14">
+      <c r="V31" s="16">
         <f>$U$3*EXP(-T31*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W31" s="15">
+      <c r="W31" s="17">
         <f>($U$3/$U$5)*EXP(-T31*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X31" s="15">
+      <c r="X31" s="17">
         <f>-$U$3*EXP(-T31*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO31" s="13">
+      <c r="AO31" s="15">
         <f>AO30+$AU$2</f>
         <v/>
       </c>
-      <c r="AP31" s="14">
+      <c r="AP31" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO31*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ31" s="14">
+      <c r="AQ31" s="16">
         <f>$AP$3*EXP(-AO31*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR31" s="15">
+      <c r="AR31" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO31*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS31" s="15">
+      <c r="AS31" s="17">
         <f>-$AP$3*EXP(-AO31*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13">
+      <c r="A32" s="15">
         <f>A31+$G$2</f>
         <v/>
       </c>
-      <c r="B32" s="14">
+      <c r="B32" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A32*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="16">
         <f>$B$3*EXP(-A32*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="17">
         <f>($B$3/$B$5)*EXP(-A32*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="17">
         <f>-$B$3*EXP(-A32*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T32" s="13">
+      <c r="T32" s="15">
         <f>T31+$Z$2</f>
         <v/>
       </c>
-      <c r="U32" s="14">
+      <c r="U32" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T32*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V32" s="14">
+      <c r="V32" s="16">
         <f>$U$3*EXP(-T32*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W32" s="15">
+      <c r="W32" s="17">
         <f>($U$3/$U$5)*EXP(-T32*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X32" s="15">
+      <c r="X32" s="17">
         <f>-$U$3*EXP(-T32*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO32" s="13">
+      <c r="AO32" s="15">
         <f>AO31+$AU$2</f>
         <v/>
       </c>
-      <c r="AP32" s="14">
+      <c r="AP32" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO32*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ32" s="14">
+      <c r="AQ32" s="16">
         <f>$AP$3*EXP(-AO32*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR32" s="15">
+      <c r="AR32" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO32*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS32" s="15">
+      <c r="AS32" s="17">
         <f>-$AP$3*EXP(-AO32*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13">
+      <c r="A33" s="15">
         <f>A32+$G$2</f>
         <v/>
       </c>
-      <c r="B33" s="14">
+      <c r="B33" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A33*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="16">
         <f>$B$3*EXP(-A33*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="17">
         <f>($B$3/$B$5)*EXP(-A33*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="17">
         <f>-$B$3*EXP(-A33*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T33" s="13">
+      <c r="T33" s="15">
         <f>T32+$Z$2</f>
         <v/>
       </c>
-      <c r="U33" s="14">
+      <c r="U33" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T33*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V33" s="14">
+      <c r="V33" s="16">
         <f>$U$3*EXP(-T33*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W33" s="15">
+      <c r="W33" s="17">
         <f>($U$3/$U$5)*EXP(-T33*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X33" s="15">
+      <c r="X33" s="17">
         <f>-$U$3*EXP(-T33*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO33" s="13">
+      <c r="AO33" s="15">
         <f>AO32+$AU$2</f>
         <v/>
       </c>
-      <c r="AP33" s="14">
+      <c r="AP33" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO33*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ33" s="14">
+      <c r="AQ33" s="16">
         <f>$AP$3*EXP(-AO33*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR33" s="15">
+      <c r="AR33" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO33*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS33" s="15">
+      <c r="AS33" s="17">
         <f>-$AP$3*EXP(-AO33*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13">
+      <c r="A34" s="15">
         <f>A33+$G$2</f>
         <v/>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A34*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="16">
         <f>$B$3*EXP(-A34*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="17">
         <f>($B$3/$B$5)*EXP(-A34*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="17">
         <f>-$B$3*EXP(-A34*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T34" s="13">
+      <c r="T34" s="15">
         <f>T33+$Z$2</f>
         <v/>
       </c>
-      <c r="U34" s="14">
+      <c r="U34" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T34*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V34" s="14">
+      <c r="V34" s="16">
         <f>$U$3*EXP(-T34*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W34" s="15">
+      <c r="W34" s="17">
         <f>($U$3/$U$5)*EXP(-T34*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X34" s="15">
+      <c r="X34" s="17">
         <f>-$U$3*EXP(-T34*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO34" s="13">
+      <c r="AO34" s="15">
         <f>AO33+$AU$2</f>
         <v/>
       </c>
-      <c r="AP34" s="14">
+      <c r="AP34" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO34*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ34" s="14">
+      <c r="AQ34" s="16">
         <f>$AP$3*EXP(-AO34*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR34" s="15">
+      <c r="AR34" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO34*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS34" s="15">
+      <c r="AS34" s="17">
         <f>-$AP$3*EXP(-AO34*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13">
+      <c r="A35" s="15">
         <f>A34+$G$2</f>
         <v/>
       </c>
-      <c r="B35" s="14">
+      <c r="B35" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A35*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="16">
         <f>$B$3*EXP(-A35*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="17">
         <f>($B$3/$B$5)*EXP(-A35*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>-$B$3*EXP(-A35*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T35" s="13">
+      <c r="T35" s="15">
         <f>T34+$Z$2</f>
         <v/>
       </c>
-      <c r="U35" s="14">
+      <c r="U35" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T35*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V35" s="14">
+      <c r="V35" s="16">
         <f>$U$3*EXP(-T35*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W35" s="15">
+      <c r="W35" s="17">
         <f>($U$3/$U$5)*EXP(-T35*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X35" s="15">
+      <c r="X35" s="17">
         <f>-$U$3*EXP(-T35*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO35" s="13">
+      <c r="AO35" s="15">
         <f>AO34+$AU$2</f>
         <v/>
       </c>
-      <c r="AP35" s="14">
+      <c r="AP35" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO35*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ35" s="14">
+      <c r="AQ35" s="16">
         <f>$AP$3*EXP(-AO35*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR35" s="15">
+      <c r="AR35" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO35*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS35" s="15">
+      <c r="AS35" s="17">
         <f>-$AP$3*EXP(-AO35*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13">
+      <c r="A36" s="15">
         <f>A35+$G$2</f>
         <v/>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A36*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="16">
         <f>$B$3*EXP(-A36*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="17">
         <f>($B$3/$B$5)*EXP(-A36*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="17">
         <f>-$B$3*EXP(-A36*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T36" s="13">
+      <c r="T36" s="15">
         <f>T35+$Z$2</f>
         <v/>
       </c>
-      <c r="U36" s="14">
+      <c r="U36" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T36*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V36" s="14">
+      <c r="V36" s="16">
         <f>$U$3*EXP(-T36*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W36" s="15">
+      <c r="W36" s="17">
         <f>($U$3/$U$5)*EXP(-T36*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X36" s="15">
+      <c r="X36" s="17">
         <f>-$U$3*EXP(-T36*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO36" s="13">
+      <c r="AO36" s="15">
         <f>AO35+$AU$2</f>
         <v/>
       </c>
-      <c r="AP36" s="14">
+      <c r="AP36" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO36*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ36" s="14">
+      <c r="AQ36" s="16">
         <f>$AP$3*EXP(-AO36*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR36" s="15">
+      <c r="AR36" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO36*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS36" s="15">
+      <c r="AS36" s="17">
         <f>-$AP$3*EXP(-AO36*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13">
+      <c r="A37" s="15">
         <f>A36+$G$2</f>
         <v/>
       </c>
-      <c r="B37" s="14">
+      <c r="B37" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A37*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="16">
         <f>$B$3*EXP(-A37*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="17">
         <f>($B$3/$B$5)*EXP(-A37*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="17">
         <f>-$B$3*EXP(-A37*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T37" s="13">
+      <c r="T37" s="15">
         <f>T36+$Z$2</f>
         <v/>
       </c>
-      <c r="U37" s="14">
+      <c r="U37" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T37*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V37" s="14">
+      <c r="V37" s="16">
         <f>$U$3*EXP(-T37*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W37" s="15">
+      <c r="W37" s="17">
         <f>($U$3/$U$5)*EXP(-T37*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X37" s="15">
+      <c r="X37" s="17">
         <f>-$U$3*EXP(-T37*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO37" s="13">
+      <c r="AO37" s="15">
         <f>AO36+$AU$2</f>
         <v/>
       </c>
-      <c r="AP37" s="14">
+      <c r="AP37" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO37*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ37" s="14">
+      <c r="AQ37" s="16">
         <f>$AP$3*EXP(-AO37*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR37" s="15">
+      <c r="AR37" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO37*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS37" s="15">
+      <c r="AS37" s="17">
         <f>-$AP$3*EXP(-AO37*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13">
+      <c r="A38" s="15">
         <f>A37+$G$2</f>
         <v/>
       </c>
-      <c r="B38" s="14">
+      <c r="B38" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A38*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="16">
         <f>$B$3*EXP(-A38*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="17">
         <f>($B$3/$B$5)*EXP(-A38*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="17">
         <f>-$B$3*EXP(-A38*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T38" s="13">
+      <c r="T38" s="15">
         <f>T37+$Z$2</f>
         <v/>
       </c>
-      <c r="U38" s="14">
+      <c r="U38" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T38*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V38" s="14">
+      <c r="V38" s="16">
         <f>$U$3*EXP(-T38*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W38" s="15">
+      <c r="W38" s="17">
         <f>($U$3/$U$5)*EXP(-T38*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X38" s="15">
+      <c r="X38" s="17">
         <f>-$U$3*EXP(-T38*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO38" s="13">
+      <c r="AO38" s="15">
         <f>AO37+$AU$2</f>
         <v/>
       </c>
-      <c r="AP38" s="14">
+      <c r="AP38" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO38*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ38" s="14">
+      <c r="AQ38" s="16">
         <f>$AP$3*EXP(-AO38*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR38" s="15">
+      <c r="AR38" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO38*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS38" s="15">
+      <c r="AS38" s="17">
         <f>-$AP$3*EXP(-AO38*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13">
+      <c r="A39" s="15">
         <f>A38+$G$2</f>
         <v/>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A39*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="16">
         <f>$B$3*EXP(-A39*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="17">
         <f>($B$3/$B$5)*EXP(-A39*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="17">
         <f>-$B$3*EXP(-A39*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T39" s="13">
+      <c r="T39" s="15">
         <f>T38+$Z$2</f>
         <v/>
       </c>
-      <c r="U39" s="14">
+      <c r="U39" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T39*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V39" s="14">
+      <c r="V39" s="16">
         <f>$U$3*EXP(-T39*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W39" s="15">
+      <c r="W39" s="17">
         <f>($U$3/$U$5)*EXP(-T39*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X39" s="15">
+      <c r="X39" s="17">
         <f>-$U$3*EXP(-T39*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO39" s="13">
+      <c r="AO39" s="15">
         <f>AO38+$AU$2</f>
         <v/>
       </c>
-      <c r="AP39" s="14">
+      <c r="AP39" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO39*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ39" s="14">
+      <c r="AQ39" s="16">
         <f>$AP$3*EXP(-AO39*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR39" s="15">
+      <c r="AR39" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO39*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS39" s="15">
+      <c r="AS39" s="17">
         <f>-$AP$3*EXP(-AO39*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13">
+      <c r="A40" s="15">
         <f>A39+$G$2</f>
         <v/>
       </c>
-      <c r="B40" s="14">
+      <c r="B40" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A40*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="16">
         <f>$B$3*EXP(-A40*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="17">
         <f>($B$3/$B$5)*EXP(-A40*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="17">
         <f>-$B$3*EXP(-A40*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T40" s="13">
+      <c r="T40" s="15">
         <f>T39+$Z$2</f>
         <v/>
       </c>
-      <c r="U40" s="14">
+      <c r="U40" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T40*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V40" s="14">
+      <c r="V40" s="16">
         <f>$U$3*EXP(-T40*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W40" s="15">
+      <c r="W40" s="17">
         <f>($U$3/$U$5)*EXP(-T40*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X40" s="15">
+      <c r="X40" s="17">
         <f>-$U$3*EXP(-T40*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO40" s="13">
+      <c r="AO40" s="15">
         <f>AO39+$AU$2</f>
         <v/>
       </c>
-      <c r="AP40" s="14">
+      <c r="AP40" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO40*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ40" s="14">
+      <c r="AQ40" s="16">
         <f>$AP$3*EXP(-AO40*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR40" s="15">
+      <c r="AR40" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO40*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS40" s="15">
+      <c r="AS40" s="17">
         <f>-$AP$3*EXP(-AO40*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13">
+      <c r="A41" s="15">
         <f>A40+$G$2</f>
         <v/>
       </c>
-      <c r="B41" s="14">
+      <c r="B41" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A41*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="16">
         <f>$B$3*EXP(-A41*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="17">
         <f>($B$3/$B$5)*EXP(-A41*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="17">
         <f>-$B$3*EXP(-A41*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T41" s="13">
+      <c r="T41" s="15">
         <f>T40+$Z$2</f>
         <v/>
       </c>
-      <c r="U41" s="14">
+      <c r="U41" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T41*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V41" s="14">
+      <c r="V41" s="16">
         <f>$U$3*EXP(-T41*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W41" s="15">
+      <c r="W41" s="17">
         <f>($U$3/$U$5)*EXP(-T41*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X41" s="15">
+      <c r="X41" s="17">
         <f>-$U$3*EXP(-T41*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO41" s="13">
+      <c r="AO41" s="15">
         <f>AO40+$AU$2</f>
         <v/>
       </c>
-      <c r="AP41" s="14">
+      <c r="AP41" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO41*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ41" s="14">
+      <c r="AQ41" s="16">
         <f>$AP$3*EXP(-AO41*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR41" s="15">
+      <c r="AR41" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO41*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS41" s="15">
+      <c r="AS41" s="17">
         <f>-$AP$3*EXP(-AO41*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13">
+      <c r="A42" s="15">
         <f>A41+$G$2</f>
         <v/>
       </c>
-      <c r="B42" s="14">
+      <c r="B42" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A42*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="16">
         <f>$B$3*EXP(-A42*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="17">
         <f>($B$3/$B$5)*EXP(-A42*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="17">
         <f>-$B$3*EXP(-A42*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T42" s="13">
+      <c r="T42" s="15">
         <f>T41+$Z$2</f>
         <v/>
       </c>
-      <c r="U42" s="14">
+      <c r="U42" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T42*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V42" s="14">
+      <c r="V42" s="16">
         <f>$U$3*EXP(-T42*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W42" s="15">
+      <c r="W42" s="17">
         <f>($U$3/$U$5)*EXP(-T42*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X42" s="15">
+      <c r="X42" s="17">
         <f>-$U$3*EXP(-T42*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO42" s="13">
+      <c r="AO42" s="15">
         <f>AO41+$AU$2</f>
         <v/>
       </c>
-      <c r="AP42" s="14">
+      <c r="AP42" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO42*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ42" s="14">
+      <c r="AQ42" s="16">
         <f>$AP$3*EXP(-AO42*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR42" s="15">
+      <c r="AR42" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO42*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS42" s="15">
+      <c r="AS42" s="17">
         <f>-$AP$3*EXP(-AO42*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13">
+      <c r="A43" s="15">
         <f>A42+$G$2</f>
         <v/>
       </c>
-      <c r="B43" s="14">
+      <c r="B43" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A43*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="16">
         <f>$B$3*EXP(-A43*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="17">
         <f>($B$3/$B$5)*EXP(-A43*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="17">
         <f>-$B$3*EXP(-A43*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T43" s="13">
+      <c r="T43" s="15">
         <f>T42+$Z$2</f>
         <v/>
       </c>
-      <c r="U43" s="14">
+      <c r="U43" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T43*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V43" s="14">
+      <c r="V43" s="16">
         <f>$U$3*EXP(-T43*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W43" s="15">
+      <c r="W43" s="17">
         <f>($U$3/$U$5)*EXP(-T43*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X43" s="15">
+      <c r="X43" s="17">
         <f>-$U$3*EXP(-T43*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO43" s="13">
+      <c r="AO43" s="15">
         <f>AO42+$AU$2</f>
         <v/>
       </c>
-      <c r="AP43" s="14">
+      <c r="AP43" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO43*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ43" s="14">
+      <c r="AQ43" s="16">
         <f>$AP$3*EXP(-AO43*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR43" s="15">
+      <c r="AR43" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO43*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS43" s="15">
+      <c r="AS43" s="17">
         <f>-$AP$3*EXP(-AO43*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13">
+      <c r="A44" s="15">
         <f>A43+$G$2</f>
         <v/>
       </c>
-      <c r="B44" s="14">
+      <c r="B44" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A44*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="16">
         <f>$B$3*EXP(-A44*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="17">
         <f>($B$3/$B$5)*EXP(-A44*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="17">
         <f>-$B$3*EXP(-A44*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T44" s="13">
+      <c r="T44" s="15">
         <f>T43+$Z$2</f>
         <v/>
       </c>
-      <c r="U44" s="14">
+      <c r="U44" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T44*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V44" s="14">
+      <c r="V44" s="16">
         <f>$U$3*EXP(-T44*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W44" s="15">
+      <c r="W44" s="17">
         <f>($U$3/$U$5)*EXP(-T44*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X44" s="15">
+      <c r="X44" s="17">
         <f>-$U$3*EXP(-T44*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO44" s="13">
+      <c r="AO44" s="15">
         <f>AO43+$AU$2</f>
         <v/>
       </c>
-      <c r="AP44" s="14">
+      <c r="AP44" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO44*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ44" s="14">
+      <c r="AQ44" s="16">
         <f>$AP$3*EXP(-AO44*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR44" s="15">
+      <c r="AR44" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO44*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS44" s="15">
+      <c r="AS44" s="17">
         <f>-$AP$3*EXP(-AO44*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13">
+      <c r="A45" s="15">
         <f>A44+$G$2</f>
         <v/>
       </c>
-      <c r="B45" s="14">
+      <c r="B45" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A45*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="16">
         <f>$B$3*EXP(-A45*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="17">
         <f>($B$3/$B$5)*EXP(-A45*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="17">
         <f>-$B$3*EXP(-A45*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T45" s="13">
+      <c r="T45" s="15">
         <f>T44+$Z$2</f>
         <v/>
       </c>
-      <c r="U45" s="14">
+      <c r="U45" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T45*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V45" s="14">
+      <c r="V45" s="16">
         <f>$U$3*EXP(-T45*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W45" s="15">
+      <c r="W45" s="17">
         <f>($U$3/$U$5)*EXP(-T45*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X45" s="15">
+      <c r="X45" s="17">
         <f>-$U$3*EXP(-T45*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO45" s="13">
+      <c r="AO45" s="15">
         <f>AO44+$AU$2</f>
         <v/>
       </c>
-      <c r="AP45" s="14">
+      <c r="AP45" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO45*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ45" s="14">
+      <c r="AQ45" s="16">
         <f>$AP$3*EXP(-AO45*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR45" s="15">
+      <c r="AR45" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO45*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS45" s="15">
+      <c r="AS45" s="17">
         <f>-$AP$3*EXP(-AO45*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13">
+      <c r="A46" s="15">
         <f>A45+$G$2</f>
         <v/>
       </c>
-      <c r="B46" s="14">
+      <c r="B46" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A46*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C46" s="14">
+      <c r="C46" s="16">
         <f>$B$3*EXP(-A46*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D46" s="15">
+      <c r="D46" s="17">
         <f>($B$3/$B$5)*EXP(-A46*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E46" s="15">
+      <c r="E46" s="17">
         <f>-$B$3*EXP(-A46*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T46" s="13">
+      <c r="T46" s="15">
         <f>T45+$Z$2</f>
         <v/>
       </c>
-      <c r="U46" s="14">
+      <c r="U46" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T46*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V46" s="14">
+      <c r="V46" s="16">
         <f>$U$3*EXP(-T46*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W46" s="15">
+      <c r="W46" s="17">
         <f>($U$3/$U$5)*EXP(-T46*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X46" s="15">
+      <c r="X46" s="17">
         <f>-$U$3*EXP(-T46*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO46" s="13">
+      <c r="AO46" s="15">
         <f>AO45+$AU$2</f>
         <v/>
       </c>
-      <c r="AP46" s="14">
+      <c r="AP46" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO46*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ46" s="14">
+      <c r="AQ46" s="16">
         <f>$AP$3*EXP(-AO46*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR46" s="15">
+      <c r="AR46" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO46*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS46" s="15">
+      <c r="AS46" s="17">
         <f>-$AP$3*EXP(-AO46*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="13">
+      <c r="A47" s="15">
         <f>A46+$G$2</f>
         <v/>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A47*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="16">
         <f>$B$3*EXP(-A47*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="17">
         <f>($B$3/$B$5)*EXP(-A47*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E47" s="15">
+      <c r="E47" s="17">
         <f>-$B$3*EXP(-A47*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T47" s="13">
+      <c r="T47" s="15">
         <f>T46+$Z$2</f>
         <v/>
       </c>
-      <c r="U47" s="14">
+      <c r="U47" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T47*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V47" s="14">
+      <c r="V47" s="16">
         <f>$U$3*EXP(-T47*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W47" s="15">
+      <c r="W47" s="17">
         <f>($U$3/$U$5)*EXP(-T47*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X47" s="15">
+      <c r="X47" s="17">
         <f>-$U$3*EXP(-T47*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO47" s="13">
+      <c r="AO47" s="15">
         <f>AO46+$AU$2</f>
         <v/>
       </c>
-      <c r="AP47" s="14">
+      <c r="AP47" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO47*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ47" s="14">
+      <c r="AQ47" s="16">
         <f>$AP$3*EXP(-AO47*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR47" s="15">
+      <c r="AR47" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO47*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS47" s="15">
+      <c r="AS47" s="17">
         <f>-$AP$3*EXP(-AO47*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="13">
+      <c r="A48" s="15">
         <f>A47+$G$2</f>
         <v/>
       </c>
-      <c r="B48" s="14">
+      <c r="B48" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A48*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C48" s="14">
+      <c r="C48" s="16">
         <f>$B$3*EXP(-A48*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D48" s="15">
+      <c r="D48" s="17">
         <f>($B$3/$B$5)*EXP(-A48*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E48" s="15">
+      <c r="E48" s="17">
         <f>-$B$3*EXP(-A48*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T48" s="13">
+      <c r="T48" s="15">
         <f>T47+$Z$2</f>
         <v/>
       </c>
-      <c r="U48" s="14">
+      <c r="U48" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T48*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V48" s="14">
+      <c r="V48" s="16">
         <f>$U$3*EXP(-T48*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W48" s="15">
+      <c r="W48" s="17">
         <f>($U$3/$U$5)*EXP(-T48*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X48" s="15">
+      <c r="X48" s="17">
         <f>-$U$3*EXP(-T48*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO48" s="13">
+      <c r="AO48" s="15">
         <f>AO47+$AU$2</f>
         <v/>
       </c>
-      <c r="AP48" s="14">
+      <c r="AP48" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO48*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ48" s="14">
+      <c r="AQ48" s="16">
         <f>$AP$3*EXP(-AO48*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR48" s="15">
+      <c r="AR48" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO48*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS48" s="15">
+      <c r="AS48" s="17">
         <f>-$AP$3*EXP(-AO48*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="13">
+      <c r="A49" s="15">
         <f>A48+$G$2</f>
         <v/>
       </c>
-      <c r="B49" s="14">
+      <c r="B49" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A49*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="16">
         <f>$B$3*EXP(-A49*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="17">
         <f>($B$3/$B$5)*EXP(-A49*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E49" s="15">
+      <c r="E49" s="17">
         <f>-$B$3*EXP(-A49*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T49" s="13">
+      <c r="T49" s="15">
         <f>T48+$Z$2</f>
         <v/>
       </c>
-      <c r="U49" s="14">
+      <c r="U49" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T49*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V49" s="14">
+      <c r="V49" s="16">
         <f>$U$3*EXP(-T49*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W49" s="15">
+      <c r="W49" s="17">
         <f>($U$3/$U$5)*EXP(-T49*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X49" s="15">
+      <c r="X49" s="17">
         <f>-$U$3*EXP(-T49*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO49" s="13">
+      <c r="AO49" s="15">
         <f>AO48+$AU$2</f>
         <v/>
       </c>
-      <c r="AP49" s="14">
+      <c r="AP49" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO49*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ49" s="14">
+      <c r="AQ49" s="16">
         <f>$AP$3*EXP(-AO49*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR49" s="15">
+      <c r="AR49" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO49*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS49" s="15">
+      <c r="AS49" s="17">
         <f>-$AP$3*EXP(-AO49*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="13">
+      <c r="A50" s="15">
         <f>A49+$G$2</f>
         <v/>
       </c>
-      <c r="B50" s="14">
+      <c r="B50" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A50*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="16">
         <f>$B$3*EXP(-A50*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="17">
         <f>($B$3/$B$5)*EXP(-A50*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E50" s="15">
+      <c r="E50" s="17">
         <f>-$B$3*EXP(-A50*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T50" s="13">
+      <c r="T50" s="15">
         <f>T49+$Z$2</f>
         <v/>
       </c>
-      <c r="U50" s="14">
+      <c r="U50" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T50*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V50" s="14">
+      <c r="V50" s="16">
         <f>$U$3*EXP(-T50*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W50" s="15">
+      <c r="W50" s="17">
         <f>($U$3/$U$5)*EXP(-T50*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X50" s="15">
+      <c r="X50" s="17">
         <f>-$U$3*EXP(-T50*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO50" s="13">
+      <c r="AO50" s="15">
         <f>AO49+$AU$2</f>
         <v/>
       </c>
-      <c r="AP50" s="14">
+      <c r="AP50" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO50*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ50" s="14">
+      <c r="AQ50" s="16">
         <f>$AP$3*EXP(-AO50*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR50" s="15">
+      <c r="AR50" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO50*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS50" s="15">
+      <c r="AS50" s="17">
         <f>-$AP$3*EXP(-AO50*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="13">
+      <c r="A51" s="15">
         <f>A50+$G$2</f>
         <v/>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A51*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C51" s="14">
+      <c r="C51" s="16">
         <f>$B$3*EXP(-A51*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="17">
         <f>($B$3/$B$5)*EXP(-A51*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="17">
         <f>-$B$3*EXP(-A51*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T51" s="13">
+      <c r="T51" s="15">
         <f>T50+$Z$2</f>
         <v/>
       </c>
-      <c r="U51" s="14">
+      <c r="U51" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T51*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V51" s="14">
+      <c r="V51" s="16">
         <f>$U$3*EXP(-T51*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W51" s="15">
+      <c r="W51" s="17">
         <f>($U$3/$U$5)*EXP(-T51*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X51" s="15">
+      <c r="X51" s="17">
         <f>-$U$3*EXP(-T51*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO51" s="13">
+      <c r="AO51" s="15">
         <f>AO50+$AU$2</f>
         <v/>
       </c>
-      <c r="AP51" s="14">
+      <c r="AP51" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO51*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ51" s="14">
+      <c r="AQ51" s="16">
         <f>$AP$3*EXP(-AO51*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR51" s="15">
+      <c r="AR51" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO51*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS51" s="15">
+      <c r="AS51" s="17">
         <f>-$AP$3*EXP(-AO51*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="13">
+      <c r="A52" s="15">
         <f>A51+$G$2</f>
         <v/>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A52*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C52" s="14">
+      <c r="C52" s="16">
         <f>$B$3*EXP(-A52*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="17">
         <f>($B$3/$B$5)*EXP(-A52*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E52" s="15">
+      <c r="E52" s="17">
         <f>-$B$3*EXP(-A52*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T52" s="13">
+      <c r="T52" s="15">
         <f>T51+$Z$2</f>
         <v/>
       </c>
-      <c r="U52" s="14">
+      <c r="U52" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T52*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V52" s="14">
+      <c r="V52" s="16">
         <f>$U$3*EXP(-T52*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W52" s="15">
+      <c r="W52" s="17">
         <f>($U$3/$U$5)*EXP(-T52*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X52" s="15">
+      <c r="X52" s="17">
         <f>-$U$3*EXP(-T52*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO52" s="13">
+      <c r="AO52" s="15">
         <f>AO51+$AU$2</f>
         <v/>
       </c>
-      <c r="AP52" s="14">
+      <c r="AP52" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO52*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ52" s="14">
+      <c r="AQ52" s="16">
         <f>$AP$3*EXP(-AO52*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR52" s="15">
+      <c r="AR52" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO52*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS52" s="15">
+      <c r="AS52" s="17">
         <f>-$AP$3*EXP(-AO52*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13">
+      <c r="A53" s="15">
         <f>A52+$G$2</f>
         <v/>
       </c>
-      <c r="B53" s="14">
+      <c r="B53" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A53*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C53" s="14">
+      <c r="C53" s="16">
         <f>$B$3*EXP(-A53*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D53" s="15">
+      <c r="D53" s="17">
         <f>($B$3/$B$5)*EXP(-A53*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E53" s="15">
+      <c r="E53" s="17">
         <f>-$B$3*EXP(-A53*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T53" s="13">
+      <c r="T53" s="15">
         <f>T52+$Z$2</f>
         <v/>
       </c>
-      <c r="U53" s="14">
+      <c r="U53" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T53*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V53" s="14">
+      <c r="V53" s="16">
         <f>$U$3*EXP(-T53*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W53" s="15">
+      <c r="W53" s="17">
         <f>($U$3/$U$5)*EXP(-T53*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X53" s="15">
+      <c r="X53" s="17">
         <f>-$U$3*EXP(-T53*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO53" s="13">
+      <c r="AO53" s="15">
         <f>AO52+$AU$2</f>
         <v/>
       </c>
-      <c r="AP53" s="14">
+      <c r="AP53" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO53*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ53" s="14">
+      <c r="AQ53" s="16">
         <f>$AP$3*EXP(-AO53*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR53" s="15">
+      <c r="AR53" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO53*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS53" s="15">
+      <c r="AS53" s="17">
         <f>-$AP$3*EXP(-AO53*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="13">
+      <c r="A54" s="15">
         <f>A53+$G$2</f>
         <v/>
       </c>
-      <c r="B54" s="14">
+      <c r="B54" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A54*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C54" s="14">
+      <c r="C54" s="16">
         <f>$B$3*EXP(-A54*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D54" s="15">
+      <c r="D54" s="17">
         <f>($B$3/$B$5)*EXP(-A54*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E54" s="15">
+      <c r="E54" s="17">
         <f>-$B$3*EXP(-A54*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T54" s="13">
+      <c r="T54" s="15">
         <f>T53+$Z$2</f>
         <v/>
       </c>
-      <c r="U54" s="14">
+      <c r="U54" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T54*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V54" s="14">
+      <c r="V54" s="16">
         <f>$U$3*EXP(-T54*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W54" s="15">
+      <c r="W54" s="17">
         <f>($U$3/$U$5)*EXP(-T54*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X54" s="15">
+      <c r="X54" s="17">
         <f>-$U$3*EXP(-T54*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO54" s="13">
+      <c r="AO54" s="15">
         <f>AO53+$AU$2</f>
         <v/>
       </c>
-      <c r="AP54" s="14">
+      <c r="AP54" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO54*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ54" s="14">
+      <c r="AQ54" s="16">
         <f>$AP$3*EXP(-AO54*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR54" s="15">
+      <c r="AR54" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO54*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS54" s="15">
+      <c r="AS54" s="17">
         <f>-$AP$3*EXP(-AO54*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="13">
+      <c r="A55" s="15">
         <f>A54+$G$2</f>
         <v/>
       </c>
-      <c r="B55" s="14">
+      <c r="B55" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A55*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="16">
         <f>$B$3*EXP(-A55*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="17">
         <f>($B$3/$B$5)*EXP(-A55*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E55" s="15">
+      <c r="E55" s="17">
         <f>-$B$3*EXP(-A55*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T55" s="13">
+      <c r="T55" s="15">
         <f>T54+$Z$2</f>
         <v/>
       </c>
-      <c r="U55" s="14">
+      <c r="U55" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T55*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V55" s="14">
+      <c r="V55" s="16">
         <f>$U$3*EXP(-T55*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W55" s="15">
+      <c r="W55" s="17">
         <f>($U$3/$U$5)*EXP(-T55*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X55" s="15">
+      <c r="X55" s="17">
         <f>-$U$3*EXP(-T55*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO55" s="13">
+      <c r="AO55" s="15">
         <f>AO54+$AU$2</f>
         <v/>
       </c>
-      <c r="AP55" s="14">
+      <c r="AP55" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO55*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ55" s="14">
+      <c r="AQ55" s="16">
         <f>$AP$3*EXP(-AO55*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR55" s="15">
+      <c r="AR55" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO55*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS55" s="15">
+      <c r="AS55" s="17">
         <f>-$AP$3*EXP(-AO55*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="13">
+      <c r="A56" s="15">
         <f>A55+$G$2</f>
         <v/>
       </c>
-      <c r="B56" s="14">
+      <c r="B56" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A56*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C56" s="14">
+      <c r="C56" s="16">
         <f>$B$3*EXP(-A56*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D56" s="15">
+      <c r="D56" s="17">
         <f>($B$3/$B$5)*EXP(-A56*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E56" s="15">
+      <c r="E56" s="17">
         <f>-$B$3*EXP(-A56*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T56" s="13">
+      <c r="T56" s="15">
         <f>T55+$Z$2</f>
         <v/>
       </c>
-      <c r="U56" s="14">
+      <c r="U56" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T56*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V56" s="14">
+      <c r="V56" s="16">
         <f>$U$3*EXP(-T56*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W56" s="15">
+      <c r="W56" s="17">
         <f>($U$3/$U$5)*EXP(-T56*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X56" s="15">
+      <c r="X56" s="17">
         <f>-$U$3*EXP(-T56*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO56" s="13">
+      <c r="AO56" s="15">
         <f>AO55+$AU$2</f>
         <v/>
       </c>
-      <c r="AP56" s="14">
+      <c r="AP56" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO56*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ56" s="14">
+      <c r="AQ56" s="16">
         <f>$AP$3*EXP(-AO56*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR56" s="15">
+      <c r="AR56" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO56*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS56" s="15">
+      <c r="AS56" s="17">
         <f>-$AP$3*EXP(-AO56*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="13">
+      <c r="A57" s="15">
         <f>A56+$G$2</f>
         <v/>
       </c>
-      <c r="B57" s="14">
+      <c r="B57" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A57*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C57" s="14">
+      <c r="C57" s="16">
         <f>$B$3*EXP(-A57*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D57" s="15">
+      <c r="D57" s="17">
         <f>($B$3/$B$5)*EXP(-A57*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E57" s="15">
+      <c r="E57" s="17">
         <f>-$B$3*EXP(-A57*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T57" s="13">
+      <c r="T57" s="15">
         <f>T56+$Z$2</f>
         <v/>
       </c>
-      <c r="U57" s="14">
+      <c r="U57" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T57*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V57" s="14">
+      <c r="V57" s="16">
         <f>$U$3*EXP(-T57*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W57" s="15">
+      <c r="W57" s="17">
         <f>($U$3/$U$5)*EXP(-T57*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X57" s="15">
+      <c r="X57" s="17">
         <f>-$U$3*EXP(-T57*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO57" s="13">
+      <c r="AO57" s="15">
         <f>AO56+$AU$2</f>
         <v/>
       </c>
-      <c r="AP57" s="14">
+      <c r="AP57" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO57*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ57" s="14">
+      <c r="AQ57" s="16">
         <f>$AP$3*EXP(-AO57*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR57" s="15">
+      <c r="AR57" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO57*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS57" s="15">
+      <c r="AS57" s="17">
         <f>-$AP$3*EXP(-AO57*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="13">
+      <c r="A58" s="15">
         <f>A57+$G$2</f>
         <v/>
       </c>
-      <c r="B58" s="14">
+      <c r="B58" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A58*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C58" s="14">
+      <c r="C58" s="16">
         <f>$B$3*EXP(-A58*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D58" s="15">
+      <c r="D58" s="17">
         <f>($B$3/$B$5)*EXP(-A58*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E58" s="15">
+      <c r="E58" s="17">
         <f>-$B$3*EXP(-A58*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T58" s="13">
+      <c r="T58" s="15">
         <f>T57+$Z$2</f>
         <v/>
       </c>
-      <c r="U58" s="14">
+      <c r="U58" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T58*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V58" s="14">
+      <c r="V58" s="16">
         <f>$U$3*EXP(-T58*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W58" s="15">
+      <c r="W58" s="17">
         <f>($U$3/$U$5)*EXP(-T58*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X58" s="15">
+      <c r="X58" s="17">
         <f>-$U$3*EXP(-T58*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO58" s="13">
+      <c r="AO58" s="15">
         <f>AO57+$AU$2</f>
         <v/>
       </c>
-      <c r="AP58" s="14">
+      <c r="AP58" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO58*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ58" s="14">
+      <c r="AQ58" s="16">
         <f>$AP$3*EXP(-AO58*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR58" s="15">
+      <c r="AR58" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO58*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS58" s="15">
+      <c r="AS58" s="17">
         <f>-$AP$3*EXP(-AO58*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13">
+      <c r="A59" s="15">
         <f>A58+$G$2</f>
         <v/>
       </c>
-      <c r="B59" s="14">
+      <c r="B59" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A59*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C59" s="14">
+      <c r="C59" s="16">
         <f>$B$3*EXP(-A59*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D59" s="15">
+      <c r="D59" s="17">
         <f>($B$3/$B$5)*EXP(-A59*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E59" s="15">
+      <c r="E59" s="17">
         <f>-$B$3*EXP(-A59*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T59" s="13">
+      <c r="T59" s="15">
         <f>T58+$Z$2</f>
         <v/>
       </c>
-      <c r="U59" s="14">
+      <c r="U59" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T59*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V59" s="14">
+      <c r="V59" s="16">
         <f>$U$3*EXP(-T59*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W59" s="15">
+      <c r="W59" s="17">
         <f>($U$3/$U$5)*EXP(-T59*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X59" s="15">
+      <c r="X59" s="17">
         <f>-$U$3*EXP(-T59*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO59" s="13">
+      <c r="AO59" s="15">
         <f>AO58+$AU$2</f>
         <v/>
       </c>
-      <c r="AP59" s="14">
+      <c r="AP59" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO59*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ59" s="14">
+      <c r="AQ59" s="16">
         <f>$AP$3*EXP(-AO59*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR59" s="15">
+      <c r="AR59" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO59*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS59" s="15">
+      <c r="AS59" s="17">
         <f>-$AP$3*EXP(-AO59*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="13">
+      <c r="A60" s="15">
         <f>A59+$G$2</f>
         <v/>
       </c>
-      <c r="B60" s="14">
+      <c r="B60" s="16">
         <f>($B$3/$B$4)*(1-EXP(-A60*$B$4/$B$6))</f>
         <v/>
       </c>
-      <c r="C60" s="14">
+      <c r="C60" s="16">
         <f>$B$3*EXP(-A60*$B$4/$B$6)</f>
         <v/>
       </c>
-      <c r="D60" s="15">
+      <c r="D60" s="17">
         <f>($B$3/$B$5)*EXP(-A60*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="E60" s="15">
+      <c r="E60" s="17">
         <f>-$B$3*EXP(-A60*$B$5/$B$6)</f>
         <v/>
       </c>
-      <c r="T60" s="13">
+      <c r="T60" s="15">
         <f>T59+$Z$2</f>
         <v/>
       </c>
-      <c r="U60" s="14">
+      <c r="U60" s="16">
         <f>($U$3/$U$4)*(1-EXP(-T60*$U$4/$U$6))</f>
         <v/>
       </c>
-      <c r="V60" s="14">
+      <c r="V60" s="16">
         <f>$U$3*EXP(-T60*$U$4/$U$6)</f>
         <v/>
       </c>
-      <c r="W60" s="15">
+      <c r="W60" s="17">
         <f>($U$3/$U$5)*EXP(-T60*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="X60" s="15">
+      <c r="X60" s="17">
         <f>-$U$3*EXP(-T60*$U$5/$U$6)</f>
         <v/>
       </c>
-      <c r="AO60" s="13">
+      <c r="AO60" s="15">
         <f>AO59+$AU$2</f>
         <v/>
       </c>
-      <c r="AP60" s="14">
+      <c r="AP60" s="16">
         <f>($AP$3/$AP$4)*(1-EXP(-AO60*$AP$4/$AP$6))</f>
         <v/>
       </c>
-      <c r="AQ60" s="14">
+      <c r="AQ60" s="16">
         <f>$AP$3*EXP(-AO60*$AP$4/$AP$6)</f>
         <v/>
       </c>
-      <c r="AR60" s="15">
+      <c r="AR60" s="17">
         <f>($AP$3/$AP$5)*EXP(-AO60*$AP$5/$AP$6)</f>
         <v/>
       </c>
-      <c r="AS60" s="15">
+      <c r="AS60" s="17">
         <f>-$AP$3*EXP(-AO60*$AP$5/$AP$6)</f>
         <v/>
       </c>
     </row>
+    <row r="68">
+      <c r="I68" s="18" t="inlineStr">
+        <is>
+          <t>Разряд для графика (10τр)</t>
+        </is>
+      </c>
+      <c r="AB68" s="18" t="inlineStr">
+        <is>
+          <t>Разряд для графика (10τр)</t>
+        </is>
+      </c>
+      <c r="AW68" s="18" t="inlineStr">
+        <is>
+          <t>Разряд для графика (10τр)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="I69" s="1" t="inlineStr">
+        <is>
+          <t>tр, c</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>Iр, А</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Uр, В</t>
+        </is>
+      </c>
+      <c r="AB69" s="1" t="inlineStr">
+        <is>
+          <t>tр, c</t>
+        </is>
+      </c>
+      <c r="AC69" s="3" t="inlineStr">
+        <is>
+          <t>Iр, А</t>
+        </is>
+      </c>
+      <c r="AD69" s="5" t="inlineStr">
+        <is>
+          <t>Uр, В</t>
+        </is>
+      </c>
+      <c r="AW69" s="1" t="inlineStr">
+        <is>
+          <t>tр, c</t>
+        </is>
+      </c>
+      <c r="AX69" s="3" t="inlineStr">
+        <is>
+          <t>Iр, А</t>
+        </is>
+      </c>
+      <c r="AY69" s="5" t="inlineStr">
+        <is>
+          <t>Uр, В</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="I70" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="17">
+        <f>($B$3/$B$5)*EXP(-I70*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K70" s="17">
+        <f>-$B$3*EXP(-I70*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB70" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="17">
+        <f>($U$3/$U$5)*EXP(-AB70*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD70" s="17">
+        <f>-$U$3*EXP(-AB70*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW70" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX70" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW70*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY70" s="17">
+        <f>-$AP$3*EXP(-AW70*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="I71" s="19">
+        <f>I70+$H$2</f>
+        <v/>
+      </c>
+      <c r="J71" s="17">
+        <f>($B$3/$B$5)*EXP(-I71*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K71" s="17">
+        <f>-$B$3*EXP(-I71*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB71" s="19">
+        <f>AB70+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC71" s="17">
+        <f>($U$3/$U$5)*EXP(-AB71*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD71" s="17">
+        <f>-$U$3*EXP(-AB71*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW71" s="19">
+        <f>AW70+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX71" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW71*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY71" s="17">
+        <f>-$AP$3*EXP(-AW71*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="I72" s="19">
+        <f>I71+$H$2</f>
+        <v/>
+      </c>
+      <c r="J72" s="17">
+        <f>($B$3/$B$5)*EXP(-I72*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K72" s="17">
+        <f>-$B$3*EXP(-I72*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB72" s="19">
+        <f>AB71+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC72" s="17">
+        <f>($U$3/$U$5)*EXP(-AB72*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD72" s="17">
+        <f>-$U$3*EXP(-AB72*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW72" s="19">
+        <f>AW71+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX72" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW72*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY72" s="17">
+        <f>-$AP$3*EXP(-AW72*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="I73" s="19">
+        <f>I72+$H$2</f>
+        <v/>
+      </c>
+      <c r="J73" s="17">
+        <f>($B$3/$B$5)*EXP(-I73*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K73" s="17">
+        <f>-$B$3*EXP(-I73*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB73" s="19">
+        <f>AB72+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC73" s="17">
+        <f>($U$3/$U$5)*EXP(-AB73*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD73" s="17">
+        <f>-$U$3*EXP(-AB73*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW73" s="19">
+        <f>AW72+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX73" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW73*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY73" s="17">
+        <f>-$AP$3*EXP(-AW73*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="I74" s="19">
+        <f>I73+$H$2</f>
+        <v/>
+      </c>
+      <c r="J74" s="17">
+        <f>($B$3/$B$5)*EXP(-I74*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K74" s="17">
+        <f>-$B$3*EXP(-I74*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB74" s="19">
+        <f>AB73+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC74" s="17">
+        <f>($U$3/$U$5)*EXP(-AB74*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD74" s="17">
+        <f>-$U$3*EXP(-AB74*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW74" s="19">
+        <f>AW73+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX74" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW74*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY74" s="17">
+        <f>-$AP$3*EXP(-AW74*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="I75" s="19">
+        <f>I74+$H$2</f>
+        <v/>
+      </c>
+      <c r="J75" s="17">
+        <f>($B$3/$B$5)*EXP(-I75*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K75" s="17">
+        <f>-$B$3*EXP(-I75*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB75" s="19">
+        <f>AB74+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC75" s="17">
+        <f>($U$3/$U$5)*EXP(-AB75*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD75" s="17">
+        <f>-$U$3*EXP(-AB75*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW75" s="19">
+        <f>AW74+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX75" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW75*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY75" s="17">
+        <f>-$AP$3*EXP(-AW75*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="I76" s="19">
+        <f>I75+$H$2</f>
+        <v/>
+      </c>
+      <c r="J76" s="17">
+        <f>($B$3/$B$5)*EXP(-I76*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K76" s="17">
+        <f>-$B$3*EXP(-I76*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB76" s="19">
+        <f>AB75+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC76" s="17">
+        <f>($U$3/$U$5)*EXP(-AB76*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD76" s="17">
+        <f>-$U$3*EXP(-AB76*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW76" s="19">
+        <f>AW75+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX76" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW76*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY76" s="17">
+        <f>-$AP$3*EXP(-AW76*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="I77" s="19">
+        <f>I76+$H$2</f>
+        <v/>
+      </c>
+      <c r="J77" s="17">
+        <f>($B$3/$B$5)*EXP(-I77*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K77" s="17">
+        <f>-$B$3*EXP(-I77*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB77" s="19">
+        <f>AB76+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC77" s="17">
+        <f>($U$3/$U$5)*EXP(-AB77*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD77" s="17">
+        <f>-$U$3*EXP(-AB77*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW77" s="19">
+        <f>AW76+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX77" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW77*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY77" s="17">
+        <f>-$AP$3*EXP(-AW77*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="I78" s="19">
+        <f>I77+$H$2</f>
+        <v/>
+      </c>
+      <c r="J78" s="17">
+        <f>($B$3/$B$5)*EXP(-I78*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K78" s="17">
+        <f>-$B$3*EXP(-I78*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB78" s="19">
+        <f>AB77+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC78" s="17">
+        <f>($U$3/$U$5)*EXP(-AB78*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD78" s="17">
+        <f>-$U$3*EXP(-AB78*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW78" s="19">
+        <f>AW77+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX78" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW78*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY78" s="17">
+        <f>-$AP$3*EXP(-AW78*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="I79" s="19">
+        <f>I78+$H$2</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>($B$3/$B$5)*EXP(-I79*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>-$B$3*EXP(-I79*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB79" s="19">
+        <f>AB78+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC79" s="17">
+        <f>($U$3/$U$5)*EXP(-AB79*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD79" s="17">
+        <f>-$U$3*EXP(-AB79*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW79" s="19">
+        <f>AW78+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX79" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW79*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY79" s="17">
+        <f>-$AP$3*EXP(-AW79*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="I80" s="19">
+        <f>I79+$H$2</f>
+        <v/>
+      </c>
+      <c r="J80" s="17">
+        <f>($B$3/$B$5)*EXP(-I80*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K80" s="17">
+        <f>-$B$3*EXP(-I80*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB80" s="19">
+        <f>AB79+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC80" s="17">
+        <f>($U$3/$U$5)*EXP(-AB80*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD80" s="17">
+        <f>-$U$3*EXP(-AB80*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW80" s="19">
+        <f>AW79+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX80" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW80*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY80" s="17">
+        <f>-$AP$3*EXP(-AW80*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="I81" s="19">
+        <f>I80+$H$2</f>
+        <v/>
+      </c>
+      <c r="J81" s="17">
+        <f>($B$3/$B$5)*EXP(-I81*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K81" s="17">
+        <f>-$B$3*EXP(-I81*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB81" s="19">
+        <f>AB80+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC81" s="17">
+        <f>($U$3/$U$5)*EXP(-AB81*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD81" s="17">
+        <f>-$U$3*EXP(-AB81*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW81" s="19">
+        <f>AW80+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX81" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW81*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY81" s="17">
+        <f>-$AP$3*EXP(-AW81*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="I82" s="19">
+        <f>I81+$H$2</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>($B$3/$B$5)*EXP(-I82*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>-$B$3*EXP(-I82*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB82" s="19">
+        <f>AB81+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC82" s="17">
+        <f>($U$3/$U$5)*EXP(-AB82*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD82" s="17">
+        <f>-$U$3*EXP(-AB82*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW82" s="19">
+        <f>AW81+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX82" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW82*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY82" s="17">
+        <f>-$AP$3*EXP(-AW82*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="I83" s="19">
+        <f>I82+$H$2</f>
+        <v/>
+      </c>
+      <c r="J83" s="17">
+        <f>($B$3/$B$5)*EXP(-I83*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K83" s="17">
+        <f>-$B$3*EXP(-I83*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB83" s="19">
+        <f>AB82+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC83" s="17">
+        <f>($U$3/$U$5)*EXP(-AB83*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD83" s="17">
+        <f>-$U$3*EXP(-AB83*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW83" s="19">
+        <f>AW82+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX83" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW83*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY83" s="17">
+        <f>-$AP$3*EXP(-AW83*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="I84" s="19">
+        <f>I83+$H$2</f>
+        <v/>
+      </c>
+      <c r="J84" s="17">
+        <f>($B$3/$B$5)*EXP(-I84*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K84" s="17">
+        <f>-$B$3*EXP(-I84*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB84" s="19">
+        <f>AB83+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC84" s="17">
+        <f>($U$3/$U$5)*EXP(-AB84*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD84" s="17">
+        <f>-$U$3*EXP(-AB84*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW84" s="19">
+        <f>AW83+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX84" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW84*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY84" s="17">
+        <f>-$AP$3*EXP(-AW84*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="I85" s="19">
+        <f>I84+$H$2</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>($B$3/$B$5)*EXP(-I85*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>-$B$3*EXP(-I85*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB85" s="19">
+        <f>AB84+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC85" s="17">
+        <f>($U$3/$U$5)*EXP(-AB85*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD85" s="17">
+        <f>-$U$3*EXP(-AB85*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW85" s="19">
+        <f>AW84+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX85" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW85*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY85" s="17">
+        <f>-$AP$3*EXP(-AW85*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="I86" s="19">
+        <f>I85+$H$2</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>($B$3/$B$5)*EXP(-I86*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>-$B$3*EXP(-I86*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB86" s="19">
+        <f>AB85+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC86" s="17">
+        <f>($U$3/$U$5)*EXP(-AB86*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD86" s="17">
+        <f>-$U$3*EXP(-AB86*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW86" s="19">
+        <f>AW85+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX86" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW86*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY86" s="17">
+        <f>-$AP$3*EXP(-AW86*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="I87" s="19">
+        <f>I86+$H$2</f>
+        <v/>
+      </c>
+      <c r="J87" s="17">
+        <f>($B$3/$B$5)*EXP(-I87*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K87" s="17">
+        <f>-$B$3*EXP(-I87*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB87" s="19">
+        <f>AB86+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC87" s="17">
+        <f>($U$3/$U$5)*EXP(-AB87*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD87" s="17">
+        <f>-$U$3*EXP(-AB87*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW87" s="19">
+        <f>AW86+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX87" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW87*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY87" s="17">
+        <f>-$AP$3*EXP(-AW87*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="I88" s="19">
+        <f>I87+$H$2</f>
+        <v/>
+      </c>
+      <c r="J88" s="17">
+        <f>($B$3/$B$5)*EXP(-I88*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K88" s="17">
+        <f>-$B$3*EXP(-I88*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB88" s="19">
+        <f>AB87+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC88" s="17">
+        <f>($U$3/$U$5)*EXP(-AB88*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD88" s="17">
+        <f>-$U$3*EXP(-AB88*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW88" s="19">
+        <f>AW87+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX88" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW88*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY88" s="17">
+        <f>-$AP$3*EXP(-AW88*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="I89" s="19">
+        <f>I88+$H$2</f>
+        <v/>
+      </c>
+      <c r="J89" s="17">
+        <f>($B$3/$B$5)*EXP(-I89*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K89" s="17">
+        <f>-$B$3*EXP(-I89*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB89" s="19">
+        <f>AB88+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC89" s="17">
+        <f>($U$3/$U$5)*EXP(-AB89*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD89" s="17">
+        <f>-$U$3*EXP(-AB89*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW89" s="19">
+        <f>AW88+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX89" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW89*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY89" s="17">
+        <f>-$AP$3*EXP(-AW89*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="I90" s="19">
+        <f>I89+$H$2</f>
+        <v/>
+      </c>
+      <c r="J90" s="17">
+        <f>($B$3/$B$5)*EXP(-I90*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K90" s="17">
+        <f>-$B$3*EXP(-I90*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB90" s="19">
+        <f>AB89+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC90" s="17">
+        <f>($U$3/$U$5)*EXP(-AB90*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD90" s="17">
+        <f>-$U$3*EXP(-AB90*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW90" s="19">
+        <f>AW89+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX90" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW90*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY90" s="17">
+        <f>-$AP$3*EXP(-AW90*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="I91" s="19">
+        <f>I90+$H$2</f>
+        <v/>
+      </c>
+      <c r="J91" s="17">
+        <f>($B$3/$B$5)*EXP(-I91*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K91" s="17">
+        <f>-$B$3*EXP(-I91*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB91" s="19">
+        <f>AB90+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC91" s="17">
+        <f>($U$3/$U$5)*EXP(-AB91*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD91" s="17">
+        <f>-$U$3*EXP(-AB91*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW91" s="19">
+        <f>AW90+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX91" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW91*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY91" s="17">
+        <f>-$AP$3*EXP(-AW91*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="I92" s="19">
+        <f>I91+$H$2</f>
+        <v/>
+      </c>
+      <c r="J92" s="17">
+        <f>($B$3/$B$5)*EXP(-I92*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K92" s="17">
+        <f>-$B$3*EXP(-I92*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB92" s="19">
+        <f>AB91+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC92" s="17">
+        <f>($U$3/$U$5)*EXP(-AB92*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD92" s="17">
+        <f>-$U$3*EXP(-AB92*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW92" s="19">
+        <f>AW91+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX92" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW92*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY92" s="17">
+        <f>-$AP$3*EXP(-AW92*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="I93" s="19">
+        <f>I92+$H$2</f>
+        <v/>
+      </c>
+      <c r="J93" s="17">
+        <f>($B$3/$B$5)*EXP(-I93*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K93" s="17">
+        <f>-$B$3*EXP(-I93*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB93" s="19">
+        <f>AB92+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC93" s="17">
+        <f>($U$3/$U$5)*EXP(-AB93*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD93" s="17">
+        <f>-$U$3*EXP(-AB93*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW93" s="19">
+        <f>AW92+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX93" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW93*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY93" s="17">
+        <f>-$AP$3*EXP(-AW93*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="I94" s="19">
+        <f>I93+$H$2</f>
+        <v/>
+      </c>
+      <c r="J94" s="17">
+        <f>($B$3/$B$5)*EXP(-I94*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K94" s="17">
+        <f>-$B$3*EXP(-I94*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB94" s="19">
+        <f>AB93+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC94" s="17">
+        <f>($U$3/$U$5)*EXP(-AB94*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD94" s="17">
+        <f>-$U$3*EXP(-AB94*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW94" s="19">
+        <f>AW93+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX94" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW94*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY94" s="17">
+        <f>-$AP$3*EXP(-AW94*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="I95" s="19">
+        <f>I94+$H$2</f>
+        <v/>
+      </c>
+      <c r="J95" s="17">
+        <f>($B$3/$B$5)*EXP(-I95*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K95" s="17">
+        <f>-$B$3*EXP(-I95*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB95" s="19">
+        <f>AB94+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC95" s="17">
+        <f>($U$3/$U$5)*EXP(-AB95*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD95" s="17">
+        <f>-$U$3*EXP(-AB95*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW95" s="19">
+        <f>AW94+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX95" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW95*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY95" s="17">
+        <f>-$AP$3*EXP(-AW95*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="I96" s="19">
+        <f>I95+$H$2</f>
+        <v/>
+      </c>
+      <c r="J96" s="17">
+        <f>($B$3/$B$5)*EXP(-I96*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K96" s="17">
+        <f>-$B$3*EXP(-I96*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB96" s="19">
+        <f>AB95+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC96" s="17">
+        <f>($U$3/$U$5)*EXP(-AB96*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD96" s="17">
+        <f>-$U$3*EXP(-AB96*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW96" s="19">
+        <f>AW95+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX96" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW96*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY96" s="17">
+        <f>-$AP$3*EXP(-AW96*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="I97" s="19">
+        <f>I96+$H$2</f>
+        <v/>
+      </c>
+      <c r="J97" s="17">
+        <f>($B$3/$B$5)*EXP(-I97*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K97" s="17">
+        <f>-$B$3*EXP(-I97*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB97" s="19">
+        <f>AB96+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC97" s="17">
+        <f>($U$3/$U$5)*EXP(-AB97*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD97" s="17">
+        <f>-$U$3*EXP(-AB97*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW97" s="19">
+        <f>AW96+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX97" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW97*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY97" s="17">
+        <f>-$AP$3*EXP(-AW97*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="I98" s="19">
+        <f>I97+$H$2</f>
+        <v/>
+      </c>
+      <c r="J98" s="17">
+        <f>($B$3/$B$5)*EXP(-I98*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K98" s="17">
+        <f>-$B$3*EXP(-I98*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB98" s="19">
+        <f>AB97+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC98" s="17">
+        <f>($U$3/$U$5)*EXP(-AB98*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD98" s="17">
+        <f>-$U$3*EXP(-AB98*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW98" s="19">
+        <f>AW97+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX98" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW98*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY98" s="17">
+        <f>-$AP$3*EXP(-AW98*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="I99" s="19">
+        <f>I98+$H$2</f>
+        <v/>
+      </c>
+      <c r="J99" s="17">
+        <f>($B$3/$B$5)*EXP(-I99*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K99" s="17">
+        <f>-$B$3*EXP(-I99*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB99" s="19">
+        <f>AB98+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC99" s="17">
+        <f>($U$3/$U$5)*EXP(-AB99*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD99" s="17">
+        <f>-$U$3*EXP(-AB99*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW99" s="19">
+        <f>AW98+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX99" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW99*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY99" s="17">
+        <f>-$AP$3*EXP(-AW99*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
     <row r="100">
-      <c r="A100" s="16" t="inlineStr">
+      <c r="I100" s="19">
+        <f>I99+$H$2</f>
+        <v/>
+      </c>
+      <c r="J100" s="17">
+        <f>($B$3/$B$5)*EXP(-I100*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K100" s="17">
+        <f>-$B$3*EXP(-I100*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB100" s="19">
+        <f>AB99+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC100" s="17">
+        <f>($U$3/$U$5)*EXP(-AB100*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD100" s="17">
+        <f>-$U$3*EXP(-AB100*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW100" s="19">
+        <f>AW99+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX100" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW100*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY100" s="17">
+        <f>-$AP$3*EXP(-AW100*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="I101" s="19">
+        <f>I100+$H$2</f>
+        <v/>
+      </c>
+      <c r="J101" s="17">
+        <f>($B$3/$B$5)*EXP(-I101*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K101" s="17">
+        <f>-$B$3*EXP(-I101*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB101" s="19">
+        <f>AB100+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC101" s="17">
+        <f>($U$3/$U$5)*EXP(-AB101*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD101" s="17">
+        <f>-$U$3*EXP(-AB101*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW101" s="19">
+        <f>AW100+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX101" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW101*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY101" s="17">
+        <f>-$AP$3*EXP(-AW101*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="I102" s="19">
+        <f>I101+$H$2</f>
+        <v/>
+      </c>
+      <c r="J102" s="17">
+        <f>($B$3/$B$5)*EXP(-I102*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>-$B$3*EXP(-I102*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB102" s="19">
+        <f>AB101+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC102" s="17">
+        <f>($U$3/$U$5)*EXP(-AB102*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD102" s="17">
+        <f>-$U$3*EXP(-AB102*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW102" s="19">
+        <f>AW101+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX102" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW102*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY102" s="17">
+        <f>-$AP$3*EXP(-AW102*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="I103" s="19">
+        <f>I102+$H$2</f>
+        <v/>
+      </c>
+      <c r="J103" s="17">
+        <f>($B$3/$B$5)*EXP(-I103*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K103" s="17">
+        <f>-$B$3*EXP(-I103*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB103" s="19">
+        <f>AB102+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC103" s="17">
+        <f>($U$3/$U$5)*EXP(-AB103*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD103" s="17">
+        <f>-$U$3*EXP(-AB103*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW103" s="19">
+        <f>AW102+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX103" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW103*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY103" s="17">
+        <f>-$AP$3*EXP(-AW103*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="I104" s="19">
+        <f>I103+$H$2</f>
+        <v/>
+      </c>
+      <c r="J104" s="17">
+        <f>($B$3/$B$5)*EXP(-I104*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K104" s="17">
+        <f>-$B$3*EXP(-I104*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB104" s="19">
+        <f>AB103+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC104" s="17">
+        <f>($U$3/$U$5)*EXP(-AB104*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD104" s="17">
+        <f>-$U$3*EXP(-AB104*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW104" s="19">
+        <f>AW103+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX104" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW104*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY104" s="17">
+        <f>-$AP$3*EXP(-AW104*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="I105" s="19">
+        <f>I104+$H$2</f>
+        <v/>
+      </c>
+      <c r="J105" s="17">
+        <f>($B$3/$B$5)*EXP(-I105*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K105" s="17">
+        <f>-$B$3*EXP(-I105*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB105" s="19">
+        <f>AB104+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC105" s="17">
+        <f>($U$3/$U$5)*EXP(-AB105*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD105" s="17">
+        <f>-$U$3*EXP(-AB105*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW105" s="19">
+        <f>AW104+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX105" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW105*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY105" s="17">
+        <f>-$AP$3*EXP(-AW105*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="I106" s="19">
+        <f>I105+$H$2</f>
+        <v/>
+      </c>
+      <c r="J106" s="17">
+        <f>($B$3/$B$5)*EXP(-I106*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K106" s="17">
+        <f>-$B$3*EXP(-I106*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB106" s="19">
+        <f>AB105+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC106" s="17">
+        <f>($U$3/$U$5)*EXP(-AB106*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD106" s="17">
+        <f>-$U$3*EXP(-AB106*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW106" s="19">
+        <f>AW105+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX106" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW106*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY106" s="17">
+        <f>-$AP$3*EXP(-AW106*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="I107" s="19">
+        <f>I106+$H$2</f>
+        <v/>
+      </c>
+      <c r="J107" s="17">
+        <f>($B$3/$B$5)*EXP(-I107*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K107" s="17">
+        <f>-$B$3*EXP(-I107*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB107" s="19">
+        <f>AB106+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC107" s="17">
+        <f>($U$3/$U$5)*EXP(-AB107*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD107" s="17">
+        <f>-$U$3*EXP(-AB107*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW107" s="19">
+        <f>AW106+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX107" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW107*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY107" s="17">
+        <f>-$AP$3*EXP(-AW107*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="I108" s="19">
+        <f>I107+$H$2</f>
+        <v/>
+      </c>
+      <c r="J108" s="17">
+        <f>($B$3/$B$5)*EXP(-I108*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K108" s="17">
+        <f>-$B$3*EXP(-I108*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB108" s="19">
+        <f>AB107+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC108" s="17">
+        <f>($U$3/$U$5)*EXP(-AB108*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD108" s="17">
+        <f>-$U$3*EXP(-AB108*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW108" s="19">
+        <f>AW107+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX108" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW108*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY108" s="17">
+        <f>-$AP$3*EXP(-AW108*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="I109" s="19">
+        <f>I108+$H$2</f>
+        <v/>
+      </c>
+      <c r="J109" s="17">
+        <f>($B$3/$B$5)*EXP(-I109*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K109" s="17">
+        <f>-$B$3*EXP(-I109*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB109" s="19">
+        <f>AB108+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC109" s="17">
+        <f>($U$3/$U$5)*EXP(-AB109*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD109" s="17">
+        <f>-$U$3*EXP(-AB109*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW109" s="19">
+        <f>AW108+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX109" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW109*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY109" s="17">
+        <f>-$AP$3*EXP(-AW109*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="I110" s="19">
+        <f>I109+$H$2</f>
+        <v/>
+      </c>
+      <c r="J110" s="17">
+        <f>($B$3/$B$5)*EXP(-I110*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K110" s="17">
+        <f>-$B$3*EXP(-I110*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB110" s="19">
+        <f>AB109+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC110" s="17">
+        <f>($U$3/$U$5)*EXP(-AB110*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD110" s="17">
+        <f>-$U$3*EXP(-AB110*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW110" s="19">
+        <f>AW109+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX110" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW110*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY110" s="17">
+        <f>-$AP$3*EXP(-AW110*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="I111" s="19">
+        <f>I110+$H$2</f>
+        <v/>
+      </c>
+      <c r="J111" s="17">
+        <f>($B$3/$B$5)*EXP(-I111*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>-$B$3*EXP(-I111*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB111" s="19">
+        <f>AB110+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC111" s="17">
+        <f>($U$3/$U$5)*EXP(-AB111*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD111" s="17">
+        <f>-$U$3*EXP(-AB111*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW111" s="19">
+        <f>AW110+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX111" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW111*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY111" s="17">
+        <f>-$AP$3*EXP(-AW111*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="I112" s="19">
+        <f>I111+$H$2</f>
+        <v/>
+      </c>
+      <c r="J112" s="17">
+        <f>($B$3/$B$5)*EXP(-I112*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K112" s="17">
+        <f>-$B$3*EXP(-I112*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB112" s="19">
+        <f>AB111+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC112" s="17">
+        <f>($U$3/$U$5)*EXP(-AB112*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD112" s="17">
+        <f>-$U$3*EXP(-AB112*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW112" s="19">
+        <f>AW111+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX112" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW112*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY112" s="17">
+        <f>-$AP$3*EXP(-AW112*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="I113" s="19">
+        <f>I112+$H$2</f>
+        <v/>
+      </c>
+      <c r="J113" s="17">
+        <f>($B$3/$B$5)*EXP(-I113*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>-$B$3*EXP(-I113*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB113" s="19">
+        <f>AB112+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC113" s="17">
+        <f>($U$3/$U$5)*EXP(-AB113*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD113" s="17">
+        <f>-$U$3*EXP(-AB113*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW113" s="19">
+        <f>AW112+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX113" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW113*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY113" s="17">
+        <f>-$AP$3*EXP(-AW113*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="I114" s="19">
+        <f>I113+$H$2</f>
+        <v/>
+      </c>
+      <c r="J114" s="17">
+        <f>($B$3/$B$5)*EXP(-I114*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K114" s="17">
+        <f>-$B$3*EXP(-I114*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB114" s="19">
+        <f>AB113+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC114" s="17">
+        <f>($U$3/$U$5)*EXP(-AB114*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD114" s="17">
+        <f>-$U$3*EXP(-AB114*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW114" s="19">
+        <f>AW113+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX114" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW114*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY114" s="17">
+        <f>-$AP$3*EXP(-AW114*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="I115" s="19">
+        <f>I114+$H$2</f>
+        <v/>
+      </c>
+      <c r="J115" s="17">
+        <f>($B$3/$B$5)*EXP(-I115*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K115" s="17">
+        <f>-$B$3*EXP(-I115*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB115" s="19">
+        <f>AB114+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC115" s="17">
+        <f>($U$3/$U$5)*EXP(-AB115*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD115" s="17">
+        <f>-$U$3*EXP(-AB115*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW115" s="19">
+        <f>AW114+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX115" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW115*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY115" s="17">
+        <f>-$AP$3*EXP(-AW115*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="I116" s="19">
+        <f>I115+$H$2</f>
+        <v/>
+      </c>
+      <c r="J116" s="17">
+        <f>($B$3/$B$5)*EXP(-I116*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K116" s="17">
+        <f>-$B$3*EXP(-I116*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB116" s="19">
+        <f>AB115+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC116" s="17">
+        <f>($U$3/$U$5)*EXP(-AB116*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD116" s="17">
+        <f>-$U$3*EXP(-AB116*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW116" s="19">
+        <f>AW115+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX116" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW116*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY116" s="17">
+        <f>-$AP$3*EXP(-AW116*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="I117" s="19">
+        <f>I116+$H$2</f>
+        <v/>
+      </c>
+      <c r="J117" s="17">
+        <f>($B$3/$B$5)*EXP(-I117*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K117" s="17">
+        <f>-$B$3*EXP(-I117*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB117" s="19">
+        <f>AB116+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC117" s="17">
+        <f>($U$3/$U$5)*EXP(-AB117*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD117" s="17">
+        <f>-$U$3*EXP(-AB117*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW117" s="19">
+        <f>AW116+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX117" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW117*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY117" s="17">
+        <f>-$AP$3*EXP(-AW117*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="I118" s="19">
+        <f>I117+$H$2</f>
+        <v/>
+      </c>
+      <c r="J118" s="17">
+        <f>($B$3/$B$5)*EXP(-I118*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K118" s="17">
+        <f>-$B$3*EXP(-I118*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB118" s="19">
+        <f>AB117+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC118" s="17">
+        <f>($U$3/$U$5)*EXP(-AB118*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD118" s="17">
+        <f>-$U$3*EXP(-AB118*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW118" s="19">
+        <f>AW117+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX118" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW118*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY118" s="17">
+        <f>-$AP$3*EXP(-AW118*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="I119" s="19">
+        <f>I118+$H$2</f>
+        <v/>
+      </c>
+      <c r="J119" s="17">
+        <f>($B$3/$B$5)*EXP(-I119*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K119" s="17">
+        <f>-$B$3*EXP(-I119*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB119" s="19">
+        <f>AB118+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC119" s="17">
+        <f>($U$3/$U$5)*EXP(-AB119*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD119" s="17">
+        <f>-$U$3*EXP(-AB119*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW119" s="19">
+        <f>AW118+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX119" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW119*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY119" s="17">
+        <f>-$AP$3*EXP(-AW119*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="I120" s="19">
+        <f>I119+$H$2</f>
+        <v/>
+      </c>
+      <c r="J120" s="17">
+        <f>($B$3/$B$5)*EXP(-I120*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="K120" s="17">
+        <f>-$B$3*EXP(-I120*$B$5/$B$6)</f>
+        <v/>
+      </c>
+      <c r="AB120" s="19">
+        <f>AB119+$AA$2</f>
+        <v/>
+      </c>
+      <c r="AC120" s="17">
+        <f>($U$3/$U$5)*EXP(-AB120*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AD120" s="17">
+        <f>-$U$3*EXP(-AB120*$U$5/$U$6)</f>
+        <v/>
+      </c>
+      <c r="AW120" s="19">
+        <f>AW119+$AV$2</f>
+        <v/>
+      </c>
+      <c r="AX120" s="17">
+        <f>($AP$3/$AP$5)*EXP(-AW120*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+      <c r="AY120" s="17">
+        <f>-$AP$3*EXP(-AW120*$AP$5/$AP$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="inlineStr">
         <is>
           <t>Формулы (совпадают с графиками)</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Iз(t) = (E/r)*(1-EXP(-t*r/L))</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>Uз(t) = E*EXP(-t*r/L)     — напряжение на катушке при заряде</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>Iр(t) = (E/R)*EXP(-t*R/L)</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>Uр(t) = -E*EXP(-t*R/L)    — напряжение на катушке при разряде</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>L задаётся как POWER(10,-4)*9  (= 9·10⁻⁴ Гн). В исходной работе было *15; по заданию 15 заменено на 9 в L и r.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>Автор расчёта: Молчанов Даниил Александрович</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Графики разряда берут tр, Iр, Uр из строк 70–120 (масштаб 10τр), иначе на шаге заряда кривая разряда не видна.</t>
         </is>
       </c>
     </row>

--- a/Daniil/задание 1.xlsx
+++ b/Daniil/задание 1.xlsx
@@ -1204,154 +1204,154 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.5e-06</c:v>
+                  <c:v>8.57142857142857e-07</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3e-06</c:v>
+                  <c:v>1.71428571428571e-06</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.5e-06</c:v>
+                  <c:v>2.57142857142857e-06</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>3.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.28571428571429e-06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>6e-06</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9e-06</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.05e-05</c:v>
-                </c:pt>
                 <c:pt idx="8">
+                  <c:v>6.85714285714286e-06</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.57142857142857e-06</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.02857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.11428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>1.2e-05</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.35e-05</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.5e-05</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.65e-05</c:v>
-                </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
+                  <c:v>1.28571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.37142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.45714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.54285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.62857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.71428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>1.8e-05</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.95e-05</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2.1e-05</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2.25e-05</c:v>
-                </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="22">
+                  <c:v>1.88571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.97142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.05714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.14285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.22857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.31428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>2.4e-05</c:v>
                 </c:pt>
-                <c:pt idx="17">
-                  <c:v>2.55e-05</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2.7e-05</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2.85e-05</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="29">
+                  <c:v>2.48571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.57142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.65714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.74285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.82857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.91428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>3e-05</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>3.15e-05</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>3.3e-05</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>3.45e-05</c:v>
-                </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="36">
+                  <c:v>3.08571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.17142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.25714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.34285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.42857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.51428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>3.6e-05</c:v>
                 </c:pt>
-                <c:pt idx="25">
-                  <c:v>3.75e-05</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>3.9e-05</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>4.05e-05</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="43">
+                  <c:v>3.68571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.77142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.85714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3.94285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.02857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4.11428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="49">
                   <c:v>4.2e-05</c:v>
                 </c:pt>
-                <c:pt idx="29">
-                  <c:v>4.35e-05</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>4.5e-05</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>4.65e-05</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>4.8e-05</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>4.95e-05</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>5.1e-05</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>5.25e-05</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>5.4e-05</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>5.55e-05</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>5.7e-05</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>5.85e-05</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>6e-05</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>6.15e-05</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>6.3e-05</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>6.45e-05</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>6.6e-05</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>6.75e-05</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>6.9e-05</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>7.05e-05</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>7.2e-05</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>7.35e-05</c:v>
-                </c:pt>
                 <c:pt idx="50">
-                  <c:v>7.5e-05</c:v>
+                  <c:v>4.28571428571429e-05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1363,157 +1363,157 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>0.0666666666666667</c:v>
+                  <c:v>0.888888888888889</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0545820502051988</c:v>
+                  <c:v>0.72776066940265</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0446880030690426</c:v>
+                  <c:v>0.595840040920568</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0365874424062684</c:v>
+                  <c:v>0.487832565416912</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0299552642744814</c:v>
+                  <c:v>0.399403523659752</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0245252960780962</c:v>
+                  <c:v>0.327003947707949</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0200796141274801</c:v>
+                  <c:v>0.267728188366402</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0164397975961071</c:v>
+                  <c:v>0.219197301281428</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0134597678663104</c:v>
+                  <c:v>0.179463571550805</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0110199258814391</c:v>
+                  <c:v>0.146932345085855</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.00902235221577418</c:v>
+                  <c:v>0.120298029543656</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.00738687722415559</c:v>
+                  <c:v>0.0984916963220746</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.0060478635526275</c:v>
+                  <c:v>0.0806381807017</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.00495157188095559</c:v>
+                  <c:v>0.0660209584127412</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.00405400417501453</c:v>
+                  <c:v>0.0540533890001937</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.00331913789119093</c:v>
+                  <c:v>0.0442551718825457</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.00271748026522441</c:v>
+                  <c:v>0.0362330702029922</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.00222488466402174</c:v>
+                  <c:v>0.0296651288536232</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.00182158149648617</c:v>
+                  <c:v>0.0242877532864823</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.00149138479041104</c:v>
+                  <c:v>0.0198851305388139</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.00122104259258228</c:v>
+                  <c:v>0.016280567901097</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.00099970512136518</c:v>
+                  <c:v>0.0133294016182024</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.000818489326871229</c:v>
+                  <c:v>0.0109131910249497</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.000670122382975572</c:v>
+                  <c:v>0.00893496510634096</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.000548649803268002</c:v>
+                  <c:v>0.00731533071024003</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.000449196466605697</c:v>
+                  <c:v>0.0059892862214093</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.000367770961384051</c:v>
+                  <c:v>0.00490361281845402</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.000301105396174177</c:v>
+                  <c:v>0.00401473861565571</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.000246524247765529</c:v>
+                  <c:v>0.00328698997020705</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.000201836983025054</c:v>
+                  <c:v>0.00269115977366739</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.00016525014511109</c:v>
+                  <c:v>0.00220333526814787</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.000135295375753049</c:v>
+                  <c:v>0.00180393834337399</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.000110770484878262</c:v>
+                  <c:v>0.00147693979837683</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>9.06912025031928e-05</c:v>
+                  <c:v>0.0012092160333759</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>7.42516765229869e-05</c:v>
+                  <c:v>0.000990022353639825</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>6.07921310369678e-05</c:v>
+                  <c:v>0.00081056174715957</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4.97723872251119e-05</c:v>
+                  <c:v>0.000663631829668159</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4.07501840753048e-05</c:v>
+                  <c:v>0.000543335787670731</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>3.33634288960407e-05</c:v>
+                  <c:v>0.000444845718613876</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2.73156652653191e-05</c:v>
+                  <c:v>0.000364208870204255</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.23641751935008e-05</c:v>
+                  <c:v>0.000298189002580011</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.83102379981428e-05</c:v>
+                  <c:v>0.000244136506641904</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.49911549452565e-05</c:v>
+                  <c:v>0.000199882065936754</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.22737195778386e-05</c:v>
+                  <c:v>0.000163649594371181</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.00488716730318e-05</c:v>
+                  <c:v>0.000133984955640424</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>8.2273202724453e-06</c:v>
+                  <c:v>0.000109697603632604</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>6.73596012247289e-06</c:v>
+                  <c:v>8.98128016329719e-05</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>5.51493770377548e-06</c:v>
+                  <c:v>7.35325027170064e-05</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>4.51524909939026e-06</c:v>
+                  <c:v>6.02033213252035e-05</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>3.69677329547846e-06</c:v>
+                  <c:v>4.92903106063795e-05</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3.02666198416565e-06</c:v>
+                  <c:v>4.03554931222088e-05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1553,154 +1553,154 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.5e-06</c:v>
+                  <c:v>8.57142857142857e-07</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3e-06</c:v>
+                  <c:v>1.71428571428571e-06</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.5e-06</c:v>
+                  <c:v>2.57142857142857e-06</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>3.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.28571428571429e-06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>6e-06</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9e-06</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.05e-05</c:v>
-                </c:pt>
                 <c:pt idx="8">
+                  <c:v>6.85714285714286e-06</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.57142857142857e-06</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.02857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.11428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>1.2e-05</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.35e-05</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.5e-05</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.65e-05</c:v>
-                </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
+                  <c:v>1.28571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.37142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.45714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.54285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.62857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.71428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>1.8e-05</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.95e-05</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2.1e-05</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2.25e-05</c:v>
-                </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="22">
+                  <c:v>1.88571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.97142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.05714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.14285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.22857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.31428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>2.4e-05</c:v>
                 </c:pt>
-                <c:pt idx="17">
-                  <c:v>2.55e-05</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2.7e-05</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2.85e-05</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="29">
+                  <c:v>2.48571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.57142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.65714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.74285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.82857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.91428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>3e-05</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>3.15e-05</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>3.3e-05</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>3.45e-05</c:v>
-                </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="36">
+                  <c:v>3.08571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.17142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.25714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.34285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.42857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.51428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>3.6e-05</c:v>
                 </c:pt>
-                <c:pt idx="25">
-                  <c:v>3.75e-05</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>3.9e-05</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>4.05e-05</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="43">
+                  <c:v>3.68571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.77142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.85714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3.94285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.02857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4.11428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="49">
                   <c:v>4.2e-05</c:v>
                 </c:pt>
-                <c:pt idx="29">
-                  <c:v>4.35e-05</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>4.5e-05</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>4.65e-05</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>4.8e-05</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>4.95e-05</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>5.1e-05</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>5.25e-05</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>5.4e-05</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>5.55e-05</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>5.7e-05</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>5.85e-05</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>6e-05</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>6.15e-05</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>6.3e-05</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>6.45e-05</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>6.6e-05</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>6.75e-05</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>6.9e-05</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>7.05e-05</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>7.2e-05</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>7.35e-05</c:v>
-                </c:pt>
                 <c:pt idx="50">
-                  <c:v>7.5e-05</c:v>
+                  <c:v>4.28571428571429e-05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1712,157 +1712,157 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>-8</c:v>
+                  <c:v>-186.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-6.54984602462385</c:v>
+                  <c:v>-152.829740574557</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5.36256036828511</c:v>
+                  <c:v>-125.126408593319</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.39049308875221</c:v>
+                  <c:v>-102.444838737552</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-3.59463171293777</c:v>
+                  <c:v>-83.874739968548</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-2.94303552937154</c:v>
+                  <c:v>-68.6708290186692</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-2.40955369529762</c:v>
+                  <c:v>-56.2229195569444</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.97277571153285</c:v>
+                  <c:v>-46.0314332690999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1.61517214395724</c:v>
+                  <c:v>-37.687350025669</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1.32239110577269</c:v>
+                  <c:v>-30.8557924680295</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.0826822658929</c:v>
+                  <c:v>-25.2625862041677</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.886425266898671</c:v>
+                  <c:v>-20.6832562276357</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.7257436263153</c:v>
+                  <c:v>-16.934017947357</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.594188625714671</c:v>
+                  <c:v>-13.8644012666757</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.486480501001744</c:v>
+                  <c:v>-11.3512116900407</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.398296546942911</c:v>
+                  <c:v>-9.2935860953346</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-0.32609763182693</c:v>
+                  <c:v>-7.60894474262836</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.266986159682609</c:v>
+                  <c:v>-6.22967705926087</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.21858977957834</c:v>
+                  <c:v>-5.10042819016128</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-0.178966174849325</c:v>
+                  <c:v>-4.17587741315091</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-0.146525111109873</c:v>
+                  <c:v>-3.41891925923038</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-0.119964614563822</c:v>
+                  <c:v>-2.7991743398225</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-0.0982187192245475</c:v>
+                  <c:v>-2.29177011523944</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-0.0804146859570687</c:v>
+                  <c:v>-1.8763426723316</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-0.0658379763921602</c:v>
+                  <c:v>-1.53621944915041</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-0.0539035759926837</c:v>
+                  <c:v>-1.25775010649595</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-0.0441325153660862</c:v>
+                  <c:v>-1.02975869187534</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-0.0361326475409013</c:v>
+                  <c:v>-0.843095109287698</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-0.0295829097318634</c:v>
+                  <c:v>-0.69026789374348</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-0.0242204379630065</c:v>
+                  <c:v>-0.565143552470152</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-0.0198300174133309</c:v>
+                  <c:v>-0.462700406311053</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-0.0162354450903659</c:v>
+                  <c:v>-0.378827052108537</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-0.0132924581853915</c:v>
+                  <c:v>-0.310157357659134</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-0.0108829443003831</c:v>
+                  <c:v>-0.25393536700894</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-0.00891020118275843</c:v>
+                  <c:v>-0.207904694264363</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-0.00729505572443613</c:v>
+                  <c:v>-0.17021796690351</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-0.00597268646701343</c:v>
+                  <c:v>-0.139362684230313</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-0.00489002208903658</c:v>
+                  <c:v>-0.114100515410853</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-0.00400361146752488</c:v>
+                  <c:v>-0.0934176009089139</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-0.00327787983183829</c:v>
+                  <c:v>-0.0764838627428935</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-0.00268370102322009</c:v>
+                  <c:v>-0.0626196905418022</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-0.00219722855977714</c:v>
+                  <c:v>-0.0512686663947998</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-0.00179893859343079</c:v>
+                  <c:v>-0.0419752338467183</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-0.00147284634934063</c:v>
+                  <c:v>-0.0343664148179481</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-0.00120586460076381</c:v>
+                  <c:v>-0.0281368406844889</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-0.000987278432693436</c:v>
+                  <c:v>-0.0230364967628468</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-0.000808315214696747</c:v>
+                  <c:v>-0.0188606883429241</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-0.000661792524453058</c:v>
+                  <c:v>-0.0154418255705713</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-0.000541829891926831</c:v>
+                  <c:v>-0.0126426974782927</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-0.000443612795457416</c:v>
+                  <c:v>-0.0103509652273397</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-0.000363199438099878</c:v>
+                  <c:v>-0.00847465355566384</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2884,154 +2884,154 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5e-07</c:v>
+                  <c:v>2.85714285714286e-07</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1e-06</c:v>
+                  <c:v>5.71428571428571e-07</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.5e-06</c:v>
+                  <c:v>8.57142857142857e-07</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>1.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>2e-06</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3e-06</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3.5e-06</c:v>
-                </c:pt>
                 <c:pt idx="8">
+                  <c:v>2.28571428571429e-06</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.57142857142857e-06</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.85714285714286e-06</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>4e-06</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>4.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5e-06</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
+                  <c:v>4.28571428571429e-06</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.57142857142857e-06</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.85714285714286e-06</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>6e-06</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>6.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>7e-06</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="22">
+                  <c:v>6.28571428571428e-06</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.57142857142857e-06</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.85714285714286e-06</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>8e-06</c:v>
                 </c:pt>
-                <c:pt idx="17">
-                  <c:v>8.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>9e-06</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>9.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="29">
+                  <c:v>8.28571428571429e-06</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8.57142857142857e-06</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8.85714285714286e-06</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>9.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>9.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>1e-05</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>1.05e-05</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.1e-05</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1.15e-05</c:v>
-                </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="36">
+                  <c:v>1.02857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.05714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.08571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.11428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.14285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.17142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>1.2e-05</c:v>
                 </c:pt>
-                <c:pt idx="25">
-                  <c:v>1.25e-05</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1.3e-05</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1.35e-05</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="43">
+                  <c:v>1.22857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.25714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.28571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.31428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.34285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.37142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="49">
                   <c:v>1.4e-05</c:v>
                 </c:pt>
-                <c:pt idx="29">
-                  <c:v>1.45e-05</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1.5e-05</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1.55e-05</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1.6e-05</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1.65e-05</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1.7e-05</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1.75e-05</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1.8e-05</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1.85e-05</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1.9e-05</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1.95e-05</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2e-05</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2.05e-05</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2.1e-05</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2.15e-05</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2.2e-05</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2.25e-05</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2.3e-05</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2.35e-05</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2.4e-05</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2.45e-05</c:v>
-                </c:pt>
                 <c:pt idx="50">
-                  <c:v>2.5e-05</c:v>
+                  <c:v>1.42857142857143e-05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3043,157 +3043,157 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>0.0666666666666667</c:v>
+                  <c:v>0.888888888888889</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0545820502051988</c:v>
+                  <c:v>0.72776066940265</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0446880030690426</c:v>
+                  <c:v>0.595840040920568</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0365874424062684</c:v>
+                  <c:v>0.487832565416912</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0299552642744814</c:v>
+                  <c:v>0.399403523659752</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0245252960780962</c:v>
+                  <c:v>0.327003947707949</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0200796141274801</c:v>
+                  <c:v>0.267728188366402</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0164397975961071</c:v>
+                  <c:v>0.219197301281428</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0134597678663104</c:v>
+                  <c:v>0.179463571550805</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0110199258814391</c:v>
+                  <c:v>0.146932345085855</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.00902235221577418</c:v>
+                  <c:v>0.120298029543656</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.00738687722415559</c:v>
+                  <c:v>0.0984916963220746</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.0060478635526275</c:v>
+                  <c:v>0.0806381807017</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.00495157188095559</c:v>
+                  <c:v>0.0660209584127412</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.00405400417501453</c:v>
+                  <c:v>0.0540533890001937</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.00331913789119093</c:v>
+                  <c:v>0.0442551718825457</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.00271748026522441</c:v>
+                  <c:v>0.0362330702029922</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.00222488466402174</c:v>
+                  <c:v>0.0296651288536232</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.00182158149648617</c:v>
+                  <c:v>0.0242877532864823</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.00149138479041104</c:v>
+                  <c:v>0.0198851305388139</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.00122104259258228</c:v>
+                  <c:v>0.016280567901097</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.00099970512136518</c:v>
+                  <c:v>0.0133294016182024</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.000818489326871229</c:v>
+                  <c:v>0.0109131910249497</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.000670122382975572</c:v>
+                  <c:v>0.00893496510634096</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.000548649803268001</c:v>
+                  <c:v>0.00731533071024002</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.000449196466605698</c:v>
+                  <c:v>0.0059892862214093</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.000367770961384051</c:v>
+                  <c:v>0.00490361281845402</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.000301105396174178</c:v>
+                  <c:v>0.0040147386156557</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.000246524247765529</c:v>
+                  <c:v>0.00328698997020705</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.000201836983025054</c:v>
+                  <c:v>0.00269115977366739</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.000165250145111091</c:v>
+                  <c:v>0.00220333526814787</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.000135295375753049</c:v>
+                  <c:v>0.00180393834337399</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.000110770484878262</c:v>
+                  <c:v>0.00147693979837683</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>9.0691202503193e-05</c:v>
+                  <c:v>0.0012092160333759</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>7.42516765229868e-05</c:v>
+                  <c:v>0.000990022353639825</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>6.07921310369678e-05</c:v>
+                  <c:v>0.00081056174715957</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4.97723872251119e-05</c:v>
+                  <c:v>0.00066363182966816</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4.07501840753049e-05</c:v>
+                  <c:v>0.000543335787670731</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>3.33634288960407e-05</c:v>
+                  <c:v>0.000444845718613876</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2.73156652653191e-05</c:v>
+                  <c:v>0.000364208870204255</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.23641751935008e-05</c:v>
+                  <c:v>0.000298189002580011</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.83102379981428e-05</c:v>
+                  <c:v>0.000244136506641904</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.49911549452565e-05</c:v>
+                  <c:v>0.000199882065936754</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.22737195778386e-05</c:v>
+                  <c:v>0.000163649594371182</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.00488716730318e-05</c:v>
+                  <c:v>0.000133984955640424</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>8.2273202724453e-06</c:v>
+                  <c:v>0.000109697603632604</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>6.73596012247288e-06</c:v>
+                  <c:v>8.98128016329719e-05</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>5.51493770377548e-06</c:v>
+                  <c:v>7.35325027170066e-05</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>4.51524909939025e-06</c:v>
+                  <c:v>6.02033213252034e-05</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>3.69677329547846e-06</c:v>
+                  <c:v>4.92903106063795e-05</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3.02666198416566e-06</c:v>
+                  <c:v>4.03554931222088e-05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3233,154 +3233,154 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5e-07</c:v>
+                  <c:v>2.85714285714286e-07</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1e-06</c:v>
+                  <c:v>5.71428571428571e-07</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.5e-06</c:v>
+                  <c:v>8.57142857142857e-07</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>1.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>2e-06</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3e-06</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3.5e-06</c:v>
-                </c:pt>
                 <c:pt idx="8">
+                  <c:v>2.28571428571429e-06</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.57142857142857e-06</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.85714285714286e-06</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>4e-06</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>4.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5e-06</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
+                  <c:v>4.28571428571429e-06</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.57142857142857e-06</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.85714285714286e-06</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>6e-06</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>6.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>7e-06</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="22">
+                  <c:v>6.28571428571428e-06</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.57142857142857e-06</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.85714285714286e-06</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>8e-06</c:v>
                 </c:pt>
-                <c:pt idx="17">
-                  <c:v>8.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>9e-06</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>9.5e-06</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="29">
+                  <c:v>8.28571428571429e-06</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8.57142857142857e-06</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8.85714285714286e-06</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.14285714285714e-06</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>9.42857142857143e-06</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>9.71428571428571e-06</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>1e-05</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>1.05e-05</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.1e-05</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1.15e-05</c:v>
-                </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="36">
+                  <c:v>1.02857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.05714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.08571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.11428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.14285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.17142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>1.2e-05</c:v>
                 </c:pt>
-                <c:pt idx="25">
-                  <c:v>1.25e-05</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1.3e-05</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1.35e-05</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="43">
+                  <c:v>1.22857142857143e-05</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.25714285714286e-05</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.28571428571429e-05</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.31428571428571e-05</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.34285714285714e-05</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.37142857142857e-05</c:v>
+                </c:pt>
+                <c:pt idx="49">
                   <c:v>1.4e-05</c:v>
                 </c:pt>
-                <c:pt idx="29">
-                  <c:v>1.45e-05</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1.5e-05</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1.55e-05</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1.6e-05</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1.65e-05</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1.7e-05</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1.75e-05</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1.8e-05</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1.85e-05</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1.9e-05</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1.95e-05</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2e-05</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2.05e-05</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2.1e-05</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2.15e-05</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2.2e-05</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2.25e-05</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2.3e-05</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2.35e-05</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2.4e-05</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2.45e-05</c:v>
-                </c:pt>
                 <c:pt idx="50">
-                  <c:v>2.5e-05</c:v>
+                  <c:v>1.42857142857143e-05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3392,157 +3392,157 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>-8</c:v>
+                  <c:v>-186.666666666667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-6.54984602462385</c:v>
+                  <c:v>-152.829740574557</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5.36256036828511</c:v>
+                  <c:v>-125.126408593319</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.39049308875221</c:v>
+                  <c:v>-102.444838737552</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-3.59463171293777</c:v>
+                  <c:v>-83.874739968548</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-2.94303552937154</c:v>
+                  <c:v>-68.6708290186692</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-2.40955369529762</c:v>
+                  <c:v>-56.2229195569444</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.97277571153285</c:v>
+                  <c:v>-46.0314332690999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1.61517214395724</c:v>
+                  <c:v>-37.687350025669</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1.32239110577269</c:v>
+                  <c:v>-30.8557924680295</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.0826822658929</c:v>
+                  <c:v>-25.2625862041677</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.886425266898671</c:v>
+                  <c:v>-20.6832562276357</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.7257436263153</c:v>
+                  <c:v>-16.934017947357</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.594188625714671</c:v>
+                  <c:v>-13.8644012666757</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.486480501001744</c:v>
+                  <c:v>-11.3512116900407</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.398296546942912</c:v>
+                  <c:v>-9.2935860953346</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-0.32609763182693</c:v>
+                  <c:v>-7.60894474262836</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.266986159682609</c:v>
+                  <c:v>-6.22967705926087</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.21858977957834</c:v>
+                  <c:v>-5.10042819016128</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-0.178966174849325</c:v>
+                  <c:v>-4.17587741315091</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-0.146525111109873</c:v>
+                  <c:v>-3.41891925923038</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-0.119964614563822</c:v>
+                  <c:v>-2.7991743398225</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-0.0982187192245475</c:v>
+                  <c:v>-2.29177011523944</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-0.0804146859570686</c:v>
+                  <c:v>-1.8763426723316</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-0.0658379763921602</c:v>
+                  <c:v>-1.5362194491504</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-0.0539035759926837</c:v>
+                  <c:v>-1.25775010649595</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-0.0441325153660862</c:v>
+                  <c:v>-1.02975869187534</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-0.0361326475409013</c:v>
+                  <c:v>-0.843095109287698</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-0.0295829097318634</c:v>
+                  <c:v>-0.690267893743481</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-0.0242204379630065</c:v>
+                  <c:v>-0.565143552470152</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-0.0198300174133309</c:v>
+                  <c:v>-0.462700406311054</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-0.0162354450903659</c:v>
+                  <c:v>-0.378827052108537</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-0.0132924581853915</c:v>
+                  <c:v>-0.310157357659134</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-0.0108829443003832</c:v>
+                  <c:v>-0.25393536700894</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-0.00891020118275842</c:v>
+                  <c:v>-0.207904694264363</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-0.00729505572443613</c:v>
+                  <c:v>-0.17021796690351</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-0.00597268646701343</c:v>
+                  <c:v>-0.139362684230314</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-0.00489002208903658</c:v>
+                  <c:v>-0.114100515410854</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-0.00400361146752488</c:v>
+                  <c:v>-0.0934176009089139</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-0.00327787983183829</c:v>
+                  <c:v>-0.0764838627428935</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-0.00268370102322009</c:v>
+                  <c:v>-0.0626196905418022</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-0.00219722855977714</c:v>
+                  <c:v>-0.0512686663947999</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-0.00179893859343079</c:v>
+                  <c:v>-0.0419752338467183</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-0.00147284634934063</c:v>
+                  <c:v>-0.0343664148179481</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-0.00120586460076381</c:v>
+                  <c:v>-0.028136840684489</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-0.000987278432693436</c:v>
+                  <c:v>-0.0230364967628468</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-0.000808315214696746</c:v>
+                  <c:v>-0.0188606883429241</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-0.000661792524453058</c:v>
+                  <c:v>-0.0154418255705714</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-0.00054182989192683</c:v>
+                  <c:v>-0.0126426974782927</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-0.000443612795457416</c:v>
+                  <c:v>-0.0103509652273397</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-0.000363199438099879</c:v>
+                  <c:v>-0.00847465355566384</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4564,154 +4564,154 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.5e-05</c:v>
+                  <c:v>1.76470588235294e-06</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>3.52941176470588e-06</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.29411764705882e-06</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.05882352941176e-06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.82352941176471e-06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.05882352941176e-05</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.23529411764706e-05</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.41176470588235e-05</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.58823529411765e-05</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.76470588235294e-05</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.94117647058824e-05</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.11764705882353e-05</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.29411764705882e-05</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.47058823529412e-05</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.64705882352941e-05</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.82352941176471e-05</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>3e-05</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.5e-05</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="18">
+                  <c:v>3.17647058823529e-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.35294117647059e-05</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.52941176470588e-05</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.70588235294118e-05</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.88235294117647e-05</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.05882352941176e-05</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.23529411764706e-05</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.41176470588235e-05</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.58823529411765e-05</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.76470588235294e-05</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4.94117647058823e-05</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.11764705882353e-05</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.29411764705882e-05</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5.47058823529412e-05</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5.64705882352941e-05</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.82352941176471e-05</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>6e-05</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.5e-05</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9e-05</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.000105</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.00012</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.000135</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.00015</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.000165</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.00018</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.000195</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.00021</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.000225</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.00024</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.000255</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.00027</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.000285</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.0003</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.000315</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.00033</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.000345</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.00036</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.000375</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.00039</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.000405</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.00042</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.000435</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.00045</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.000465</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.00048</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.000495</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.00051</c:v>
-                </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.000525</c:v>
+                  <c:v>6.17647058823529e-05</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.00054</c:v>
+                  <c:v>6.35294117647059e-05</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.000555</c:v>
+                  <c:v>6.52941176470588e-05</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.00057</c:v>
+                  <c:v>6.70588235294118e-05</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.000585</c:v>
+                  <c:v>6.88235294117647e-05</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.0006</c:v>
+                  <c:v>7.05882352941176e-05</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.000615</c:v>
+                  <c:v>7.23529411764706e-05</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.00063</c:v>
+                  <c:v>7.41176470588235e-05</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.000645</c:v>
+                  <c:v>7.58823529411765e-05</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.00066</c:v>
+                  <c:v>7.76470588235294e-05</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.000675</c:v>
+                  <c:v>7.94117647058823e-05</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.00069</c:v>
+                  <c:v>8.11764705882353e-05</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.000705</c:v>
+                  <c:v>8.29411764705882e-05</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.00072</c:v>
+                  <c:v>8.47058823529412e-05</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.000735</c:v>
+                  <c:v>8.64705882352941e-05</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.00075</c:v>
+                  <c:v>8.82352941176471e-05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4723,157 +4723,157 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>0.666666666666667</c:v>
+                  <c:v>1.77777777777778</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.545820502051988</c:v>
+                  <c:v>1.4555213388053</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.446880030690426</c:v>
+                  <c:v>1.19168008184114</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.365874424062684</c:v>
+                  <c:v>0.975665130833825</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.299552642744814</c:v>
+                  <c:v>0.798807047319505</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.245252960780962</c:v>
+                  <c:v>0.654007895415897</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.200796141274801</c:v>
+                  <c:v>0.535456376732804</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.164397975961071</c:v>
+                  <c:v>0.438394602562856</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.134597678663104</c:v>
+                  <c:v>0.35892714310161</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.110199258814391</c:v>
+                  <c:v>0.293864690171709</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.0902235221577418</c:v>
+                  <c:v>0.240596059087311</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.0738687722415559</c:v>
+                  <c:v>0.196983392644149</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.060478635526275</c:v>
+                  <c:v>0.1612763614034</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.0495157188095559</c:v>
+                  <c:v>0.132041916825482</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.0405400417501453</c:v>
+                  <c:v>0.108106778000387</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.0331913789119093</c:v>
+                  <c:v>0.0885103437650915</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.0271748026522441</c:v>
+                  <c:v>0.0724661404059844</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.0222488466402174</c:v>
+                  <c:v>0.0593302577072464</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.0182158149648617</c:v>
+                  <c:v>0.0485755065729645</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.0149138479041104</c:v>
+                  <c:v>0.0397702610776277</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.0122104259258228</c:v>
+                  <c:v>0.0325611358021941</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.00999705121365181</c:v>
+                  <c:v>0.0266588032364048</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.00818489326871229</c:v>
+                  <c:v>0.0218263820498994</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.00670122382975572</c:v>
+                  <c:v>0.0178699302126819</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.00548649803268002</c:v>
+                  <c:v>0.0146306614204801</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.00449196466605698</c:v>
+                  <c:v>0.0119785724428186</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.00367770961384052</c:v>
+                  <c:v>0.00980722563690805</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.00301105396174178</c:v>
+                  <c:v>0.00802947723131141</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.00246524247765529</c:v>
+                  <c:v>0.0065739799404141</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.00201836983025055</c:v>
+                  <c:v>0.00538231954733478</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.0016525014511109</c:v>
+                  <c:v>0.00440667053629575</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.00135295375753049</c:v>
+                  <c:v>0.00360787668674797</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.00110770484878262</c:v>
+                  <c:v>0.00295387959675366</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.000906912025031929</c:v>
+                  <c:v>0.00241843206675181</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.00074251676522987</c:v>
+                  <c:v>0.00198004470727965</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.000607921310369677</c:v>
+                  <c:v>0.00162112349431914</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.00049772387225112</c:v>
+                  <c:v>0.00132726365933632</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.000407501840753049</c:v>
+                  <c:v>0.00108667157534146</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.000333634288960407</c:v>
+                  <c:v>0.000889691437227753</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.000273156652653191</c:v>
+                  <c:v>0.00072841774040851</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.000223641751935008</c:v>
+                  <c:v>0.000596378005160021</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.000183102379981428</c:v>
+                  <c:v>0.000488273013283809</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.000149911549452566</c:v>
+                  <c:v>0.000399764131873509</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.000122737195778386</c:v>
+                  <c:v>0.000327299188742363</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.000100488716730318</c:v>
+                  <c:v>0.000267969911280847</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>8.2273202724453e-05</c:v>
+                  <c:v>0.000219395207265208</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>6.73596012247289e-05</c:v>
+                  <c:v>0.000179625603265944</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>5.51493770377549e-05</c:v>
+                  <c:v>0.000147065005434013</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>4.51524909939027e-05</c:v>
+                  <c:v>0.000120406642650407</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>3.69677329547846e-05</c:v>
+                  <c:v>9.8580621212759e-05</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3.02666198416566e-05</c:v>
+                  <c:v>8.07109862444175e-05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4913,154 +4913,154 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.5e-05</c:v>
+                  <c:v>1.76470588235294e-06</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>3.52941176470588e-06</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.29411764705882e-06</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.05882352941176e-06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.82352941176471e-06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.05882352941176e-05</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.23529411764706e-05</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.41176470588235e-05</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.58823529411765e-05</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.76470588235294e-05</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.94117647058824e-05</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.11764705882353e-05</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.29411764705882e-05</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.47058823529412e-05</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.64705882352941e-05</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.82352941176471e-05</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>3e-05</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.5e-05</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="18">
+                  <c:v>3.17647058823529e-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.35294117647059e-05</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.52941176470588e-05</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.70588235294118e-05</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.88235294117647e-05</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.05882352941176e-05</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.23529411764706e-05</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.41176470588235e-05</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.58823529411765e-05</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.76470588235294e-05</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4.94117647058823e-05</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.11764705882353e-05</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.29411764705882e-05</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5.47058823529412e-05</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5.64705882352941e-05</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.82352941176471e-05</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>6e-05</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.5e-05</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9e-05</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.000105</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.00012</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.000135</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.00015</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.000165</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.00018</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.000195</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.00021</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.000225</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.00024</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.000255</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.00027</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.000285</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.0003</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.000315</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.00033</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.000345</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.00036</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.000375</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.00039</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.000405</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.00042</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.000435</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.00045</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.000465</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.00048</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.000495</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.00051</c:v>
-                </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.000525</c:v>
+                  <c:v>6.17647058823529e-05</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.00054</c:v>
+                  <c:v>6.35294117647059e-05</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.000555</c:v>
+                  <c:v>6.52941176470588e-05</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.00057</c:v>
+                  <c:v>6.70588235294118e-05</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.000585</c:v>
+                  <c:v>6.88235294117647e-05</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.0006</c:v>
+                  <c:v>7.05882352941176e-05</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.000615</c:v>
+                  <c:v>7.23529411764706e-05</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.00063</c:v>
+                  <c:v>7.41176470588235e-05</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.000645</c:v>
+                  <c:v>7.58823529411765e-05</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.00066</c:v>
+                  <c:v>7.76470588235294e-05</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.000675</c:v>
+                  <c:v>7.94117647058823e-05</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.00069</c:v>
+                  <c:v>8.11764705882353e-05</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.000705</c:v>
+                  <c:v>8.29411764705882e-05</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.00072</c:v>
+                  <c:v>8.47058823529412e-05</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.000735</c:v>
+                  <c:v>8.64705882352941e-05</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.00075</c:v>
+                  <c:v>8.82352941176471e-05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5072,157 +5072,157 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>-8</c:v>
+                  <c:v>-181.333333333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-6.54984602462385</c:v>
+                  <c:v>-148.463176558141</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5.36256036828511</c:v>
+                  <c:v>-121.551368347796</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.39049308875221</c:v>
+                  <c:v>-99.5178433450501</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-3.59463171293777</c:v>
+                  <c:v>-81.4783188265895</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-2.94303552937154</c:v>
+                  <c:v>-66.7088053324215</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-2.40955369529762</c:v>
+                  <c:v>-54.616550426746</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.97277571153285</c:v>
+                  <c:v>-44.7162494614113</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1.61517214395724</c:v>
+                  <c:v>-36.6105685963642</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1.32239110577269</c:v>
+                  <c:v>-29.9741983975144</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.0826822658929</c:v>
+                  <c:v>-24.5407980269058</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.886425266898671</c:v>
+                  <c:v>-20.0923060497032</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.7257436263153</c:v>
+                  <c:v>-16.4501888631468</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.594188625714671</c:v>
+                  <c:v>-13.4682755161992</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.486480501001744</c:v>
+                  <c:v>-11.0268913560395</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.398296546942911</c:v>
+                  <c:v>-9.02805506403933</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-0.32609763182693</c:v>
+                  <c:v>-7.39154632141041</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.266986159682609</c:v>
+                  <c:v>-6.05168628613913</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.218589779578341</c:v>
+                  <c:v>-4.95470167044238</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-0.178966174849325</c:v>
+                  <c:v>-4.05656662991803</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-0.146525111109873</c:v>
+                  <c:v>-3.3212358518238</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-0.119964614563822</c:v>
+                  <c:v>-2.71919793011329</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-0.0982187192245475</c:v>
+                  <c:v>-2.22629096908974</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-0.0804146859570687</c:v>
+                  <c:v>-1.82273288169356</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-0.0658379763921603</c:v>
+                  <c:v>-1.49232746488897</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-0.0539035759926837</c:v>
+                  <c:v>-1.2218143891675</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-0.0441325153660862</c:v>
+                  <c:v>-1.00033701496462</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-0.0361326475409014</c:v>
+                  <c:v>-0.819006677593764</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-0.0295829097318635</c:v>
+                  <c:v>-0.670545953922238</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-0.0242204379630065</c:v>
+                  <c:v>-0.548996593828148</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-0.0198300174133309</c:v>
+                  <c:v>-0.449480394702167</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-0.0162354450903659</c:v>
+                  <c:v>-0.368003422048293</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-0.0132924581853915</c:v>
+                  <c:v>-0.301295718868874</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-0.0108829443003831</c:v>
+                  <c:v>-0.246680070808685</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-0.00891020118275843</c:v>
+                  <c:v>-0.201964560142524</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-0.00729505572443613</c:v>
+                  <c:v>-0.165354596420552</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-0.00597268646701344</c:v>
+                  <c:v>-0.135380893252304</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-0.00489002208903658</c:v>
+                  <c:v>-0.110840500684829</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-0.00400361146752489</c:v>
+                  <c:v>-0.0907485265972308</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-0.0032778798318383</c:v>
+                  <c:v>-0.074298609521668</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-0.00268370102322009</c:v>
+                  <c:v>-0.0608305565263221</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-0.00219722855977714</c:v>
+                  <c:v>-0.0498038473549485</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-0.00179893859343079</c:v>
+                  <c:v>-0.0407759414510979</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-0.00147284634934063</c:v>
+                  <c:v>-0.033384517251721</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-0.00120586460076381</c:v>
+                  <c:v>-0.0273329309506464</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-0.000987278432693436</c:v>
+                  <c:v>-0.0223783111410512</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-0.000808315214696747</c:v>
+                  <c:v>-0.0183218115331263</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-0.000661792524453059</c:v>
+                  <c:v>-0.0150006305542693</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-0.000541829891926832</c:v>
+                  <c:v>-0.0122814775503415</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-0.000443612795457416</c:v>
+                  <c:v>-0.0100552233637014</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-0.000363199438099879</c:v>
+                  <c:v>-0.00823252059693059</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5381,7 +5381,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>базовый (L, r)</c:v>
+            <c:v>базовый (L, r1)</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="25000">
@@ -6067,7 +6067,7 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>r меньше в 2 раза</c:v>
+            <c:v>r1 меньше в 2 раза</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="25000">
@@ -7185,7 +7185,7 @@
       <c r="AS1" s="5" t="n"/>
       <c r="AT1" s="6" t="inlineStr">
         <is>
-          <t>r/2 и R/10</t>
+          <t>r1/2 и R/10</t>
         </is>
       </c>
       <c r="AU1" s="5" t="n"/>
@@ -7436,7 +7436,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>r1</t>
         </is>
       </c>
       <c r="B4" s="11" t="n">
@@ -7447,12 +7447,18 @@
           <t>Ом</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>Заряд — ключ на E через r.
-Разряд — контур L и R.</t>
+          <t>Заряд — ключ влево, через r1.
+Разряд — L, R и r2.</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -7470,7 +7476,7 @@
       <c r="S4" s="5" t="n"/>
       <c r="T4" s="10" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>r1</t>
         </is>
       </c>
       <c r="U4" s="11" t="n">
@@ -7481,8 +7487,14 @@
           <t>Ом</t>
         </is>
       </c>
-      <c r="W4" s="5" t="n"/>
-      <c r="X4" s="5" t="n"/>
+      <c r="W4" s="10" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="X4" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="Y4" s="13" t="inlineStr">
         <is>
           <t>меньше L — быстрее нарастает ток</t>
@@ -7505,7 +7517,7 @@
       <c r="AN4" s="5" t="n"/>
       <c r="AO4" s="10" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>r1</t>
         </is>
       </c>
       <c r="AP4" s="11" t="n">
@@ -7516,12 +7528,18 @@
           <t>Ом</t>
         </is>
       </c>
-      <c r="AR4" s="5" t="n"/>
-      <c r="AS4" s="5" t="n"/>
+      <c r="AR4" s="10" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="AS4" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="AT4" s="13" t="inlineStr">
         <is>
-          <t>меньше r — больше E/r,
-разряд через R=12 Ом</t>
+          <t>меньше r1 — больше E/r1,
+разряд через R=12 Ом и r2</t>
         </is>
       </c>
       <c r="AU4" s="5" t="n"/>
@@ -7714,7 +7732,7 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>τз = L/r</t>
+          <t>τз = L/r1</t>
         </is>
       </c>
       <c r="B7" s="16">
@@ -7744,7 +7762,7 @@
       <c r="S7" s="5" t="n"/>
       <c r="T7" s="15" t="inlineStr">
         <is>
-          <t>τз = L/r</t>
+          <t>τз = L/r1</t>
         </is>
       </c>
       <c r="U7" s="16">
@@ -7776,7 +7794,7 @@
       <c r="AN7" s="5" t="n"/>
       <c r="AO7" s="15" t="inlineStr">
         <is>
-          <t>τз = L/r</t>
+          <t>τз = L/r1</t>
         </is>
       </c>
       <c r="AP7" s="16">
@@ -7804,11 +7822,11 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>τр = L/R</t>
+          <t>τр = L/(R+r2)</t>
         </is>
       </c>
       <c r="B8" s="16">
-        <f>B6/B5</f>
+        <f>B6/(B5+E4)</f>
         <v/>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -7834,11 +7852,11 @@
       <c r="S8" s="5" t="n"/>
       <c r="T8" s="15" t="inlineStr">
         <is>
-          <t>τр = L/R</t>
+          <t>τр = L/(R+r2)</t>
         </is>
       </c>
       <c r="U8" s="16">
-        <f>U6/U5</f>
+        <f>U6/(U5+X4)</f>
         <v/>
       </c>
       <c r="V8" s="15" t="inlineStr">
@@ -7866,11 +7884,11 @@
       <c r="AN8" s="5" t="n"/>
       <c r="AO8" s="15" t="inlineStr">
         <is>
-          <t>τр = L/R</t>
+          <t>τр = L/(R+r2)</t>
         </is>
       </c>
       <c r="AP8" s="16">
-        <f>AP6/AP5</f>
+        <f>AP6/(AP5+AS4)</f>
         <v/>
       </c>
       <c r="AQ8" s="15" t="inlineStr">
@@ -8021,11 +8039,11 @@
         <v/>
       </c>
       <c r="D10" s="20">
-        <f>($B$3/$B$5)*EXP(-A10*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A10*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E10" s="20">
-        <f>-$B$3*EXP(-A10*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D10</f>
         <v/>
       </c>
       <c r="F10" s="5" t="n"/>
@@ -8054,11 +8072,11 @@
         <v/>
       </c>
       <c r="W10" s="20">
-        <f>($U$3/$U$5)*EXP(-T10*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T10*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X10" s="20">
-        <f>-$U$3*EXP(-T10*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W10</f>
         <v/>
       </c>
       <c r="Y10" s="5" t="n"/>
@@ -8089,11 +8107,11 @@
         <v/>
       </c>
       <c r="AR10" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO10*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO10*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS10" s="20">
-        <f>-$AP$3*EXP(-AO10*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR10</f>
         <v/>
       </c>
       <c r="AT10" s="5" t="n"/>
@@ -8121,11 +8139,11 @@
         <v/>
       </c>
       <c r="D11" s="23">
-        <f>($B$3/$B$5)*EXP(-A11*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A11*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E11" s="23">
-        <f>-$B$3*EXP(-A11*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D11</f>
         <v/>
       </c>
       <c r="F11" s="5" t="n"/>
@@ -8155,11 +8173,11 @@
         <v/>
       </c>
       <c r="W11" s="23">
-        <f>($U$3/$U$5)*EXP(-T11*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T11*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X11" s="23">
-        <f>-$U$3*EXP(-T11*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W11</f>
         <v/>
       </c>
       <c r="Y11" s="5" t="n"/>
@@ -8191,11 +8209,11 @@
         <v/>
       </c>
       <c r="AR11" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO11*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO11*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS11" s="23">
-        <f>-$AP$3*EXP(-AO11*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR11</f>
         <v/>
       </c>
       <c r="AT11" s="5" t="n"/>
@@ -8223,11 +8241,11 @@
         <v/>
       </c>
       <c r="D12" s="20">
-        <f>($B$3/$B$5)*EXP(-A12*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A12*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E12" s="20">
-        <f>-$B$3*EXP(-A12*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D12</f>
         <v/>
       </c>
       <c r="F12" s="5" t="n"/>
@@ -8257,11 +8275,11 @@
         <v/>
       </c>
       <c r="W12" s="20">
-        <f>($U$3/$U$5)*EXP(-T12*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T12*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X12" s="20">
-        <f>-$U$3*EXP(-T12*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W12</f>
         <v/>
       </c>
       <c r="Y12" s="5" t="n"/>
@@ -8293,11 +8311,11 @@
         <v/>
       </c>
       <c r="AR12" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO12*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO12*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS12" s="20">
-        <f>-$AP$3*EXP(-AO12*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR12</f>
         <v/>
       </c>
       <c r="AT12" s="5" t="n"/>
@@ -8325,11 +8343,11 @@
         <v/>
       </c>
       <c r="D13" s="23">
-        <f>($B$3/$B$5)*EXP(-A13*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A13*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E13" s="23">
-        <f>-$B$3*EXP(-A13*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D13</f>
         <v/>
       </c>
       <c r="F13" s="5" t="n"/>
@@ -8359,11 +8377,11 @@
         <v/>
       </c>
       <c r="W13" s="23">
-        <f>($U$3/$U$5)*EXP(-T13*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T13*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X13" s="23">
-        <f>-$U$3*EXP(-T13*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W13</f>
         <v/>
       </c>
       <c r="Y13" s="5" t="n"/>
@@ -8395,11 +8413,11 @@
         <v/>
       </c>
       <c r="AR13" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO13*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO13*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS13" s="23">
-        <f>-$AP$3*EXP(-AO13*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR13</f>
         <v/>
       </c>
       <c r="AT13" s="5" t="n"/>
@@ -8427,11 +8445,11 @@
         <v/>
       </c>
       <c r="D14" s="20">
-        <f>($B$3/$B$5)*EXP(-A14*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A14*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E14" s="20">
-        <f>-$B$3*EXP(-A14*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D14</f>
         <v/>
       </c>
       <c r="F14" s="5" t="n"/>
@@ -8461,11 +8479,11 @@
         <v/>
       </c>
       <c r="W14" s="20">
-        <f>($U$3/$U$5)*EXP(-T14*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T14*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X14" s="20">
-        <f>-$U$3*EXP(-T14*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W14</f>
         <v/>
       </c>
       <c r="Y14" s="5" t="n"/>
@@ -8497,11 +8515,11 @@
         <v/>
       </c>
       <c r="AR14" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO14*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO14*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS14" s="20">
-        <f>-$AP$3*EXP(-AO14*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR14</f>
         <v/>
       </c>
       <c r="AT14" s="5" t="n"/>
@@ -8529,11 +8547,11 @@
         <v/>
       </c>
       <c r="D15" s="23">
-        <f>($B$3/$B$5)*EXP(-A15*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A15*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E15" s="23">
-        <f>-$B$3*EXP(-A15*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D15</f>
         <v/>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -8563,11 +8581,11 @@
         <v/>
       </c>
       <c r="W15" s="23">
-        <f>($U$3/$U$5)*EXP(-T15*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T15*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X15" s="23">
-        <f>-$U$3*EXP(-T15*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W15</f>
         <v/>
       </c>
       <c r="Y15" s="5" t="n"/>
@@ -8599,11 +8617,11 @@
         <v/>
       </c>
       <c r="AR15" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO15*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO15*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS15" s="23">
-        <f>-$AP$3*EXP(-AO15*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR15</f>
         <v/>
       </c>
       <c r="AT15" s="5" t="n"/>
@@ -8631,11 +8649,11 @@
         <v/>
       </c>
       <c r="D16" s="20">
-        <f>($B$3/$B$5)*EXP(-A16*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A16*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E16" s="20">
-        <f>-$B$3*EXP(-A16*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D16</f>
         <v/>
       </c>
       <c r="F16" s="5" t="n"/>
@@ -8665,11 +8683,11 @@
         <v/>
       </c>
       <c r="W16" s="20">
-        <f>($U$3/$U$5)*EXP(-T16*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T16*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X16" s="20">
-        <f>-$U$3*EXP(-T16*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W16</f>
         <v/>
       </c>
       <c r="Y16" s="5" t="n"/>
@@ -8701,11 +8719,11 @@
         <v/>
       </c>
       <c r="AR16" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO16*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO16*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS16" s="20">
-        <f>-$AP$3*EXP(-AO16*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR16</f>
         <v/>
       </c>
       <c r="AT16" s="5" t="n"/>
@@ -8733,11 +8751,11 @@
         <v/>
       </c>
       <c r="D17" s="23">
-        <f>($B$3/$B$5)*EXP(-A17*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A17*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E17" s="23">
-        <f>-$B$3*EXP(-A17*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D17</f>
         <v/>
       </c>
       <c r="F17" s="5" t="n"/>
@@ -8767,11 +8785,11 @@
         <v/>
       </c>
       <c r="W17" s="23">
-        <f>($U$3/$U$5)*EXP(-T17*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T17*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X17" s="23">
-        <f>-$U$3*EXP(-T17*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W17</f>
         <v/>
       </c>
       <c r="Y17" s="5" t="n"/>
@@ -8803,11 +8821,11 @@
         <v/>
       </c>
       <c r="AR17" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO17*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO17*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS17" s="23">
-        <f>-$AP$3*EXP(-AO17*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR17</f>
         <v/>
       </c>
       <c r="AT17" s="5" t="n"/>
@@ -8835,11 +8853,11 @@
         <v/>
       </c>
       <c r="D18" s="20">
-        <f>($B$3/$B$5)*EXP(-A18*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A18*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E18" s="20">
-        <f>-$B$3*EXP(-A18*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D18</f>
         <v/>
       </c>
       <c r="F18" s="5" t="n"/>
@@ -8869,11 +8887,11 @@
         <v/>
       </c>
       <c r="W18" s="20">
-        <f>($U$3/$U$5)*EXP(-T18*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T18*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X18" s="20">
-        <f>-$U$3*EXP(-T18*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W18</f>
         <v/>
       </c>
       <c r="Y18" s="5" t="n"/>
@@ -8905,11 +8923,11 @@
         <v/>
       </c>
       <c r="AR18" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO18*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO18*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS18" s="20">
-        <f>-$AP$3*EXP(-AO18*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR18</f>
         <v/>
       </c>
       <c r="AT18" s="5" t="n"/>
@@ -8937,11 +8955,11 @@
         <v/>
       </c>
       <c r="D19" s="23">
-        <f>($B$3/$B$5)*EXP(-A19*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A19*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E19" s="23">
-        <f>-$B$3*EXP(-A19*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D19</f>
         <v/>
       </c>
       <c r="F19" s="5" t="n"/>
@@ -8971,11 +8989,11 @@
         <v/>
       </c>
       <c r="W19" s="23">
-        <f>($U$3/$U$5)*EXP(-T19*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T19*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X19" s="23">
-        <f>-$U$3*EXP(-T19*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W19</f>
         <v/>
       </c>
       <c r="Y19" s="5" t="n"/>
@@ -9007,11 +9025,11 @@
         <v/>
       </c>
       <c r="AR19" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO19*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO19*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS19" s="23">
-        <f>-$AP$3*EXP(-AO19*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR19</f>
         <v/>
       </c>
       <c r="AT19" s="5" t="n"/>
@@ -9039,11 +9057,11 @@
         <v/>
       </c>
       <c r="D20" s="20">
-        <f>($B$3/$B$5)*EXP(-A20*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A20*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E20" s="20">
-        <f>-$B$3*EXP(-A20*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D20</f>
         <v/>
       </c>
       <c r="F20" s="5" t="n"/>
@@ -9073,11 +9091,11 @@
         <v/>
       </c>
       <c r="W20" s="20">
-        <f>($U$3/$U$5)*EXP(-T20*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T20*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X20" s="20">
-        <f>-$U$3*EXP(-T20*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W20</f>
         <v/>
       </c>
       <c r="Y20" s="5" t="n"/>
@@ -9109,11 +9127,11 @@
         <v/>
       </c>
       <c r="AR20" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO20*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO20*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS20" s="20">
-        <f>-$AP$3*EXP(-AO20*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR20</f>
         <v/>
       </c>
       <c r="AT20" s="5" t="n"/>
@@ -9141,11 +9159,11 @@
         <v/>
       </c>
       <c r="D21" s="23">
-        <f>($B$3/$B$5)*EXP(-A21*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A21*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E21" s="23">
-        <f>-$B$3*EXP(-A21*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D21</f>
         <v/>
       </c>
       <c r="F21" s="5" t="n"/>
@@ -9175,11 +9193,11 @@
         <v/>
       </c>
       <c r="W21" s="23">
-        <f>($U$3/$U$5)*EXP(-T21*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T21*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X21" s="23">
-        <f>-$U$3*EXP(-T21*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W21</f>
         <v/>
       </c>
       <c r="Y21" s="5" t="n"/>
@@ -9211,11 +9229,11 @@
         <v/>
       </c>
       <c r="AR21" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO21*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO21*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS21" s="23">
-        <f>-$AP$3*EXP(-AO21*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR21</f>
         <v/>
       </c>
       <c r="AT21" s="5" t="n"/>
@@ -9243,11 +9261,11 @@
         <v/>
       </c>
       <c r="D22" s="20">
-        <f>($B$3/$B$5)*EXP(-A22*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A22*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E22" s="20">
-        <f>-$B$3*EXP(-A22*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D22</f>
         <v/>
       </c>
       <c r="F22" s="5" t="n"/>
@@ -9277,11 +9295,11 @@
         <v/>
       </c>
       <c r="W22" s="20">
-        <f>($U$3/$U$5)*EXP(-T22*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T22*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X22" s="20">
-        <f>-$U$3*EXP(-T22*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W22</f>
         <v/>
       </c>
       <c r="Y22" s="5" t="n"/>
@@ -9313,11 +9331,11 @@
         <v/>
       </c>
       <c r="AR22" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO22*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO22*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS22" s="20">
-        <f>-$AP$3*EXP(-AO22*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR22</f>
         <v/>
       </c>
       <c r="AT22" s="5" t="n"/>
@@ -9345,11 +9363,11 @@
         <v/>
       </c>
       <c r="D23" s="23">
-        <f>($B$3/$B$5)*EXP(-A23*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A23*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E23" s="23">
-        <f>-$B$3*EXP(-A23*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D23</f>
         <v/>
       </c>
       <c r="F23" s="5" t="n"/>
@@ -9379,11 +9397,11 @@
         <v/>
       </c>
       <c r="W23" s="23">
-        <f>($U$3/$U$5)*EXP(-T23*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T23*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X23" s="23">
-        <f>-$U$3*EXP(-T23*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W23</f>
         <v/>
       </c>
       <c r="Y23" s="5" t="n"/>
@@ -9415,11 +9433,11 @@
         <v/>
       </c>
       <c r="AR23" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO23*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO23*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS23" s="23">
-        <f>-$AP$3*EXP(-AO23*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR23</f>
         <v/>
       </c>
       <c r="AT23" s="5" t="n"/>
@@ -9447,11 +9465,11 @@
         <v/>
       </c>
       <c r="D24" s="20">
-        <f>($B$3/$B$5)*EXP(-A24*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A24*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E24" s="20">
-        <f>-$B$3*EXP(-A24*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D24</f>
         <v/>
       </c>
       <c r="F24" s="5" t="n"/>
@@ -9481,11 +9499,11 @@
         <v/>
       </c>
       <c r="W24" s="20">
-        <f>($U$3/$U$5)*EXP(-T24*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T24*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X24" s="20">
-        <f>-$U$3*EXP(-T24*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W24</f>
         <v/>
       </c>
       <c r="Y24" s="5" t="n"/>
@@ -9517,11 +9535,11 @@
         <v/>
       </c>
       <c r="AR24" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO24*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO24*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS24" s="20">
-        <f>-$AP$3*EXP(-AO24*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR24</f>
         <v/>
       </c>
       <c r="AT24" s="5" t="n"/>
@@ -9549,11 +9567,11 @@
         <v/>
       </c>
       <c r="D25" s="23">
-        <f>($B$3/$B$5)*EXP(-A25*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A25*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E25" s="23">
-        <f>-$B$3*EXP(-A25*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D25</f>
         <v/>
       </c>
       <c r="F25" s="5" t="n"/>
@@ -9583,11 +9601,11 @@
         <v/>
       </c>
       <c r="W25" s="23">
-        <f>($U$3/$U$5)*EXP(-T25*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T25*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X25" s="23">
-        <f>-$U$3*EXP(-T25*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W25</f>
         <v/>
       </c>
       <c r="Y25" s="5" t="n"/>
@@ -9619,11 +9637,11 @@
         <v/>
       </c>
       <c r="AR25" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO25*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO25*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS25" s="23">
-        <f>-$AP$3*EXP(-AO25*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR25</f>
         <v/>
       </c>
       <c r="AT25" s="5" t="n"/>
@@ -9651,11 +9669,11 @@
         <v/>
       </c>
       <c r="D26" s="20">
-        <f>($B$3/$B$5)*EXP(-A26*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A26*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E26" s="20">
-        <f>-$B$3*EXP(-A26*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D26</f>
         <v/>
       </c>
       <c r="F26" s="5" t="n"/>
@@ -9685,11 +9703,11 @@
         <v/>
       </c>
       <c r="W26" s="20">
-        <f>($U$3/$U$5)*EXP(-T26*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T26*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X26" s="20">
-        <f>-$U$3*EXP(-T26*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W26</f>
         <v/>
       </c>
       <c r="Y26" s="5" t="n"/>
@@ -9721,11 +9739,11 @@
         <v/>
       </c>
       <c r="AR26" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO26*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO26*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS26" s="20">
-        <f>-$AP$3*EXP(-AO26*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR26</f>
         <v/>
       </c>
       <c r="AT26" s="5" t="n"/>
@@ -9753,11 +9771,11 @@
         <v/>
       </c>
       <c r="D27" s="23">
-        <f>($B$3/$B$5)*EXP(-A27*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A27*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E27" s="23">
-        <f>-$B$3*EXP(-A27*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D27</f>
         <v/>
       </c>
       <c r="F27" s="5" t="n"/>
@@ -9787,11 +9805,11 @@
         <v/>
       </c>
       <c r="W27" s="23">
-        <f>($U$3/$U$5)*EXP(-T27*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T27*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X27" s="23">
-        <f>-$U$3*EXP(-T27*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W27</f>
         <v/>
       </c>
       <c r="Y27" s="5" t="n"/>
@@ -9823,11 +9841,11 @@
         <v/>
       </c>
       <c r="AR27" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO27*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO27*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS27" s="23">
-        <f>-$AP$3*EXP(-AO27*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR27</f>
         <v/>
       </c>
       <c r="AT27" s="5" t="n"/>
@@ -9855,11 +9873,11 @@
         <v/>
       </c>
       <c r="D28" s="20">
-        <f>($B$3/$B$5)*EXP(-A28*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A28*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E28" s="20">
-        <f>-$B$3*EXP(-A28*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D28</f>
         <v/>
       </c>
       <c r="F28" s="5" t="n"/>
@@ -9889,11 +9907,11 @@
         <v/>
       </c>
       <c r="W28" s="20">
-        <f>($U$3/$U$5)*EXP(-T28*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T28*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X28" s="20">
-        <f>-$U$3*EXP(-T28*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W28</f>
         <v/>
       </c>
       <c r="Y28" s="5" t="n"/>
@@ -9925,11 +9943,11 @@
         <v/>
       </c>
       <c r="AR28" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO28*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO28*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS28" s="20">
-        <f>-$AP$3*EXP(-AO28*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR28</f>
         <v/>
       </c>
       <c r="AT28" s="5" t="n"/>
@@ -9957,11 +9975,11 @@
         <v/>
       </c>
       <c r="D29" s="23">
-        <f>($B$3/$B$5)*EXP(-A29*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A29*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E29" s="23">
-        <f>-$B$3*EXP(-A29*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D29</f>
         <v/>
       </c>
       <c r="F29" s="5" t="n"/>
@@ -9991,11 +10009,11 @@
         <v/>
       </c>
       <c r="W29" s="23">
-        <f>($U$3/$U$5)*EXP(-T29*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T29*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X29" s="23">
-        <f>-$U$3*EXP(-T29*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W29</f>
         <v/>
       </c>
       <c r="Y29" s="5" t="n"/>
@@ -10027,11 +10045,11 @@
         <v/>
       </c>
       <c r="AR29" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO29*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO29*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS29" s="23">
-        <f>-$AP$3*EXP(-AO29*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR29</f>
         <v/>
       </c>
       <c r="AT29" s="5" t="n"/>
@@ -10059,11 +10077,11 @@
         <v/>
       </c>
       <c r="D30" s="20">
-        <f>($B$3/$B$5)*EXP(-A30*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A30*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E30" s="20">
-        <f>-$B$3*EXP(-A30*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D30</f>
         <v/>
       </c>
       <c r="F30" s="5" t="n"/>
@@ -10093,11 +10111,11 @@
         <v/>
       </c>
       <c r="W30" s="20">
-        <f>($U$3/$U$5)*EXP(-T30*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T30*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X30" s="20">
-        <f>-$U$3*EXP(-T30*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W30</f>
         <v/>
       </c>
       <c r="Y30" s="5" t="n"/>
@@ -10129,11 +10147,11 @@
         <v/>
       </c>
       <c r="AR30" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO30*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO30*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS30" s="20">
-        <f>-$AP$3*EXP(-AO30*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR30</f>
         <v/>
       </c>
       <c r="AT30" s="5" t="n"/>
@@ -10161,11 +10179,11 @@
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>($B$3/$B$5)*EXP(-A31*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A31*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E31" s="23">
-        <f>-$B$3*EXP(-A31*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D31</f>
         <v/>
       </c>
       <c r="F31" s="5" t="n"/>
@@ -10195,11 +10213,11 @@
         <v/>
       </c>
       <c r="W31" s="23">
-        <f>($U$3/$U$5)*EXP(-T31*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T31*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X31" s="23">
-        <f>-$U$3*EXP(-T31*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W31</f>
         <v/>
       </c>
       <c r="Y31" s="5" t="n"/>
@@ -10231,11 +10249,11 @@
         <v/>
       </c>
       <c r="AR31" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO31*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO31*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS31" s="23">
-        <f>-$AP$3*EXP(-AO31*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR31</f>
         <v/>
       </c>
       <c r="AT31" s="5" t="n"/>
@@ -10263,11 +10281,11 @@
         <v/>
       </c>
       <c r="D32" s="20">
-        <f>($B$3/$B$5)*EXP(-A32*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A32*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f>-$B$3*EXP(-A32*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D32</f>
         <v/>
       </c>
       <c r="F32" s="5" t="n"/>
@@ -10297,11 +10315,11 @@
         <v/>
       </c>
       <c r="W32" s="20">
-        <f>($U$3/$U$5)*EXP(-T32*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T32*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X32" s="20">
-        <f>-$U$3*EXP(-T32*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W32</f>
         <v/>
       </c>
       <c r="Y32" s="5" t="n"/>
@@ -10333,11 +10351,11 @@
         <v/>
       </c>
       <c r="AR32" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO32*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO32*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS32" s="20">
-        <f>-$AP$3*EXP(-AO32*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR32</f>
         <v/>
       </c>
       <c r="AT32" s="5" t="n"/>
@@ -10365,11 +10383,11 @@
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>($B$3/$B$5)*EXP(-A33*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A33*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E33" s="23">
-        <f>-$B$3*EXP(-A33*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D33</f>
         <v/>
       </c>
       <c r="F33" s="5" t="n"/>
@@ -10399,11 +10417,11 @@
         <v/>
       </c>
       <c r="W33" s="23">
-        <f>($U$3/$U$5)*EXP(-T33*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T33*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X33" s="23">
-        <f>-$U$3*EXP(-T33*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W33</f>
         <v/>
       </c>
       <c r="Y33" s="5" t="n"/>
@@ -10435,11 +10453,11 @@
         <v/>
       </c>
       <c r="AR33" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO33*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO33*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS33" s="23">
-        <f>-$AP$3*EXP(-AO33*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR33</f>
         <v/>
       </c>
       <c r="AT33" s="5" t="n"/>
@@ -10467,11 +10485,11 @@
         <v/>
       </c>
       <c r="D34" s="20">
-        <f>($B$3/$B$5)*EXP(-A34*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A34*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E34" s="20">
-        <f>-$B$3*EXP(-A34*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D34</f>
         <v/>
       </c>
       <c r="F34" s="5" t="n"/>
@@ -10501,11 +10519,11 @@
         <v/>
       </c>
       <c r="W34" s="20">
-        <f>($U$3/$U$5)*EXP(-T34*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T34*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X34" s="20">
-        <f>-$U$3*EXP(-T34*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W34</f>
         <v/>
       </c>
       <c r="Y34" s="5" t="n"/>
@@ -10537,11 +10555,11 @@
         <v/>
       </c>
       <c r="AR34" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO34*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO34*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS34" s="20">
-        <f>-$AP$3*EXP(-AO34*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR34</f>
         <v/>
       </c>
       <c r="AT34" s="5" t="n"/>
@@ -10569,11 +10587,11 @@
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>($B$3/$B$5)*EXP(-A35*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A35*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E35" s="23">
-        <f>-$B$3*EXP(-A35*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D35</f>
         <v/>
       </c>
       <c r="F35" s="5" t="n"/>
@@ -10603,11 +10621,11 @@
         <v/>
       </c>
       <c r="W35" s="23">
-        <f>($U$3/$U$5)*EXP(-T35*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T35*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X35" s="23">
-        <f>-$U$3*EXP(-T35*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W35</f>
         <v/>
       </c>
       <c r="Y35" s="5" t="n"/>
@@ -10639,11 +10657,11 @@
         <v/>
       </c>
       <c r="AR35" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO35*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO35*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS35" s="23">
-        <f>-$AP$3*EXP(-AO35*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR35</f>
         <v/>
       </c>
       <c r="AT35" s="5" t="n"/>
@@ -10671,11 +10689,11 @@
         <v/>
       </c>
       <c r="D36" s="20">
-        <f>($B$3/$B$5)*EXP(-A36*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A36*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E36" s="20">
-        <f>-$B$3*EXP(-A36*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D36</f>
         <v/>
       </c>
       <c r="F36" s="5" t="n"/>
@@ -10705,11 +10723,11 @@
         <v/>
       </c>
       <c r="W36" s="20">
-        <f>($U$3/$U$5)*EXP(-T36*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T36*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X36" s="20">
-        <f>-$U$3*EXP(-T36*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W36</f>
         <v/>
       </c>
       <c r="Y36" s="5" t="n"/>
@@ -10741,11 +10759,11 @@
         <v/>
       </c>
       <c r="AR36" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO36*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO36*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS36" s="20">
-        <f>-$AP$3*EXP(-AO36*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR36</f>
         <v/>
       </c>
       <c r="AT36" s="5" t="n"/>
@@ -10773,11 +10791,11 @@
         <v/>
       </c>
       <c r="D37" s="23">
-        <f>($B$3/$B$5)*EXP(-A37*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A37*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E37" s="23">
-        <f>-$B$3*EXP(-A37*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D37</f>
         <v/>
       </c>
       <c r="F37" s="5" t="n"/>
@@ -10807,11 +10825,11 @@
         <v/>
       </c>
       <c r="W37" s="23">
-        <f>($U$3/$U$5)*EXP(-T37*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T37*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X37" s="23">
-        <f>-$U$3*EXP(-T37*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W37</f>
         <v/>
       </c>
       <c r="Y37" s="5" t="n"/>
@@ -10843,11 +10861,11 @@
         <v/>
       </c>
       <c r="AR37" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO37*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO37*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS37" s="23">
-        <f>-$AP$3*EXP(-AO37*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR37</f>
         <v/>
       </c>
       <c r="AT37" s="5" t="n"/>
@@ -10875,11 +10893,11 @@
         <v/>
       </c>
       <c r="D38" s="20">
-        <f>($B$3/$B$5)*EXP(-A38*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A38*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E38" s="20">
-        <f>-$B$3*EXP(-A38*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D38</f>
         <v/>
       </c>
       <c r="F38" s="5" t="n"/>
@@ -10909,11 +10927,11 @@
         <v/>
       </c>
       <c r="W38" s="20">
-        <f>($U$3/$U$5)*EXP(-T38*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T38*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X38" s="20">
-        <f>-$U$3*EXP(-T38*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W38</f>
         <v/>
       </c>
       <c r="Y38" s="5" t="n"/>
@@ -10945,11 +10963,11 @@
         <v/>
       </c>
       <c r="AR38" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO38*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO38*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS38" s="20">
-        <f>-$AP$3*EXP(-AO38*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR38</f>
         <v/>
       </c>
       <c r="AT38" s="5" t="n"/>
@@ -10977,11 +10995,11 @@
         <v/>
       </c>
       <c r="D39" s="23">
-        <f>($B$3/$B$5)*EXP(-A39*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A39*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E39" s="23">
-        <f>-$B$3*EXP(-A39*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D39</f>
         <v/>
       </c>
       <c r="F39" s="5" t="n"/>
@@ -11011,11 +11029,11 @@
         <v/>
       </c>
       <c r="W39" s="23">
-        <f>($U$3/$U$5)*EXP(-T39*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T39*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X39" s="23">
-        <f>-$U$3*EXP(-T39*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W39</f>
         <v/>
       </c>
       <c r="Y39" s="5" t="n"/>
@@ -11047,11 +11065,11 @@
         <v/>
       </c>
       <c r="AR39" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO39*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO39*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS39" s="23">
-        <f>-$AP$3*EXP(-AO39*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR39</f>
         <v/>
       </c>
       <c r="AT39" s="5" t="n"/>
@@ -11079,11 +11097,11 @@
         <v/>
       </c>
       <c r="D40" s="20">
-        <f>($B$3/$B$5)*EXP(-A40*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A40*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E40" s="20">
-        <f>-$B$3*EXP(-A40*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D40</f>
         <v/>
       </c>
       <c r="F40" s="5" t="n"/>
@@ -11113,11 +11131,11 @@
         <v/>
       </c>
       <c r="W40" s="20">
-        <f>($U$3/$U$5)*EXP(-T40*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T40*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X40" s="20">
-        <f>-$U$3*EXP(-T40*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W40</f>
         <v/>
       </c>
       <c r="Y40" s="5" t="n"/>
@@ -11149,11 +11167,11 @@
         <v/>
       </c>
       <c r="AR40" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO40*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO40*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS40" s="20">
-        <f>-$AP$3*EXP(-AO40*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR40</f>
         <v/>
       </c>
       <c r="AT40" s="5" t="n"/>
@@ -11181,11 +11199,11 @@
         <v/>
       </c>
       <c r="D41" s="23">
-        <f>($B$3/$B$5)*EXP(-A41*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A41*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E41" s="23">
-        <f>-$B$3*EXP(-A41*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D41</f>
         <v/>
       </c>
       <c r="F41" s="5" t="n"/>
@@ -11215,11 +11233,11 @@
         <v/>
       </c>
       <c r="W41" s="23">
-        <f>($U$3/$U$5)*EXP(-T41*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T41*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X41" s="23">
-        <f>-$U$3*EXP(-T41*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W41</f>
         <v/>
       </c>
       <c r="Y41" s="5" t="n"/>
@@ -11251,11 +11269,11 @@
         <v/>
       </c>
       <c r="AR41" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO41*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO41*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS41" s="23">
-        <f>-$AP$3*EXP(-AO41*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR41</f>
         <v/>
       </c>
       <c r="AT41" s="5" t="n"/>
@@ -11283,11 +11301,11 @@
         <v/>
       </c>
       <c r="D42" s="20">
-        <f>($B$3/$B$5)*EXP(-A42*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A42*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E42" s="20">
-        <f>-$B$3*EXP(-A42*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D42</f>
         <v/>
       </c>
       <c r="F42" s="5" t="n"/>
@@ -11317,11 +11335,11 @@
         <v/>
       </c>
       <c r="W42" s="20">
-        <f>($U$3/$U$5)*EXP(-T42*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T42*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X42" s="20">
-        <f>-$U$3*EXP(-T42*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W42</f>
         <v/>
       </c>
       <c r="Y42" s="5" t="n"/>
@@ -11353,11 +11371,11 @@
         <v/>
       </c>
       <c r="AR42" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO42*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO42*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS42" s="20">
-        <f>-$AP$3*EXP(-AO42*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR42</f>
         <v/>
       </c>
       <c r="AT42" s="5" t="n"/>
@@ -11385,11 +11403,11 @@
         <v/>
       </c>
       <c r="D43" s="23">
-        <f>($B$3/$B$5)*EXP(-A43*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A43*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E43" s="23">
-        <f>-$B$3*EXP(-A43*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D43</f>
         <v/>
       </c>
       <c r="F43" s="5" t="n"/>
@@ -11419,11 +11437,11 @@
         <v/>
       </c>
       <c r="W43" s="23">
-        <f>($U$3/$U$5)*EXP(-T43*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T43*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X43" s="23">
-        <f>-$U$3*EXP(-T43*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W43</f>
         <v/>
       </c>
       <c r="Y43" s="5" t="n"/>
@@ -11455,11 +11473,11 @@
         <v/>
       </c>
       <c r="AR43" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO43*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO43*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS43" s="23">
-        <f>-$AP$3*EXP(-AO43*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR43</f>
         <v/>
       </c>
       <c r="AT43" s="5" t="n"/>
@@ -11487,11 +11505,11 @@
         <v/>
       </c>
       <c r="D44" s="20">
-        <f>($B$3/$B$5)*EXP(-A44*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A44*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E44" s="20">
-        <f>-$B$3*EXP(-A44*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D44</f>
         <v/>
       </c>
       <c r="F44" s="5" t="n"/>
@@ -11521,11 +11539,11 @@
         <v/>
       </c>
       <c r="W44" s="20">
-        <f>($U$3/$U$5)*EXP(-T44*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T44*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X44" s="20">
-        <f>-$U$3*EXP(-T44*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W44</f>
         <v/>
       </c>
       <c r="Y44" s="5" t="n"/>
@@ -11557,11 +11575,11 @@
         <v/>
       </c>
       <c r="AR44" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO44*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO44*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS44" s="20">
-        <f>-$AP$3*EXP(-AO44*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR44</f>
         <v/>
       </c>
       <c r="AT44" s="5" t="n"/>
@@ -11589,11 +11607,11 @@
         <v/>
       </c>
       <c r="D45" s="23">
-        <f>($B$3/$B$5)*EXP(-A45*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A45*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E45" s="23">
-        <f>-$B$3*EXP(-A45*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D45</f>
         <v/>
       </c>
       <c r="F45" s="5" t="n"/>
@@ -11623,11 +11641,11 @@
         <v/>
       </c>
       <c r="W45" s="23">
-        <f>($U$3/$U$5)*EXP(-T45*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T45*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X45" s="23">
-        <f>-$U$3*EXP(-T45*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W45</f>
         <v/>
       </c>
       <c r="Y45" s="5" t="n"/>
@@ -11659,11 +11677,11 @@
         <v/>
       </c>
       <c r="AR45" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO45*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO45*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS45" s="23">
-        <f>-$AP$3*EXP(-AO45*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR45</f>
         <v/>
       </c>
       <c r="AT45" s="5" t="n"/>
@@ -11691,11 +11709,11 @@
         <v/>
       </c>
       <c r="D46" s="20">
-        <f>($B$3/$B$5)*EXP(-A46*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A46*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E46" s="20">
-        <f>-$B$3*EXP(-A46*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D46</f>
         <v/>
       </c>
       <c r="F46" s="5" t="n"/>
@@ -11725,11 +11743,11 @@
         <v/>
       </c>
       <c r="W46" s="20">
-        <f>($U$3/$U$5)*EXP(-T46*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T46*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X46" s="20">
-        <f>-$U$3*EXP(-T46*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W46</f>
         <v/>
       </c>
       <c r="Y46" s="5" t="n"/>
@@ -11761,11 +11779,11 @@
         <v/>
       </c>
       <c r="AR46" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO46*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO46*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS46" s="20">
-        <f>-$AP$3*EXP(-AO46*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR46</f>
         <v/>
       </c>
       <c r="AT46" s="5" t="n"/>
@@ -11793,11 +11811,11 @@
         <v/>
       </c>
       <c r="D47" s="23">
-        <f>($B$3/$B$5)*EXP(-A47*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A47*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E47" s="23">
-        <f>-$B$3*EXP(-A47*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D47</f>
         <v/>
       </c>
       <c r="F47" s="5" t="n"/>
@@ -11827,11 +11845,11 @@
         <v/>
       </c>
       <c r="W47" s="23">
-        <f>($U$3/$U$5)*EXP(-T47*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T47*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X47" s="23">
-        <f>-$U$3*EXP(-T47*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W47</f>
         <v/>
       </c>
       <c r="Y47" s="5" t="n"/>
@@ -11863,11 +11881,11 @@
         <v/>
       </c>
       <c r="AR47" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO47*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO47*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS47" s="23">
-        <f>-$AP$3*EXP(-AO47*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR47</f>
         <v/>
       </c>
       <c r="AT47" s="5" t="n"/>
@@ -11895,11 +11913,11 @@
         <v/>
       </c>
       <c r="D48" s="20">
-        <f>($B$3/$B$5)*EXP(-A48*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A48*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E48" s="20">
-        <f>-$B$3*EXP(-A48*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D48</f>
         <v/>
       </c>
       <c r="F48" s="5" t="n"/>
@@ -11929,11 +11947,11 @@
         <v/>
       </c>
       <c r="W48" s="20">
-        <f>($U$3/$U$5)*EXP(-T48*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T48*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X48" s="20">
-        <f>-$U$3*EXP(-T48*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W48</f>
         <v/>
       </c>
       <c r="Y48" s="5" t="n"/>
@@ -11965,11 +11983,11 @@
         <v/>
       </c>
       <c r="AR48" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO48*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO48*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS48" s="20">
-        <f>-$AP$3*EXP(-AO48*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR48</f>
         <v/>
       </c>
       <c r="AT48" s="5" t="n"/>
@@ -11997,11 +12015,11 @@
         <v/>
       </c>
       <c r="D49" s="23">
-        <f>($B$3/$B$5)*EXP(-A49*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A49*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E49" s="23">
-        <f>-$B$3*EXP(-A49*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D49</f>
         <v/>
       </c>
       <c r="F49" s="5" t="n"/>
@@ -12031,11 +12049,11 @@
         <v/>
       </c>
       <c r="W49" s="23">
-        <f>($U$3/$U$5)*EXP(-T49*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T49*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X49" s="23">
-        <f>-$U$3*EXP(-T49*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W49</f>
         <v/>
       </c>
       <c r="Y49" s="5" t="n"/>
@@ -12067,11 +12085,11 @@
         <v/>
       </c>
       <c r="AR49" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO49*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO49*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS49" s="23">
-        <f>-$AP$3*EXP(-AO49*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR49</f>
         <v/>
       </c>
       <c r="AT49" s="5" t="n"/>
@@ -12099,11 +12117,11 @@
         <v/>
       </c>
       <c r="D50" s="20">
-        <f>($B$3/$B$5)*EXP(-A50*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A50*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E50" s="20">
-        <f>-$B$3*EXP(-A50*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D50</f>
         <v/>
       </c>
       <c r="F50" s="5" t="n"/>
@@ -12133,11 +12151,11 @@
         <v/>
       </c>
       <c r="W50" s="20">
-        <f>($U$3/$U$5)*EXP(-T50*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T50*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X50" s="20">
-        <f>-$U$3*EXP(-T50*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W50</f>
         <v/>
       </c>
       <c r="Y50" s="5" t="n"/>
@@ -12169,11 +12187,11 @@
         <v/>
       </c>
       <c r="AR50" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO50*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO50*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS50" s="20">
-        <f>-$AP$3*EXP(-AO50*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR50</f>
         <v/>
       </c>
       <c r="AT50" s="5" t="n"/>
@@ -12201,11 +12219,11 @@
         <v/>
       </c>
       <c r="D51" s="23">
-        <f>($B$3/$B$5)*EXP(-A51*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A51*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E51" s="23">
-        <f>-$B$3*EXP(-A51*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D51</f>
         <v/>
       </c>
       <c r="F51" s="5" t="n"/>
@@ -12235,11 +12253,11 @@
         <v/>
       </c>
       <c r="W51" s="23">
-        <f>($U$3/$U$5)*EXP(-T51*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T51*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X51" s="23">
-        <f>-$U$3*EXP(-T51*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W51</f>
         <v/>
       </c>
       <c r="Y51" s="5" t="n"/>
@@ -12271,11 +12289,11 @@
         <v/>
       </c>
       <c r="AR51" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO51*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO51*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS51" s="23">
-        <f>-$AP$3*EXP(-AO51*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR51</f>
         <v/>
       </c>
       <c r="AT51" s="5" t="n"/>
@@ -12303,11 +12321,11 @@
         <v/>
       </c>
       <c r="D52" s="20">
-        <f>($B$3/$B$5)*EXP(-A52*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A52*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E52" s="20">
-        <f>-$B$3*EXP(-A52*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D52</f>
         <v/>
       </c>
       <c r="F52" s="5" t="n"/>
@@ -12337,11 +12355,11 @@
         <v/>
       </c>
       <c r="W52" s="20">
-        <f>($U$3/$U$5)*EXP(-T52*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T52*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X52" s="20">
-        <f>-$U$3*EXP(-T52*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W52</f>
         <v/>
       </c>
       <c r="Y52" s="5" t="n"/>
@@ -12373,11 +12391,11 @@
         <v/>
       </c>
       <c r="AR52" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO52*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO52*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS52" s="20">
-        <f>-$AP$3*EXP(-AO52*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR52</f>
         <v/>
       </c>
       <c r="AT52" s="5" t="n"/>
@@ -12405,11 +12423,11 @@
         <v/>
       </c>
       <c r="D53" s="23">
-        <f>($B$3/$B$5)*EXP(-A53*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A53*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E53" s="23">
-        <f>-$B$3*EXP(-A53*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D53</f>
         <v/>
       </c>
       <c r="F53" s="5" t="n"/>
@@ -12439,11 +12457,11 @@
         <v/>
       </c>
       <c r="W53" s="23">
-        <f>($U$3/$U$5)*EXP(-T53*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T53*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X53" s="23">
-        <f>-$U$3*EXP(-T53*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W53</f>
         <v/>
       </c>
       <c r="Y53" s="5" t="n"/>
@@ -12475,11 +12493,11 @@
         <v/>
       </c>
       <c r="AR53" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO53*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO53*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS53" s="23">
-        <f>-$AP$3*EXP(-AO53*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR53</f>
         <v/>
       </c>
       <c r="AT53" s="5" t="n"/>
@@ -12507,11 +12525,11 @@
         <v/>
       </c>
       <c r="D54" s="20">
-        <f>($B$3/$B$5)*EXP(-A54*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A54*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E54" s="20">
-        <f>-$B$3*EXP(-A54*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D54</f>
         <v/>
       </c>
       <c r="F54" s="5" t="n"/>
@@ -12541,11 +12559,11 @@
         <v/>
       </c>
       <c r="W54" s="20">
-        <f>($U$3/$U$5)*EXP(-T54*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T54*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X54" s="20">
-        <f>-$U$3*EXP(-T54*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W54</f>
         <v/>
       </c>
       <c r="Y54" s="5" t="n"/>
@@ -12577,11 +12595,11 @@
         <v/>
       </c>
       <c r="AR54" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO54*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO54*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS54" s="20">
-        <f>-$AP$3*EXP(-AO54*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR54</f>
         <v/>
       </c>
       <c r="AT54" s="5" t="n"/>
@@ -12609,11 +12627,11 @@
         <v/>
       </c>
       <c r="D55" s="23">
-        <f>($B$3/$B$5)*EXP(-A55*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A55*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E55" s="23">
-        <f>-$B$3*EXP(-A55*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D55</f>
         <v/>
       </c>
       <c r="F55" s="5" t="n"/>
@@ -12643,11 +12661,11 @@
         <v/>
       </c>
       <c r="W55" s="23">
-        <f>($U$3/$U$5)*EXP(-T55*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T55*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X55" s="23">
-        <f>-$U$3*EXP(-T55*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W55</f>
         <v/>
       </c>
       <c r="Y55" s="5" t="n"/>
@@ -12679,11 +12697,11 @@
         <v/>
       </c>
       <c r="AR55" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO55*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO55*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS55" s="23">
-        <f>-$AP$3*EXP(-AO55*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR55</f>
         <v/>
       </c>
       <c r="AT55" s="5" t="n"/>
@@ -12711,11 +12729,11 @@
         <v/>
       </c>
       <c r="D56" s="20">
-        <f>($B$3/$B$5)*EXP(-A56*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A56*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E56" s="20">
-        <f>-$B$3*EXP(-A56*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D56</f>
         <v/>
       </c>
       <c r="F56" s="5" t="n"/>
@@ -12745,11 +12763,11 @@
         <v/>
       </c>
       <c r="W56" s="20">
-        <f>($U$3/$U$5)*EXP(-T56*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T56*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X56" s="20">
-        <f>-$U$3*EXP(-T56*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W56</f>
         <v/>
       </c>
       <c r="Y56" s="5" t="n"/>
@@ -12781,11 +12799,11 @@
         <v/>
       </c>
       <c r="AR56" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO56*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO56*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS56" s="20">
-        <f>-$AP$3*EXP(-AO56*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR56</f>
         <v/>
       </c>
       <c r="AT56" s="5" t="n"/>
@@ -12813,11 +12831,11 @@
         <v/>
       </c>
       <c r="D57" s="23">
-        <f>($B$3/$B$5)*EXP(-A57*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A57*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E57" s="23">
-        <f>-$B$3*EXP(-A57*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D57</f>
         <v/>
       </c>
       <c r="F57" s="5" t="n"/>
@@ -12847,11 +12865,11 @@
         <v/>
       </c>
       <c r="W57" s="23">
-        <f>($U$3/$U$5)*EXP(-T57*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T57*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X57" s="23">
-        <f>-$U$3*EXP(-T57*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W57</f>
         <v/>
       </c>
       <c r="Y57" s="5" t="n"/>
@@ -12883,11 +12901,11 @@
         <v/>
       </c>
       <c r="AR57" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO57*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO57*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS57" s="23">
-        <f>-$AP$3*EXP(-AO57*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR57</f>
         <v/>
       </c>
       <c r="AT57" s="5" t="n"/>
@@ -12915,11 +12933,11 @@
         <v/>
       </c>
       <c r="D58" s="20">
-        <f>($B$3/$B$5)*EXP(-A58*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A58*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E58" s="20">
-        <f>-$B$3*EXP(-A58*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D58</f>
         <v/>
       </c>
       <c r="F58" s="5" t="n"/>
@@ -12949,11 +12967,11 @@
         <v/>
       </c>
       <c r="W58" s="20">
-        <f>($U$3/$U$5)*EXP(-T58*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T58*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X58" s="20">
-        <f>-$U$3*EXP(-T58*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W58</f>
         <v/>
       </c>
       <c r="Y58" s="5" t="n"/>
@@ -12985,11 +13003,11 @@
         <v/>
       </c>
       <c r="AR58" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO58*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO58*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS58" s="20">
-        <f>-$AP$3*EXP(-AO58*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR58</f>
         <v/>
       </c>
       <c r="AT58" s="5" t="n"/>
@@ -13017,11 +13035,11 @@
         <v/>
       </c>
       <c r="D59" s="23">
-        <f>($B$3/$B$5)*EXP(-A59*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A59*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E59" s="23">
-        <f>-$B$3*EXP(-A59*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D59</f>
         <v/>
       </c>
       <c r="F59" s="5" t="n"/>
@@ -13051,11 +13069,11 @@
         <v/>
       </c>
       <c r="W59" s="23">
-        <f>($U$3/$U$5)*EXP(-T59*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T59*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X59" s="23">
-        <f>-$U$3*EXP(-T59*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W59</f>
         <v/>
       </c>
       <c r="Y59" s="5" t="n"/>
@@ -13087,11 +13105,11 @@
         <v/>
       </c>
       <c r="AR59" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AO59*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO59*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS59" s="23">
-        <f>-$AP$3*EXP(-AO59*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR59</f>
         <v/>
       </c>
       <c r="AT59" s="5" t="n"/>
@@ -13119,11 +13137,11 @@
         <v/>
       </c>
       <c r="D60" s="20">
-        <f>($B$3/$B$5)*EXP(-A60*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-A60*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="E60" s="20">
-        <f>-$B$3*EXP(-A60*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*D60</f>
         <v/>
       </c>
       <c r="F60" s="5" t="n"/>
@@ -13153,11 +13171,11 @@
         <v/>
       </c>
       <c r="W60" s="20">
-        <f>($U$3/$U$5)*EXP(-T60*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-T60*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="X60" s="20">
-        <f>-$U$3*EXP(-T60*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*W60</f>
         <v/>
       </c>
       <c r="Y60" s="5" t="n"/>
@@ -13189,11 +13207,11 @@
         <v/>
       </c>
       <c r="AR60" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AO60*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AO60*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AS60" s="20">
-        <f>-$AP$3*EXP(-AO60*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AR60</f>
         <v/>
       </c>
       <c r="AT60" s="5" t="n"/>
@@ -13781,11 +13799,11 @@
         <v>0</v>
       </c>
       <c r="J70" s="20">
-        <f>($B$3/$B$5)*EXP(-I70*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I70*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K70" s="20">
-        <f>-$B$3*EXP(-I70*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J70</f>
         <v/>
       </c>
       <c r="L70" s="5" t="n"/>
@@ -13808,11 +13826,11 @@
         <v>0</v>
       </c>
       <c r="AC70" s="20">
-        <f>($U$3/$U$5)*EXP(-AB70*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB70*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD70" s="20">
-        <f>-$U$3*EXP(-AB70*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC70</f>
         <v/>
       </c>
       <c r="AE70" s="5" t="n"/>
@@ -13837,11 +13855,11 @@
         <v>0</v>
       </c>
       <c r="AX70" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW70*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW70*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY70" s="20">
-        <f>-$AP$3*EXP(-AW70*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX70</f>
         <v/>
       </c>
       <c r="AZ70" s="5" t="n"/>
@@ -13863,11 +13881,11 @@
         <v/>
       </c>
       <c r="J71" s="23">
-        <f>($B$3/$B$5)*EXP(-I71*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I71*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K71" s="23">
-        <f>-$B$3*EXP(-I71*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J71</f>
         <v/>
       </c>
       <c r="L71" s="5" t="n"/>
@@ -13891,11 +13909,11 @@
         <v/>
       </c>
       <c r="AC71" s="23">
-        <f>($U$3/$U$5)*EXP(-AB71*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB71*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD71" s="23">
-        <f>-$U$3*EXP(-AB71*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC71</f>
         <v/>
       </c>
       <c r="AE71" s="5" t="n"/>
@@ -13921,11 +13939,11 @@
         <v/>
       </c>
       <c r="AX71" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW71*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW71*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY71" s="23">
-        <f>-$AP$3*EXP(-AW71*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX71</f>
         <v/>
       </c>
       <c r="AZ71" s="5" t="n"/>
@@ -13947,11 +13965,11 @@
         <v/>
       </c>
       <c r="J72" s="20">
-        <f>($B$3/$B$5)*EXP(-I72*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I72*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K72" s="20">
-        <f>-$B$3*EXP(-I72*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J72</f>
         <v/>
       </c>
       <c r="L72" s="5" t="n"/>
@@ -13975,11 +13993,11 @@
         <v/>
       </c>
       <c r="AC72" s="20">
-        <f>($U$3/$U$5)*EXP(-AB72*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB72*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD72" s="20">
-        <f>-$U$3*EXP(-AB72*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC72</f>
         <v/>
       </c>
       <c r="AE72" s="5" t="n"/>
@@ -14005,11 +14023,11 @@
         <v/>
       </c>
       <c r="AX72" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW72*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW72*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY72" s="20">
-        <f>-$AP$3*EXP(-AW72*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX72</f>
         <v/>
       </c>
       <c r="AZ72" s="5" t="n"/>
@@ -14031,11 +14049,11 @@
         <v/>
       </c>
       <c r="J73" s="23">
-        <f>($B$3/$B$5)*EXP(-I73*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I73*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K73" s="23">
-        <f>-$B$3*EXP(-I73*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J73</f>
         <v/>
       </c>
       <c r="L73" s="5" t="n"/>
@@ -14059,11 +14077,11 @@
         <v/>
       </c>
       <c r="AC73" s="23">
-        <f>($U$3/$U$5)*EXP(-AB73*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB73*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD73" s="23">
-        <f>-$U$3*EXP(-AB73*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC73</f>
         <v/>
       </c>
       <c r="AE73" s="5" t="n"/>
@@ -14089,11 +14107,11 @@
         <v/>
       </c>
       <c r="AX73" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW73*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW73*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY73" s="23">
-        <f>-$AP$3*EXP(-AW73*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX73</f>
         <v/>
       </c>
       <c r="AZ73" s="5" t="n"/>
@@ -14115,11 +14133,11 @@
         <v/>
       </c>
       <c r="J74" s="20">
-        <f>($B$3/$B$5)*EXP(-I74*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I74*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K74" s="20">
-        <f>-$B$3*EXP(-I74*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J74</f>
         <v/>
       </c>
       <c r="L74" s="5" t="n"/>
@@ -14143,11 +14161,11 @@
         <v/>
       </c>
       <c r="AC74" s="20">
-        <f>($U$3/$U$5)*EXP(-AB74*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB74*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD74" s="20">
-        <f>-$U$3*EXP(-AB74*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC74</f>
         <v/>
       </c>
       <c r="AE74" s="5" t="n"/>
@@ -14173,11 +14191,11 @@
         <v/>
       </c>
       <c r="AX74" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW74*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW74*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY74" s="20">
-        <f>-$AP$3*EXP(-AW74*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX74</f>
         <v/>
       </c>
       <c r="AZ74" s="5" t="n"/>
@@ -14199,11 +14217,11 @@
         <v/>
       </c>
       <c r="J75" s="23">
-        <f>($B$3/$B$5)*EXP(-I75*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I75*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K75" s="23">
-        <f>-$B$3*EXP(-I75*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J75</f>
         <v/>
       </c>
       <c r="L75" s="5" t="n"/>
@@ -14227,11 +14245,11 @@
         <v/>
       </c>
       <c r="AC75" s="23">
-        <f>($U$3/$U$5)*EXP(-AB75*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB75*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD75" s="23">
-        <f>-$U$3*EXP(-AB75*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC75</f>
         <v/>
       </c>
       <c r="AE75" s="5" t="n"/>
@@ -14257,11 +14275,11 @@
         <v/>
       </c>
       <c r="AX75" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW75*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW75*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY75" s="23">
-        <f>-$AP$3*EXP(-AW75*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX75</f>
         <v/>
       </c>
       <c r="AZ75" s="5" t="n"/>
@@ -14283,11 +14301,11 @@
         <v/>
       </c>
       <c r="J76" s="20">
-        <f>($B$3/$B$5)*EXP(-I76*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I76*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K76" s="20">
-        <f>-$B$3*EXP(-I76*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J76</f>
         <v/>
       </c>
       <c r="L76" s="5" t="n"/>
@@ -14311,11 +14329,11 @@
         <v/>
       </c>
       <c r="AC76" s="20">
-        <f>($U$3/$U$5)*EXP(-AB76*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB76*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD76" s="20">
-        <f>-$U$3*EXP(-AB76*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC76</f>
         <v/>
       </c>
       <c r="AE76" s="5" t="n"/>
@@ -14341,11 +14359,11 @@
         <v/>
       </c>
       <c r="AX76" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW76*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW76*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY76" s="20">
-        <f>-$AP$3*EXP(-AW76*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX76</f>
         <v/>
       </c>
       <c r="AZ76" s="5" t="n"/>
@@ -14367,11 +14385,11 @@
         <v/>
       </c>
       <c r="J77" s="23">
-        <f>($B$3/$B$5)*EXP(-I77*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I77*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K77" s="23">
-        <f>-$B$3*EXP(-I77*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J77</f>
         <v/>
       </c>
       <c r="L77" s="5" t="n"/>
@@ -14395,11 +14413,11 @@
         <v/>
       </c>
       <c r="AC77" s="23">
-        <f>($U$3/$U$5)*EXP(-AB77*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB77*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD77" s="23">
-        <f>-$U$3*EXP(-AB77*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC77</f>
         <v/>
       </c>
       <c r="AE77" s="5" t="n"/>
@@ -14425,11 +14443,11 @@
         <v/>
       </c>
       <c r="AX77" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW77*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW77*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY77" s="23">
-        <f>-$AP$3*EXP(-AW77*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX77</f>
         <v/>
       </c>
       <c r="AZ77" s="5" t="n"/>
@@ -14451,11 +14469,11 @@
         <v/>
       </c>
       <c r="J78" s="20">
-        <f>($B$3/$B$5)*EXP(-I78*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I78*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K78" s="20">
-        <f>-$B$3*EXP(-I78*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J78</f>
         <v/>
       </c>
       <c r="L78" s="5" t="n"/>
@@ -14479,11 +14497,11 @@
         <v/>
       </c>
       <c r="AC78" s="20">
-        <f>($U$3/$U$5)*EXP(-AB78*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB78*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD78" s="20">
-        <f>-$U$3*EXP(-AB78*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC78</f>
         <v/>
       </c>
       <c r="AE78" s="5" t="n"/>
@@ -14509,11 +14527,11 @@
         <v/>
       </c>
       <c r="AX78" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW78*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW78*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY78" s="20">
-        <f>-$AP$3*EXP(-AW78*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX78</f>
         <v/>
       </c>
       <c r="AZ78" s="5" t="n"/>
@@ -14535,11 +14553,11 @@
         <v/>
       </c>
       <c r="J79" s="23">
-        <f>($B$3/$B$5)*EXP(-I79*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I79*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K79" s="23">
-        <f>-$B$3*EXP(-I79*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J79</f>
         <v/>
       </c>
       <c r="L79" s="5" t="n"/>
@@ -14563,11 +14581,11 @@
         <v/>
       </c>
       <c r="AC79" s="23">
-        <f>($U$3/$U$5)*EXP(-AB79*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB79*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD79" s="23">
-        <f>-$U$3*EXP(-AB79*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC79</f>
         <v/>
       </c>
       <c r="AE79" s="5" t="n"/>
@@ -14593,11 +14611,11 @@
         <v/>
       </c>
       <c r="AX79" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW79*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW79*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY79" s="23">
-        <f>-$AP$3*EXP(-AW79*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX79</f>
         <v/>
       </c>
       <c r="AZ79" s="5" t="n"/>
@@ -14619,11 +14637,11 @@
         <v/>
       </c>
       <c r="J80" s="20">
-        <f>($B$3/$B$5)*EXP(-I80*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I80*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K80" s="20">
-        <f>-$B$3*EXP(-I80*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J80</f>
         <v/>
       </c>
       <c r="L80" s="5" t="n"/>
@@ -14647,11 +14665,11 @@
         <v/>
       </c>
       <c r="AC80" s="20">
-        <f>($U$3/$U$5)*EXP(-AB80*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB80*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD80" s="20">
-        <f>-$U$3*EXP(-AB80*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC80</f>
         <v/>
       </c>
       <c r="AE80" s="5" t="n"/>
@@ -14677,11 +14695,11 @@
         <v/>
       </c>
       <c r="AX80" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW80*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW80*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY80" s="20">
-        <f>-$AP$3*EXP(-AW80*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX80</f>
         <v/>
       </c>
       <c r="AZ80" s="5" t="n"/>
@@ -14703,11 +14721,11 @@
         <v/>
       </c>
       <c r="J81" s="23">
-        <f>($B$3/$B$5)*EXP(-I81*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I81*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K81" s="23">
-        <f>-$B$3*EXP(-I81*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J81</f>
         <v/>
       </c>
       <c r="L81" s="5" t="n"/>
@@ -14731,11 +14749,11 @@
         <v/>
       </c>
       <c r="AC81" s="23">
-        <f>($U$3/$U$5)*EXP(-AB81*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB81*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD81" s="23">
-        <f>-$U$3*EXP(-AB81*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC81</f>
         <v/>
       </c>
       <c r="AE81" s="5" t="n"/>
@@ -14761,11 +14779,11 @@
         <v/>
       </c>
       <c r="AX81" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW81*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW81*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY81" s="23">
-        <f>-$AP$3*EXP(-AW81*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX81</f>
         <v/>
       </c>
       <c r="AZ81" s="5" t="n"/>
@@ -14787,11 +14805,11 @@
         <v/>
       </c>
       <c r="J82" s="20">
-        <f>($B$3/$B$5)*EXP(-I82*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I82*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K82" s="20">
-        <f>-$B$3*EXP(-I82*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J82</f>
         <v/>
       </c>
       <c r="L82" s="5" t="n"/>
@@ -14815,11 +14833,11 @@
         <v/>
       </c>
       <c r="AC82" s="20">
-        <f>($U$3/$U$5)*EXP(-AB82*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB82*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD82" s="20">
-        <f>-$U$3*EXP(-AB82*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC82</f>
         <v/>
       </c>
       <c r="AE82" s="5" t="n"/>
@@ -14845,11 +14863,11 @@
         <v/>
       </c>
       <c r="AX82" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW82*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW82*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY82" s="20">
-        <f>-$AP$3*EXP(-AW82*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX82</f>
         <v/>
       </c>
       <c r="AZ82" s="5" t="n"/>
@@ -14871,11 +14889,11 @@
         <v/>
       </c>
       <c r="J83" s="23">
-        <f>($B$3/$B$5)*EXP(-I83*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I83*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K83" s="23">
-        <f>-$B$3*EXP(-I83*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J83</f>
         <v/>
       </c>
       <c r="L83" s="5" t="n"/>
@@ -14899,11 +14917,11 @@
         <v/>
       </c>
       <c r="AC83" s="23">
-        <f>($U$3/$U$5)*EXP(-AB83*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB83*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD83" s="23">
-        <f>-$U$3*EXP(-AB83*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC83</f>
         <v/>
       </c>
       <c r="AE83" s="5" t="n"/>
@@ -14929,11 +14947,11 @@
         <v/>
       </c>
       <c r="AX83" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW83*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW83*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY83" s="23">
-        <f>-$AP$3*EXP(-AW83*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX83</f>
         <v/>
       </c>
       <c r="AZ83" s="5" t="n"/>
@@ -14955,11 +14973,11 @@
         <v/>
       </c>
       <c r="J84" s="20">
-        <f>($B$3/$B$5)*EXP(-I84*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I84*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K84" s="20">
-        <f>-$B$3*EXP(-I84*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J84</f>
         <v/>
       </c>
       <c r="L84" s="5" t="n"/>
@@ -14983,11 +15001,11 @@
         <v/>
       </c>
       <c r="AC84" s="20">
-        <f>($U$3/$U$5)*EXP(-AB84*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB84*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD84" s="20">
-        <f>-$U$3*EXP(-AB84*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC84</f>
         <v/>
       </c>
       <c r="AE84" s="5" t="n"/>
@@ -15013,11 +15031,11 @@
         <v/>
       </c>
       <c r="AX84" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW84*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW84*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY84" s="20">
-        <f>-$AP$3*EXP(-AW84*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX84</f>
         <v/>
       </c>
       <c r="AZ84" s="5" t="n"/>
@@ -15039,11 +15057,11 @@
         <v/>
       </c>
       <c r="J85" s="23">
-        <f>($B$3/$B$5)*EXP(-I85*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I85*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K85" s="23">
-        <f>-$B$3*EXP(-I85*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J85</f>
         <v/>
       </c>
       <c r="L85" s="5" t="n"/>
@@ -15067,11 +15085,11 @@
         <v/>
       </c>
       <c r="AC85" s="23">
-        <f>($U$3/$U$5)*EXP(-AB85*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB85*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD85" s="23">
-        <f>-$U$3*EXP(-AB85*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC85</f>
         <v/>
       </c>
       <c r="AE85" s="5" t="n"/>
@@ -15097,11 +15115,11 @@
         <v/>
       </c>
       <c r="AX85" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW85*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW85*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY85" s="23">
-        <f>-$AP$3*EXP(-AW85*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX85</f>
         <v/>
       </c>
       <c r="AZ85" s="5" t="n"/>
@@ -15123,11 +15141,11 @@
         <v/>
       </c>
       <c r="J86" s="20">
-        <f>($B$3/$B$5)*EXP(-I86*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I86*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K86" s="20">
-        <f>-$B$3*EXP(-I86*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J86</f>
         <v/>
       </c>
       <c r="L86" s="5" t="n"/>
@@ -15151,11 +15169,11 @@
         <v/>
       </c>
       <c r="AC86" s="20">
-        <f>($U$3/$U$5)*EXP(-AB86*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB86*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD86" s="20">
-        <f>-$U$3*EXP(-AB86*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC86</f>
         <v/>
       </c>
       <c r="AE86" s="5" t="n"/>
@@ -15181,11 +15199,11 @@
         <v/>
       </c>
       <c r="AX86" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW86*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW86*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY86" s="20">
-        <f>-$AP$3*EXP(-AW86*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX86</f>
         <v/>
       </c>
       <c r="AZ86" s="5" t="n"/>
@@ -15207,11 +15225,11 @@
         <v/>
       </c>
       <c r="J87" s="23">
-        <f>($B$3/$B$5)*EXP(-I87*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I87*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K87" s="23">
-        <f>-$B$3*EXP(-I87*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J87</f>
         <v/>
       </c>
       <c r="L87" s="5" t="n"/>
@@ -15235,11 +15253,11 @@
         <v/>
       </c>
       <c r="AC87" s="23">
-        <f>($U$3/$U$5)*EXP(-AB87*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB87*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD87" s="23">
-        <f>-$U$3*EXP(-AB87*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC87</f>
         <v/>
       </c>
       <c r="AE87" s="5" t="n"/>
@@ -15265,11 +15283,11 @@
         <v/>
       </c>
       <c r="AX87" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW87*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW87*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY87" s="23">
-        <f>-$AP$3*EXP(-AW87*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX87</f>
         <v/>
       </c>
       <c r="AZ87" s="5" t="n"/>
@@ -15291,11 +15309,11 @@
         <v/>
       </c>
       <c r="J88" s="20">
-        <f>($B$3/$B$5)*EXP(-I88*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I88*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K88" s="20">
-        <f>-$B$3*EXP(-I88*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J88</f>
         <v/>
       </c>
       <c r="L88" s="5" t="n"/>
@@ -15319,11 +15337,11 @@
         <v/>
       </c>
       <c r="AC88" s="20">
-        <f>($U$3/$U$5)*EXP(-AB88*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB88*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD88" s="20">
-        <f>-$U$3*EXP(-AB88*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC88</f>
         <v/>
       </c>
       <c r="AE88" s="5" t="n"/>
@@ -15349,11 +15367,11 @@
         <v/>
       </c>
       <c r="AX88" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW88*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW88*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY88" s="20">
-        <f>-$AP$3*EXP(-AW88*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX88</f>
         <v/>
       </c>
       <c r="AZ88" s="5" t="n"/>
@@ -15375,11 +15393,11 @@
         <v/>
       </c>
       <c r="J89" s="23">
-        <f>($B$3/$B$5)*EXP(-I89*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I89*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K89" s="23">
-        <f>-$B$3*EXP(-I89*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J89</f>
         <v/>
       </c>
       <c r="L89" s="5" t="n"/>
@@ -15403,11 +15421,11 @@
         <v/>
       </c>
       <c r="AC89" s="23">
-        <f>($U$3/$U$5)*EXP(-AB89*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB89*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD89" s="23">
-        <f>-$U$3*EXP(-AB89*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC89</f>
         <v/>
       </c>
       <c r="AE89" s="5" t="n"/>
@@ -15433,11 +15451,11 @@
         <v/>
       </c>
       <c r="AX89" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW89*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW89*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY89" s="23">
-        <f>-$AP$3*EXP(-AW89*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX89</f>
         <v/>
       </c>
       <c r="AZ89" s="5" t="n"/>
@@ -15459,11 +15477,11 @@
         <v/>
       </c>
       <c r="J90" s="20">
-        <f>($B$3/$B$5)*EXP(-I90*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I90*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K90" s="20">
-        <f>-$B$3*EXP(-I90*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J90</f>
         <v/>
       </c>
       <c r="L90" s="5" t="n"/>
@@ -15487,11 +15505,11 @@
         <v/>
       </c>
       <c r="AC90" s="20">
-        <f>($U$3/$U$5)*EXP(-AB90*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB90*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD90" s="20">
-        <f>-$U$3*EXP(-AB90*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC90</f>
         <v/>
       </c>
       <c r="AE90" s="5" t="n"/>
@@ -15517,11 +15535,11 @@
         <v/>
       </c>
       <c r="AX90" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW90*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW90*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY90" s="20">
-        <f>-$AP$3*EXP(-AW90*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX90</f>
         <v/>
       </c>
       <c r="AZ90" s="5" t="n"/>
@@ -15543,11 +15561,11 @@
         <v/>
       </c>
       <c r="J91" s="23">
-        <f>($B$3/$B$5)*EXP(-I91*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I91*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K91" s="23">
-        <f>-$B$3*EXP(-I91*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J91</f>
         <v/>
       </c>
       <c r="L91" s="5" t="n"/>
@@ -15571,11 +15589,11 @@
         <v/>
       </c>
       <c r="AC91" s="23">
-        <f>($U$3/$U$5)*EXP(-AB91*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB91*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD91" s="23">
-        <f>-$U$3*EXP(-AB91*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC91</f>
         <v/>
       </c>
       <c r="AE91" s="5" t="n"/>
@@ -15601,11 +15619,11 @@
         <v/>
       </c>
       <c r="AX91" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW91*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW91*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY91" s="23">
-        <f>-$AP$3*EXP(-AW91*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX91</f>
         <v/>
       </c>
       <c r="AZ91" s="5" t="n"/>
@@ -15627,11 +15645,11 @@
         <v/>
       </c>
       <c r="J92" s="20">
-        <f>($B$3/$B$5)*EXP(-I92*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I92*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K92" s="20">
-        <f>-$B$3*EXP(-I92*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J92</f>
         <v/>
       </c>
       <c r="L92" s="5" t="n"/>
@@ -15655,11 +15673,11 @@
         <v/>
       </c>
       <c r="AC92" s="20">
-        <f>($U$3/$U$5)*EXP(-AB92*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB92*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD92" s="20">
-        <f>-$U$3*EXP(-AB92*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC92</f>
         <v/>
       </c>
       <c r="AE92" s="5" t="n"/>
@@ -15685,11 +15703,11 @@
         <v/>
       </c>
       <c r="AX92" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW92*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW92*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY92" s="20">
-        <f>-$AP$3*EXP(-AW92*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX92</f>
         <v/>
       </c>
       <c r="AZ92" s="5" t="n"/>
@@ -15711,11 +15729,11 @@
         <v/>
       </c>
       <c r="J93" s="23">
-        <f>($B$3/$B$5)*EXP(-I93*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I93*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K93" s="23">
-        <f>-$B$3*EXP(-I93*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J93</f>
         <v/>
       </c>
       <c r="L93" s="5" t="n"/>
@@ -15739,11 +15757,11 @@
         <v/>
       </c>
       <c r="AC93" s="23">
-        <f>($U$3/$U$5)*EXP(-AB93*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB93*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD93" s="23">
-        <f>-$U$3*EXP(-AB93*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC93</f>
         <v/>
       </c>
       <c r="AE93" s="5" t="n"/>
@@ -15769,11 +15787,11 @@
         <v/>
       </c>
       <c r="AX93" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW93*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW93*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY93" s="23">
-        <f>-$AP$3*EXP(-AW93*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX93</f>
         <v/>
       </c>
       <c r="AZ93" s="5" t="n"/>
@@ -15795,11 +15813,11 @@
         <v/>
       </c>
       <c r="J94" s="20">
-        <f>($B$3/$B$5)*EXP(-I94*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I94*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K94" s="20">
-        <f>-$B$3*EXP(-I94*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J94</f>
         <v/>
       </c>
       <c r="L94" s="5" t="n"/>
@@ -15823,11 +15841,11 @@
         <v/>
       </c>
       <c r="AC94" s="20">
-        <f>($U$3/$U$5)*EXP(-AB94*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB94*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD94" s="20">
-        <f>-$U$3*EXP(-AB94*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC94</f>
         <v/>
       </c>
       <c r="AE94" s="5" t="n"/>
@@ -15853,11 +15871,11 @@
         <v/>
       </c>
       <c r="AX94" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW94*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW94*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY94" s="20">
-        <f>-$AP$3*EXP(-AW94*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX94</f>
         <v/>
       </c>
       <c r="AZ94" s="5" t="n"/>
@@ -15879,11 +15897,11 @@
         <v/>
       </c>
       <c r="J95" s="23">
-        <f>($B$3/$B$5)*EXP(-I95*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I95*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K95" s="23">
-        <f>-$B$3*EXP(-I95*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J95</f>
         <v/>
       </c>
       <c r="L95" s="5" t="n"/>
@@ -15907,11 +15925,11 @@
         <v/>
       </c>
       <c r="AC95" s="23">
-        <f>($U$3/$U$5)*EXP(-AB95*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB95*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD95" s="23">
-        <f>-$U$3*EXP(-AB95*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC95</f>
         <v/>
       </c>
       <c r="AE95" s="5" t="n"/>
@@ -15937,11 +15955,11 @@
         <v/>
       </c>
       <c r="AX95" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW95*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW95*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY95" s="23">
-        <f>-$AP$3*EXP(-AW95*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX95</f>
         <v/>
       </c>
       <c r="AZ95" s="5" t="n"/>
@@ -15963,11 +15981,11 @@
         <v/>
       </c>
       <c r="J96" s="20">
-        <f>($B$3/$B$5)*EXP(-I96*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I96*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K96" s="20">
-        <f>-$B$3*EXP(-I96*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J96</f>
         <v/>
       </c>
       <c r="L96" s="5" t="n"/>
@@ -15991,11 +16009,11 @@
         <v/>
       </c>
       <c r="AC96" s="20">
-        <f>($U$3/$U$5)*EXP(-AB96*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB96*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD96" s="20">
-        <f>-$U$3*EXP(-AB96*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC96</f>
         <v/>
       </c>
       <c r="AE96" s="5" t="n"/>
@@ -16021,11 +16039,11 @@
         <v/>
       </c>
       <c r="AX96" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW96*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW96*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY96" s="20">
-        <f>-$AP$3*EXP(-AW96*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX96</f>
         <v/>
       </c>
       <c r="AZ96" s="5" t="n"/>
@@ -16047,11 +16065,11 @@
         <v/>
       </c>
       <c r="J97" s="23">
-        <f>($B$3/$B$5)*EXP(-I97*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I97*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K97" s="23">
-        <f>-$B$3*EXP(-I97*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J97</f>
         <v/>
       </c>
       <c r="L97" s="5" t="n"/>
@@ -16075,11 +16093,11 @@
         <v/>
       </c>
       <c r="AC97" s="23">
-        <f>($U$3/$U$5)*EXP(-AB97*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB97*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD97" s="23">
-        <f>-$U$3*EXP(-AB97*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC97</f>
         <v/>
       </c>
       <c r="AE97" s="5" t="n"/>
@@ -16105,11 +16123,11 @@
         <v/>
       </c>
       <c r="AX97" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW97*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW97*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY97" s="23">
-        <f>-$AP$3*EXP(-AW97*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX97</f>
         <v/>
       </c>
       <c r="AZ97" s="5" t="n"/>
@@ -16131,11 +16149,11 @@
         <v/>
       </c>
       <c r="J98" s="20">
-        <f>($B$3/$B$5)*EXP(-I98*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I98*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K98" s="20">
-        <f>-$B$3*EXP(-I98*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J98</f>
         <v/>
       </c>
       <c r="L98" s="5" t="n"/>
@@ -16159,11 +16177,11 @@
         <v/>
       </c>
       <c r="AC98" s="20">
-        <f>($U$3/$U$5)*EXP(-AB98*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB98*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD98" s="20">
-        <f>-$U$3*EXP(-AB98*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC98</f>
         <v/>
       </c>
       <c r="AE98" s="5" t="n"/>
@@ -16189,11 +16207,11 @@
         <v/>
       </c>
       <c r="AX98" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW98*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW98*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY98" s="20">
-        <f>-$AP$3*EXP(-AW98*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX98</f>
         <v/>
       </c>
       <c r="AZ98" s="5" t="n"/>
@@ -16215,11 +16233,11 @@
         <v/>
       </c>
       <c r="J99" s="23">
-        <f>($B$3/$B$5)*EXP(-I99*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I99*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K99" s="23">
-        <f>-$B$3*EXP(-I99*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J99</f>
         <v/>
       </c>
       <c r="L99" s="5" t="n"/>
@@ -16243,11 +16261,11 @@
         <v/>
       </c>
       <c r="AC99" s="23">
-        <f>($U$3/$U$5)*EXP(-AB99*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB99*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD99" s="23">
-        <f>-$U$3*EXP(-AB99*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC99</f>
         <v/>
       </c>
       <c r="AE99" s="5" t="n"/>
@@ -16273,11 +16291,11 @@
         <v/>
       </c>
       <c r="AX99" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW99*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW99*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY99" s="23">
-        <f>-$AP$3*EXP(-AW99*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX99</f>
         <v/>
       </c>
       <c r="AZ99" s="5" t="n"/>
@@ -16299,11 +16317,11 @@
         <v/>
       </c>
       <c r="J100" s="20">
-        <f>($B$3/$B$5)*EXP(-I100*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I100*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K100" s="20">
-        <f>-$B$3*EXP(-I100*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J100</f>
         <v/>
       </c>
       <c r="L100" s="5" t="n"/>
@@ -16327,11 +16345,11 @@
         <v/>
       </c>
       <c r="AC100" s="20">
-        <f>($U$3/$U$5)*EXP(-AB100*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB100*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD100" s="20">
-        <f>-$U$3*EXP(-AB100*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC100</f>
         <v/>
       </c>
       <c r="AE100" s="5" t="n"/>
@@ -16357,11 +16375,11 @@
         <v/>
       </c>
       <c r="AX100" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW100*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW100*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY100" s="20">
-        <f>-$AP$3*EXP(-AW100*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX100</f>
         <v/>
       </c>
       <c r="AZ100" s="5" t="n"/>
@@ -16383,11 +16401,11 @@
         <v/>
       </c>
       <c r="J101" s="23">
-        <f>($B$3/$B$5)*EXP(-I101*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I101*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K101" s="23">
-        <f>-$B$3*EXP(-I101*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J101</f>
         <v/>
       </c>
       <c r="L101" s="5" t="n"/>
@@ -16411,11 +16429,11 @@
         <v/>
       </c>
       <c r="AC101" s="23">
-        <f>($U$3/$U$5)*EXP(-AB101*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB101*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD101" s="23">
-        <f>-$U$3*EXP(-AB101*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC101</f>
         <v/>
       </c>
       <c r="AE101" s="5" t="n"/>
@@ -16441,11 +16459,11 @@
         <v/>
       </c>
       <c r="AX101" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW101*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW101*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY101" s="23">
-        <f>-$AP$3*EXP(-AW101*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX101</f>
         <v/>
       </c>
       <c r="AZ101" s="5" t="n"/>
@@ -16467,11 +16485,11 @@
         <v/>
       </c>
       <c r="J102" s="20">
-        <f>($B$3/$B$5)*EXP(-I102*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I102*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K102" s="20">
-        <f>-$B$3*EXP(-I102*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J102</f>
         <v/>
       </c>
       <c r="L102" s="5" t="n"/>
@@ -16495,11 +16513,11 @@
         <v/>
       </c>
       <c r="AC102" s="20">
-        <f>($U$3/$U$5)*EXP(-AB102*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB102*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD102" s="20">
-        <f>-$U$3*EXP(-AB102*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC102</f>
         <v/>
       </c>
       <c r="AE102" s="5" t="n"/>
@@ -16525,11 +16543,11 @@
         <v/>
       </c>
       <c r="AX102" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW102*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW102*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY102" s="20">
-        <f>-$AP$3*EXP(-AW102*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX102</f>
         <v/>
       </c>
       <c r="AZ102" s="5" t="n"/>
@@ -16551,11 +16569,11 @@
         <v/>
       </c>
       <c r="J103" s="23">
-        <f>($B$3/$B$5)*EXP(-I103*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I103*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K103" s="23">
-        <f>-$B$3*EXP(-I103*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J103</f>
         <v/>
       </c>
       <c r="L103" s="5" t="n"/>
@@ -16579,11 +16597,11 @@
         <v/>
       </c>
       <c r="AC103" s="23">
-        <f>($U$3/$U$5)*EXP(-AB103*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB103*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD103" s="23">
-        <f>-$U$3*EXP(-AB103*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC103</f>
         <v/>
       </c>
       <c r="AE103" s="5" t="n"/>
@@ -16609,11 +16627,11 @@
         <v/>
       </c>
       <c r="AX103" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW103*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW103*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY103" s="23">
-        <f>-$AP$3*EXP(-AW103*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX103</f>
         <v/>
       </c>
       <c r="AZ103" s="5" t="n"/>
@@ -16635,11 +16653,11 @@
         <v/>
       </c>
       <c r="J104" s="20">
-        <f>($B$3/$B$5)*EXP(-I104*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I104*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K104" s="20">
-        <f>-$B$3*EXP(-I104*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J104</f>
         <v/>
       </c>
       <c r="L104" s="5" t="n"/>
@@ -16663,11 +16681,11 @@
         <v/>
       </c>
       <c r="AC104" s="20">
-        <f>($U$3/$U$5)*EXP(-AB104*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB104*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD104" s="20">
-        <f>-$U$3*EXP(-AB104*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC104</f>
         <v/>
       </c>
       <c r="AE104" s="5" t="n"/>
@@ -16693,11 +16711,11 @@
         <v/>
       </c>
       <c r="AX104" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW104*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW104*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY104" s="20">
-        <f>-$AP$3*EXP(-AW104*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX104</f>
         <v/>
       </c>
       <c r="AZ104" s="5" t="n"/>
@@ -16719,11 +16737,11 @@
         <v/>
       </c>
       <c r="J105" s="23">
-        <f>($B$3/$B$5)*EXP(-I105*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I105*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K105" s="23">
-        <f>-$B$3*EXP(-I105*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J105</f>
         <v/>
       </c>
       <c r="L105" s="5" t="n"/>
@@ -16747,11 +16765,11 @@
         <v/>
       </c>
       <c r="AC105" s="23">
-        <f>($U$3/$U$5)*EXP(-AB105*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB105*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD105" s="23">
-        <f>-$U$3*EXP(-AB105*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC105</f>
         <v/>
       </c>
       <c r="AE105" s="5" t="n"/>
@@ -16777,11 +16795,11 @@
         <v/>
       </c>
       <c r="AX105" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW105*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW105*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY105" s="23">
-        <f>-$AP$3*EXP(-AW105*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX105</f>
         <v/>
       </c>
       <c r="AZ105" s="5" t="n"/>
@@ -16803,11 +16821,11 @@
         <v/>
       </c>
       <c r="J106" s="20">
-        <f>($B$3/$B$5)*EXP(-I106*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I106*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K106" s="20">
-        <f>-$B$3*EXP(-I106*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J106</f>
         <v/>
       </c>
       <c r="L106" s="5" t="n"/>
@@ -16831,11 +16849,11 @@
         <v/>
       </c>
       <c r="AC106" s="20">
-        <f>($U$3/$U$5)*EXP(-AB106*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB106*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD106" s="20">
-        <f>-$U$3*EXP(-AB106*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC106</f>
         <v/>
       </c>
       <c r="AE106" s="5" t="n"/>
@@ -16861,11 +16879,11 @@
         <v/>
       </c>
       <c r="AX106" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW106*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW106*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY106" s="20">
-        <f>-$AP$3*EXP(-AW106*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX106</f>
         <v/>
       </c>
       <c r="AZ106" s="5" t="n"/>
@@ -16887,11 +16905,11 @@
         <v/>
       </c>
       <c r="J107" s="23">
-        <f>($B$3/$B$5)*EXP(-I107*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I107*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K107" s="23">
-        <f>-$B$3*EXP(-I107*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J107</f>
         <v/>
       </c>
       <c r="L107" s="5" t="n"/>
@@ -16915,11 +16933,11 @@
         <v/>
       </c>
       <c r="AC107" s="23">
-        <f>($U$3/$U$5)*EXP(-AB107*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB107*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD107" s="23">
-        <f>-$U$3*EXP(-AB107*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC107</f>
         <v/>
       </c>
       <c r="AE107" s="5" t="n"/>
@@ -16945,11 +16963,11 @@
         <v/>
       </c>
       <c r="AX107" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW107*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW107*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY107" s="23">
-        <f>-$AP$3*EXP(-AW107*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX107</f>
         <v/>
       </c>
       <c r="AZ107" s="5" t="n"/>
@@ -16971,11 +16989,11 @@
         <v/>
       </c>
       <c r="J108" s="20">
-        <f>($B$3/$B$5)*EXP(-I108*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I108*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K108" s="20">
-        <f>-$B$3*EXP(-I108*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J108</f>
         <v/>
       </c>
       <c r="L108" s="5" t="n"/>
@@ -16999,11 +17017,11 @@
         <v/>
       </c>
       <c r="AC108" s="20">
-        <f>($U$3/$U$5)*EXP(-AB108*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB108*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD108" s="20">
-        <f>-$U$3*EXP(-AB108*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC108</f>
         <v/>
       </c>
       <c r="AE108" s="5" t="n"/>
@@ -17029,11 +17047,11 @@
         <v/>
       </c>
       <c r="AX108" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW108*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW108*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY108" s="20">
-        <f>-$AP$3*EXP(-AW108*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX108</f>
         <v/>
       </c>
       <c r="AZ108" s="5" t="n"/>
@@ -17055,11 +17073,11 @@
         <v/>
       </c>
       <c r="J109" s="23">
-        <f>($B$3/$B$5)*EXP(-I109*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I109*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K109" s="23">
-        <f>-$B$3*EXP(-I109*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J109</f>
         <v/>
       </c>
       <c r="L109" s="5" t="n"/>
@@ -17083,11 +17101,11 @@
         <v/>
       </c>
       <c r="AC109" s="23">
-        <f>($U$3/$U$5)*EXP(-AB109*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB109*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD109" s="23">
-        <f>-$U$3*EXP(-AB109*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC109</f>
         <v/>
       </c>
       <c r="AE109" s="5" t="n"/>
@@ -17113,11 +17131,11 @@
         <v/>
       </c>
       <c r="AX109" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW109*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW109*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY109" s="23">
-        <f>-$AP$3*EXP(-AW109*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX109</f>
         <v/>
       </c>
       <c r="AZ109" s="5" t="n"/>
@@ -17139,11 +17157,11 @@
         <v/>
       </c>
       <c r="J110" s="20">
-        <f>($B$3/$B$5)*EXP(-I110*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I110*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K110" s="20">
-        <f>-$B$3*EXP(-I110*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J110</f>
         <v/>
       </c>
       <c r="L110" s="5" t="n"/>
@@ -17167,11 +17185,11 @@
         <v/>
       </c>
       <c r="AC110" s="20">
-        <f>($U$3/$U$5)*EXP(-AB110*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB110*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD110" s="20">
-        <f>-$U$3*EXP(-AB110*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC110</f>
         <v/>
       </c>
       <c r="AE110" s="5" t="n"/>
@@ -17197,11 +17215,11 @@
         <v/>
       </c>
       <c r="AX110" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW110*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW110*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY110" s="20">
-        <f>-$AP$3*EXP(-AW110*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX110</f>
         <v/>
       </c>
       <c r="AZ110" s="5" t="n"/>
@@ -17223,11 +17241,11 @@
         <v/>
       </c>
       <c r="J111" s="23">
-        <f>($B$3/$B$5)*EXP(-I111*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I111*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K111" s="23">
-        <f>-$B$3*EXP(-I111*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J111</f>
         <v/>
       </c>
       <c r="L111" s="5" t="n"/>
@@ -17251,11 +17269,11 @@
         <v/>
       </c>
       <c r="AC111" s="23">
-        <f>($U$3/$U$5)*EXP(-AB111*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB111*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD111" s="23">
-        <f>-$U$3*EXP(-AB111*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC111</f>
         <v/>
       </c>
       <c r="AE111" s="5" t="n"/>
@@ -17281,11 +17299,11 @@
         <v/>
       </c>
       <c r="AX111" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW111*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW111*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY111" s="23">
-        <f>-$AP$3*EXP(-AW111*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX111</f>
         <v/>
       </c>
       <c r="AZ111" s="5" t="n"/>
@@ -17307,11 +17325,11 @@
         <v/>
       </c>
       <c r="J112" s="20">
-        <f>($B$3/$B$5)*EXP(-I112*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I112*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K112" s="20">
-        <f>-$B$3*EXP(-I112*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J112</f>
         <v/>
       </c>
       <c r="L112" s="5" t="n"/>
@@ -17335,11 +17353,11 @@
         <v/>
       </c>
       <c r="AC112" s="20">
-        <f>($U$3/$U$5)*EXP(-AB112*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB112*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD112" s="20">
-        <f>-$U$3*EXP(-AB112*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC112</f>
         <v/>
       </c>
       <c r="AE112" s="5" t="n"/>
@@ -17365,11 +17383,11 @@
         <v/>
       </c>
       <c r="AX112" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW112*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW112*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY112" s="20">
-        <f>-$AP$3*EXP(-AW112*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX112</f>
         <v/>
       </c>
       <c r="AZ112" s="5" t="n"/>
@@ -17391,11 +17409,11 @@
         <v/>
       </c>
       <c r="J113" s="23">
-        <f>($B$3/$B$5)*EXP(-I113*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I113*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K113" s="23">
-        <f>-$B$3*EXP(-I113*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J113</f>
         <v/>
       </c>
       <c r="L113" s="5" t="n"/>
@@ -17419,11 +17437,11 @@
         <v/>
       </c>
       <c r="AC113" s="23">
-        <f>($U$3/$U$5)*EXP(-AB113*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB113*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD113" s="23">
-        <f>-$U$3*EXP(-AB113*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC113</f>
         <v/>
       </c>
       <c r="AE113" s="5" t="n"/>
@@ -17449,11 +17467,11 @@
         <v/>
       </c>
       <c r="AX113" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW113*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW113*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY113" s="23">
-        <f>-$AP$3*EXP(-AW113*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX113</f>
         <v/>
       </c>
       <c r="AZ113" s="5" t="n"/>
@@ -17475,11 +17493,11 @@
         <v/>
       </c>
       <c r="J114" s="20">
-        <f>($B$3/$B$5)*EXP(-I114*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I114*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K114" s="20">
-        <f>-$B$3*EXP(-I114*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J114</f>
         <v/>
       </c>
       <c r="L114" s="5" t="n"/>
@@ -17503,11 +17521,11 @@
         <v/>
       </c>
       <c r="AC114" s="20">
-        <f>($U$3/$U$5)*EXP(-AB114*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB114*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD114" s="20">
-        <f>-$U$3*EXP(-AB114*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC114</f>
         <v/>
       </c>
       <c r="AE114" s="5" t="n"/>
@@ -17533,11 +17551,11 @@
         <v/>
       </c>
       <c r="AX114" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW114*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW114*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY114" s="20">
-        <f>-$AP$3*EXP(-AW114*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX114</f>
         <v/>
       </c>
       <c r="AZ114" s="5" t="n"/>
@@ -17559,11 +17577,11 @@
         <v/>
       </c>
       <c r="J115" s="23">
-        <f>($B$3/$B$5)*EXP(-I115*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I115*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K115" s="23">
-        <f>-$B$3*EXP(-I115*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J115</f>
         <v/>
       </c>
       <c r="L115" s="5" t="n"/>
@@ -17587,11 +17605,11 @@
         <v/>
       </c>
       <c r="AC115" s="23">
-        <f>($U$3/$U$5)*EXP(-AB115*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB115*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD115" s="23">
-        <f>-$U$3*EXP(-AB115*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC115</f>
         <v/>
       </c>
       <c r="AE115" s="5" t="n"/>
@@ -17617,11 +17635,11 @@
         <v/>
       </c>
       <c r="AX115" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW115*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW115*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY115" s="23">
-        <f>-$AP$3*EXP(-AW115*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX115</f>
         <v/>
       </c>
       <c r="AZ115" s="5" t="n"/>
@@ -17643,11 +17661,11 @@
         <v/>
       </c>
       <c r="J116" s="20">
-        <f>($B$3/$B$5)*EXP(-I116*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I116*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K116" s="20">
-        <f>-$B$3*EXP(-I116*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J116</f>
         <v/>
       </c>
       <c r="L116" s="5" t="n"/>
@@ -17671,11 +17689,11 @@
         <v/>
       </c>
       <c r="AC116" s="20">
-        <f>($U$3/$U$5)*EXP(-AB116*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB116*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD116" s="20">
-        <f>-$U$3*EXP(-AB116*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC116</f>
         <v/>
       </c>
       <c r="AE116" s="5" t="n"/>
@@ -17701,11 +17719,11 @@
         <v/>
       </c>
       <c r="AX116" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW116*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW116*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY116" s="20">
-        <f>-$AP$3*EXP(-AW116*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX116</f>
         <v/>
       </c>
       <c r="AZ116" s="5" t="n"/>
@@ -17727,11 +17745,11 @@
         <v/>
       </c>
       <c r="J117" s="23">
-        <f>($B$3/$B$5)*EXP(-I117*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I117*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K117" s="23">
-        <f>-$B$3*EXP(-I117*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J117</f>
         <v/>
       </c>
       <c r="L117" s="5" t="n"/>
@@ -17755,11 +17773,11 @@
         <v/>
       </c>
       <c r="AC117" s="23">
-        <f>($U$3/$U$5)*EXP(-AB117*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB117*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD117" s="23">
-        <f>-$U$3*EXP(-AB117*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC117</f>
         <v/>
       </c>
       <c r="AE117" s="5" t="n"/>
@@ -17785,11 +17803,11 @@
         <v/>
       </c>
       <c r="AX117" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW117*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW117*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY117" s="23">
-        <f>-$AP$3*EXP(-AW117*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX117</f>
         <v/>
       </c>
       <c r="AZ117" s="5" t="n"/>
@@ -17811,11 +17829,11 @@
         <v/>
       </c>
       <c r="J118" s="20">
-        <f>($B$3/$B$5)*EXP(-I118*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I118*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K118" s="20">
-        <f>-$B$3*EXP(-I118*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J118</f>
         <v/>
       </c>
       <c r="L118" s="5" t="n"/>
@@ -17839,11 +17857,11 @@
         <v/>
       </c>
       <c r="AC118" s="20">
-        <f>($U$3/$U$5)*EXP(-AB118*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB118*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD118" s="20">
-        <f>-$U$3*EXP(-AB118*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC118</f>
         <v/>
       </c>
       <c r="AE118" s="5" t="n"/>
@@ -17869,11 +17887,11 @@
         <v/>
       </c>
       <c r="AX118" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW118*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW118*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY118" s="20">
-        <f>-$AP$3*EXP(-AW118*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX118</f>
         <v/>
       </c>
       <c r="AZ118" s="5" t="n"/>
@@ -17895,11 +17913,11 @@
         <v/>
       </c>
       <c r="J119" s="23">
-        <f>($B$3/$B$5)*EXP(-I119*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I119*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K119" s="23">
-        <f>-$B$3*EXP(-I119*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J119</f>
         <v/>
       </c>
       <c r="L119" s="5" t="n"/>
@@ -17923,11 +17941,11 @@
         <v/>
       </c>
       <c r="AC119" s="23">
-        <f>($U$3/$U$5)*EXP(-AB119*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB119*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD119" s="23">
-        <f>-$U$3*EXP(-AB119*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC119</f>
         <v/>
       </c>
       <c r="AE119" s="5" t="n"/>
@@ -17953,11 +17971,11 @@
         <v/>
       </c>
       <c r="AX119" s="23">
-        <f>($AP$3/$AP$5)*EXP(-AW119*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW119*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY119" s="23">
-        <f>-$AP$3*EXP(-AW119*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX119</f>
         <v/>
       </c>
       <c r="AZ119" s="5" t="n"/>
@@ -17979,11 +17997,11 @@
         <v/>
       </c>
       <c r="J120" s="20">
-        <f>($B$3/$B$5)*EXP(-I120*$B$5/$B$6)</f>
+        <f>($B$3/$B$4)*EXP(-I120*($B$5+$E$4)/$B$6)</f>
         <v/>
       </c>
       <c r="K120" s="20">
-        <f>-$B$3*EXP(-I120*$B$5/$B$6)</f>
+        <f>-($B$5+$E$4)*J120</f>
         <v/>
       </c>
       <c r="L120" s="5" t="n"/>
@@ -18007,11 +18025,11 @@
         <v/>
       </c>
       <c r="AC120" s="20">
-        <f>($U$3/$U$5)*EXP(-AB120*$U$5/$U$6)</f>
+        <f>($U$3/$U$4)*EXP(-AB120*($U$5+$X$4)/$U$6)</f>
         <v/>
       </c>
       <c r="AD120" s="20">
-        <f>-$U$3*EXP(-AB120*$U$5/$U$6)</f>
+        <f>-($U$5+$X$4)*AC120</f>
         <v/>
       </c>
       <c r="AE120" s="5" t="n"/>
@@ -18037,11 +18055,11 @@
         <v/>
       </c>
       <c r="AX120" s="20">
-        <f>($AP$3/$AP$5)*EXP(-AW120*$AP$5/$AP$6)</f>
+        <f>($AP$3/$AP$4)*EXP(-AW120*($AP$5+$AS$4)/$AP$6)</f>
         <v/>
       </c>
       <c r="AY120" s="20">
-        <f>-$AP$3*EXP(-AW120*$AP$5/$AP$6)</f>
+        <f>-($AP$5+$AS$4)*AX120</f>
         <v/>
       </c>
       <c r="AZ120" s="5" t="n"/>
@@ -18626,7 +18644,7 @@
     <row r="131">
       <c r="A131" s="28" t="inlineStr">
         <is>
-          <t>заряд:   Iз=(E/r)*(1-EXP(-t*r/L)),   Uз=E*EXP(-t*r/L)</t>
+          <t>заряд:   Iз=(E/r1)*(1-EXP(-t*r1/L)),   Uз=E*EXP(-t*r1/L)</t>
         </is>
       </c>
       <c r="B131" s="29" t="n"/>
@@ -18687,7 +18705,7 @@
     <row r="132">
       <c r="A132" s="28" t="inlineStr">
         <is>
-          <t>разряд: Iр=(E/R)*EXP(-t*R/L),   Uр=-E*EXP(-t*R/L)</t>
+          <t>разряд: Iр=(E/r1)*EXP(-t*(R+r2)/L),   Uр=-(R+r2)*Iр,   Iр(0)=E/r1</t>
         </is>
       </c>
       <c r="B132" s="29" t="n"/>
@@ -18748,7 +18766,7 @@
     <row r="133">
       <c r="A133" s="28" t="inlineStr">
         <is>
-          <t>L в ячейке B6:  =POWER(10,-4)*9   (это 9*10^(-4) Гн)</t>
+          <t>L в B6: =POWER(10,-4)*9;   r1 в B4;   r2 в E4 (=90 Ом, как Л2 на схеме)</t>
         </is>
       </c>
       <c r="B133" s="29" t="n"/>
